--- a/resultados_akademia.xlsx
+++ b/resultados_akademia.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Ranking municipios" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Resumen por provincia" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Perfiles estratégicos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Guía de archivos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +518,11 @@
           <t>perfil</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>perfil_corto</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -574,6 +580,11 @@
           <t>Zona premium — máxima solvencia</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -631,6 +642,11 @@
           <t>Zona premium — máxima solvencia</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -688,6 +704,11 @@
           <t>Zona premium — máxima solvencia</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -745,6 +766,11 @@
           <t>Zona premium — máxima solvencia</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -802,6 +828,11 @@
           <t>Zona premium — máxima solvencia</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -859,6 +890,11 @@
           <t>Zona premium — máxima solvencia</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -916,6 +952,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -973,6 +1014,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1030,6 +1076,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1087,6 +1138,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1144,6 +1200,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1201,6 +1262,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1258,6 +1324,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1315,6 +1386,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1372,6 +1448,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1429,6 +1510,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1486,6 +1572,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1543,6 +1634,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1600,6 +1696,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1657,6 +1758,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1714,6 +1820,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1771,6 +1882,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1828,6 +1944,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1885,6 +2007,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1940,6 +2068,12 @@
       <c r="Q26" t="inlineStr">
         <is>
           <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
         </is>
       </c>
     </row>
@@ -1999,6 +2133,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2056,6 +2195,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2113,6 +2257,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2170,6 +2320,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2227,6 +2382,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2284,6 +2444,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2341,6 +2506,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2398,6 +2568,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2455,6 +2630,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2510,6 +2690,11 @@
       <c r="Q36" t="inlineStr">
         <is>
           <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
         </is>
       </c>
     </row>
@@ -2569,6 +2754,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2626,6 +2816,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2683,6 +2878,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2740,6 +2940,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2797,6 +3003,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2854,6 +3066,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2911,6 +3129,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2968,6 +3191,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3025,6 +3253,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3082,6 +3315,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3139,6 +3377,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3196,6 +3439,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3253,6 +3502,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3310,6 +3564,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3367,6 +3626,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3424,6 +3688,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3481,6 +3750,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3538,6 +3812,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3595,6 +3874,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3652,6 +3936,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3709,6 +3998,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3766,6 +4060,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3823,6 +4122,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3880,6 +4184,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3937,6 +4247,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3994,6 +4309,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4051,6 +4372,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4108,6 +4435,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4165,6 +4497,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4222,6 +4560,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4279,6 +4622,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4336,6 +4684,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4393,6 +4746,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4450,6 +4808,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4507,6 +4870,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4564,6 +4932,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4621,6 +4994,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4678,6 +5056,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4735,6 +5119,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4792,6 +5181,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4849,6 +5244,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4906,6 +5306,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4963,6 +5369,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5020,6 +5432,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5077,6 +5494,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5134,6 +5556,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5191,6 +5618,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5248,6 +5680,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5305,6 +5742,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5362,6 +5805,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5419,6 +5867,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5476,6 +5930,11 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5533,6 +5992,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5590,6 +6055,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5647,6 +6118,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5704,6 +6180,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5761,6 +6243,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5818,6 +6305,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5875,6 +6368,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5932,6 +6430,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5989,6 +6493,12 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6046,6 +6556,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6103,6 +6618,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6160,6 +6680,11 @@
           <t>Municipio equilibrado — perfil estándar</t>
         </is>
       </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6215,6 +6740,12 @@
       <c r="Q101" t="inlineStr">
         <is>
           <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
         </is>
       </c>
     </row>
@@ -30230,4 +30761,114 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Para qué sirve</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mapa_top100.html</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mapa interactivo — abrir en navegador, clicar en cada punto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>grafico_perfiles.png</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gráfico de barras con los 4 perfiles estratégicos — meter en slides</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>grafico_top20.png</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ranking visual del top 20 municipios — meter en slides</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>grafico_solvencia_mercado.png</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Scatter solvencia vs mercado — meter en slides</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>resultados_akademia.xlsx</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Excel con todas las pestañas de resultados</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>top100_con_clusters.csv</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Datos completos del top 100 con perfil asignado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dataset_maestro.csv</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dataset central con todas las variables calculadas</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/resultados_akademia.xlsx
+++ b/resultados_akademia.xlsx
@@ -10,6 +10,8 @@
     <sheet name="Top 100 ubicaciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Ranking municipios" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Resumen por provincia" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Perfiles estratégicos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Guía de archivos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:T101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,6 +518,21 @@
           <t>posicion_final</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>perfil</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>perfil_corto</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -571,6 +588,19 @@
       <c r="Q2" t="n">
         <v>1</v>
       </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Zona premium — máxima solvencia</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -618,13 +648,26 @@
         <v>40.41240833333333</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.888334666666666</v>
+        <v>-3.888334666666665</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Zona premium — máxima solvencia</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -681,6 +724,19 @@
       <c r="Q4" t="n">
         <v>3</v>
       </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Zona premium — máxima solvencia</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -701,7 +757,7 @@
         <v>0.4710962657811085</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4992752984995301</v>
+        <v>0.49927529849953</v>
       </c>
       <c r="G5" t="n">
         <v>5967</v>
@@ -735,6 +791,19 @@
       </c>
       <c r="Q5" t="n">
         <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Zona premium — máxima solvencia</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -756,7 +825,7 @@
         <v>0.4432404023831725</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4498010966345256</v>
+        <v>0.4498010966345255</v>
       </c>
       <c r="G6" t="n">
         <v>757</v>
@@ -790,6 +859,19 @@
       </c>
       <c r="Q6" t="n">
         <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Zona premium — máxima solvencia</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -808,10 +890,10 @@
         <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4068771970727668</v>
+        <v>0.4068771970727667</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4300106893861274</v>
+        <v>0.4300106893861273</v>
       </c>
       <c r="G7" t="n">
         <v>5434</v>
@@ -845,6 +927,20 @@
       </c>
       <c r="Q7" t="n">
         <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -901,6 +997,19 @@
       <c r="Q8" t="n">
         <v>7</v>
       </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -918,7 +1027,7 @@
         <v>144</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3170504917120007</v>
+        <v>0.3170504917120006</v>
       </c>
       <c r="F9" t="n">
         <v>0.3414396819797916</v>
@@ -927,7 +1036,7 @@
         <v>23273</v>
       </c>
       <c r="H9" t="n">
-        <v>13.06230010984515</v>
+        <v>13.06230010984514</v>
       </c>
       <c r="I9" t="n">
         <v>2.182128026570019</v>
@@ -955,6 +1064,19 @@
       </c>
       <c r="Q9" t="n">
         <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1003,13 +1125,27 @@
         <v>39.67150431707317</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2472086585365854</v>
+        <v>-0.2472086585365853</v>
       </c>
       <c r="P10" t="n">
         <v>192</v>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1066,6 +1202,20 @@
       <c r="Q11" t="n">
         <v>10</v>
       </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1121,6 +1271,20 @@
       <c r="Q12" t="n">
         <v>11</v>
       </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1138,7 +1302,7 @@
         <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3020496236136052</v>
+        <v>0.3020496236136051</v>
       </c>
       <c r="F13" t="n">
         <v>0.3424089031161846</v>
@@ -1168,13 +1332,27 @@
         <v>38.40051353846154</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4339552307692308</v>
+        <v>-0.4339552307692307</v>
       </c>
       <c r="P13" t="n">
         <v>232</v>
       </c>
       <c r="Q13" t="n">
         <v>12</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1196,7 +1374,7 @@
         <v>0.3015859678611488</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3325271833683439</v>
+        <v>0.3325271833683438</v>
       </c>
       <c r="G14" t="n">
         <v>45720</v>
@@ -1205,7 +1383,7 @@
         <v>13.70222885208217</v>
       </c>
       <c r="I14" t="n">
-        <v>2.187028161933439</v>
+        <v>2.18702816193344</v>
       </c>
       <c r="J14" t="n">
         <v>40724</v>
@@ -1230,6 +1408,19 @@
       </c>
       <c r="Q14" t="n">
         <v>13</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1286,6 +1477,19 @@
       <c r="Q15" t="n">
         <v>14</v>
       </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1306,7 +1510,7 @@
         <v>0.2951935003511251</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3078604466924986</v>
+        <v>0.3078604466924985</v>
       </c>
       <c r="G16" t="n">
         <v>2980</v>
@@ -1340,6 +1544,20 @@
       </c>
       <c r="Q16" t="n">
         <v>15</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1385,7 +1603,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>38.35649095918367</v>
+        <v>38.35649095918368</v>
       </c>
       <c r="O17" t="n">
         <v>-0.4861343714285714</v>
@@ -1395,6 +1613,19 @@
       </c>
       <c r="Q17" t="n">
         <v>16</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1413,10 +1644,10 @@
         <v>532</v>
       </c>
       <c r="E18" t="n">
-        <v>0.292574516389671</v>
+        <v>0.2925745163896709</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3394754208877948</v>
+        <v>0.3394754208877947</v>
       </c>
       <c r="G18" t="n">
         <v>66968</v>
@@ -1425,7 +1656,7 @@
         <v>10.59990746047573</v>
       </c>
       <c r="I18" t="n">
-        <v>2.146141140670535</v>
+        <v>2.146141140670536</v>
       </c>
       <c r="J18" t="n">
         <v>73233</v>
@@ -1450,6 +1681,19 @@
       </c>
       <c r="Q18" t="n">
         <v>17</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1471,7 +1715,7 @@
         <v>0.2903719867788724</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3852801044787885</v>
+        <v>0.3852801044787884</v>
       </c>
       <c r="G19" t="n">
         <v>23793</v>
@@ -1505,6 +1749,19 @@
       </c>
       <c r="Q19" t="n">
         <v>18</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1561,6 +1818,20 @@
       <c r="Q20" t="n">
         <v>19</v>
       </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1590,7 +1861,7 @@
         <v>12.08517876777488</v>
       </c>
       <c r="I21" t="n">
-        <v>2.193999061190571</v>
+        <v>2.19399906119057</v>
       </c>
       <c r="J21" t="n">
         <v>15372</v>
@@ -1615,6 +1886,19 @@
       </c>
       <c r="Q21" t="n">
         <v>20</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1671,6 +1955,19 @@
       <c r="Q22" t="n">
         <v>21</v>
       </c>
+      <c r="R22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1726,6 +2023,19 @@
       <c r="Q23" t="n">
         <v>22</v>
       </c>
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1773,13 +2083,27 @@
         <v>35.28889113636364</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.946369295454546</v>
+        <v>-2.946369295454545</v>
       </c>
       <c r="P24" t="n">
         <v>404</v>
       </c>
       <c r="Q24" t="n">
         <v>23</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1798,7 +2122,7 @@
         <v>179</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2793792296023777</v>
+        <v>0.2793792296023776</v>
       </c>
       <c r="F25" t="n">
         <v>0.3115778203873842</v>
@@ -1835,6 +2159,19 @@
       </c>
       <c r="Q25" t="n">
         <v>24</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1891,6 +2228,20 @@
       <c r="Q26" t="n">
         <v>25</v>
       </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1946,6 +2297,19 @@
       <c r="Q27" t="n">
         <v>26</v>
       </c>
+      <c r="R27" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2001,6 +2365,19 @@
       <c r="Q28" t="n">
         <v>27</v>
       </c>
+      <c r="R28" t="n">
+        <v>3</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2056,6 +2433,19 @@
       <c r="Q29" t="n">
         <v>28</v>
       </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2076,7 +2466,7 @@
         <v>0.2779316207501539</v>
       </c>
       <c r="F30" t="n">
-        <v>0.308395459516959</v>
+        <v>0.3083954595169589</v>
       </c>
       <c r="G30" t="n">
         <v>25182</v>
@@ -2110,6 +2500,19 @@
       </c>
       <c r="Q30" t="n">
         <v>29</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2131,7 +2534,7 @@
         <v>0.2779157972239722</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2940426135448309</v>
+        <v>0.2940426135448308</v>
       </c>
       <c r="G31" t="n">
         <v>2805</v>
@@ -2165,6 +2568,20 @@
       </c>
       <c r="Q31" t="n">
         <v>30</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2221,6 +2638,20 @@
       <c r="Q32" t="n">
         <v>31</v>
       </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2241,7 +2672,7 @@
         <v>0.2743419755076222</v>
       </c>
       <c r="F33" t="n">
-        <v>0.327642651569287</v>
+        <v>0.3276426515692869</v>
       </c>
       <c r="G33" t="n">
         <v>34198</v>
@@ -2275,6 +2706,19 @@
       </c>
       <c r="Q33" t="n">
         <v>32</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2331,6 +2775,20 @@
       <c r="Q34" t="n">
         <v>33</v>
       </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2348,7 +2806,7 @@
         <v>61</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2732458117957992</v>
+        <v>0.2732458117957991</v>
       </c>
       <c r="F35" t="n">
         <v>0.2949950326455233</v>
@@ -2385,6 +2843,20 @@
       </c>
       <c r="Q35" t="n">
         <v>34</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2441,6 +2913,19 @@
       <c r="Q36" t="n">
         <v>35</v>
       </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2496,6 +2981,20 @@
       <c r="Q37" t="n">
         <v>36</v>
       </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2516,7 +3015,7 @@
         <v>0.2711086808682969</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3106297849484551</v>
+        <v>0.310629784948455</v>
       </c>
       <c r="G38" t="n">
         <v>10296</v>
@@ -2550,6 +3049,19 @@
       </c>
       <c r="Q38" t="n">
         <v>37</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2606,6 +3118,20 @@
       <c r="Q39" t="n">
         <v>38</v>
       </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2623,7 +3149,7 @@
         <v>75</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2697507469230077</v>
+        <v>0.2697507469230076</v>
       </c>
       <c r="F40" t="n">
         <v>0.2937662965017688</v>
@@ -2660,6 +3186,19 @@
       </c>
       <c r="Q40" t="n">
         <v>39</v>
+      </c>
+      <c r="R40" t="n">
+        <v>3</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2678,10 +3217,10 @@
         <v>164</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2694057956761921</v>
+        <v>0.269405795676192</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2942936117384761</v>
+        <v>0.294293611738476</v>
       </c>
       <c r="G41" t="n">
         <v>20025</v>
@@ -2715,6 +3254,19 @@
       </c>
       <c r="Q41" t="n">
         <v>40</v>
+      </c>
+      <c r="R41" t="n">
+        <v>3</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -2736,7 +3288,7 @@
         <v>0.2683708490455727</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2889261173411353</v>
+        <v>0.2889261173411352</v>
       </c>
       <c r="G42" t="n">
         <v>2530</v>
@@ -2770,6 +3322,20 @@
       </c>
       <c r="Q42" t="n">
         <v>41</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2826,6 +3392,20 @@
       <c r="Q43" t="n">
         <v>42</v>
       </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2881,6 +3461,20 @@
       <c r="Q44" t="n">
         <v>43</v>
       </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2898,7 +3492,7 @@
         <v>166</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2676487736542129</v>
+        <v>0.2676487736542128</v>
       </c>
       <c r="F45" t="n">
         <v>0.3103149517109111</v>
@@ -2910,7 +3504,7 @@
         <v>11.65582751425326</v>
       </c>
       <c r="I45" t="n">
-        <v>1.740500258576811</v>
+        <v>1.740500258576812</v>
       </c>
       <c r="J45" t="n">
         <v>29207</v>
@@ -2928,13 +3522,26 @@
         <v>42.85095603614458</v>
       </c>
       <c r="O45" t="n">
-        <v>-2.677920487951807</v>
+        <v>-2.677920487951808</v>
       </c>
       <c r="P45" t="n">
         <v>480</v>
       </c>
       <c r="Q45" t="n">
         <v>44</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -2956,7 +3563,7 @@
         <v>0.267218218527344</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2791977230829014</v>
+        <v>0.2791977230829013</v>
       </c>
       <c r="G46" t="n">
         <v>1745</v>
@@ -2990,6 +3597,20 @@
       </c>
       <c r="Q46" t="n">
         <v>45</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -3008,10 +3629,10 @@
         <v>21</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2671068487828123</v>
+        <v>0.2671068487828122</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2864107414894768</v>
+        <v>0.2864107414894767</v>
       </c>
       <c r="G47" t="n">
         <v>3634</v>
@@ -3045,6 +3666,20 @@
       </c>
       <c r="Q47" t="n">
         <v>46</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3101,6 +3736,19 @@
       <c r="Q48" t="n">
         <v>47</v>
       </c>
+      <c r="R48" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3121,7 +3769,7 @@
         <v>0.2665283776815991</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2927397652522232</v>
+        <v>0.2927397652522231</v>
       </c>
       <c r="G49" t="n">
         <v>1676</v>
@@ -3130,7 +3778,7 @@
         <v>12.41265615146908</v>
       </c>
       <c r="I49" t="n">
-        <v>1.756206548892383</v>
+        <v>1.756206548892384</v>
       </c>
       <c r="J49" t="n">
         <v>1791</v>
@@ -3155,6 +3803,20 @@
       </c>
       <c r="Q49" t="n">
         <v>48</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3173,7 +3835,7 @@
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2660496889440158</v>
+        <v>0.2660496889440157</v>
       </c>
       <c r="F50" t="n">
         <v>0.2778515348217613</v>
@@ -3210,6 +3872,20 @@
       </c>
       <c r="Q50" t="n">
         <v>49</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3228,7 +3904,7 @@
         <v>186</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2658883647369945</v>
+        <v>0.2658883647369944</v>
       </c>
       <c r="F51" t="n">
         <v>0.3005120395760801</v>
@@ -3265,6 +3941,19 @@
       </c>
       <c r="Q51" t="n">
         <v>50</v>
+      </c>
+      <c r="R51" t="n">
+        <v>3</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -3321,6 +4010,19 @@
       <c r="Q52" t="n">
         <v>51</v>
       </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3376,6 +4078,20 @@
       <c r="Q53" t="n">
         <v>52</v>
       </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3393,10 +4109,10 @@
         <v>62</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2642453833336855</v>
+        <v>0.2642453833336854</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2945133054663712</v>
+        <v>0.2945133054663711</v>
       </c>
       <c r="G54" t="n">
         <v>8804</v>
@@ -3430,6 +4146,19 @@
       </c>
       <c r="Q54" t="n">
         <v>53</v>
+      </c>
+      <c r="R54" t="n">
+        <v>3</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -3486,6 +4215,20 @@
       <c r="Q55" t="n">
         <v>54</v>
       </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3541,6 +4284,20 @@
       <c r="Q56" t="n">
         <v>55</v>
       </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3596,6 +4353,20 @@
       <c r="Q57" t="n">
         <v>56</v>
       </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3651,6 +4422,19 @@
       <c r="Q58" t="n">
         <v>57</v>
       </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3706,6 +4490,20 @@
       <c r="Q59" t="n">
         <v>58</v>
       </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3761,6 +4559,19 @@
       <c r="Q60" t="n">
         <v>59</v>
       </c>
+      <c r="R60" t="n">
+        <v>3</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3790,7 +4601,7 @@
         <v>8.024810093925742</v>
       </c>
       <c r="I61" t="n">
-        <v>1.698042052441507</v>
+        <v>1.698042052441506</v>
       </c>
       <c r="J61" t="n">
         <v>11687</v>
@@ -3815,6 +4626,20 @@
       </c>
       <c r="Q61" t="n">
         <v>60</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -3836,7 +4661,7 @@
         <v>0.2594338939384877</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2806870560028688</v>
+        <v>0.2806870560028687</v>
       </c>
       <c r="G62" t="n">
         <v>4118</v>
@@ -3870,6 +4695,20 @@
       </c>
       <c r="Q62" t="n">
         <v>61</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -3926,6 +4765,19 @@
       <c r="Q63" t="n">
         <v>62</v>
       </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3981,6 +4833,20 @@
       <c r="Q64" t="n">
         <v>63</v>
       </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3998,10 +4864,10 @@
         <v>74</v>
       </c>
       <c r="E65" t="n">
-        <v>0.2531958964058652</v>
+        <v>0.2531958964058651</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2781220238591696</v>
+        <v>0.2781220238591695</v>
       </c>
       <c r="G65" t="n">
         <v>11665</v>
@@ -4035,6 +4901,19 @@
       </c>
       <c r="Q65" t="n">
         <v>64</v>
+      </c>
+      <c r="R65" t="n">
+        <v>3</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -4053,7 +4932,7 @@
         <v>81</v>
       </c>
       <c r="E66" t="n">
-        <v>0.2519216566113767</v>
+        <v>0.2519216566113766</v>
       </c>
       <c r="F66" t="n">
         <v>0.2751768598416108</v>
@@ -4090,6 +4969,20 @@
       </c>
       <c r="Q66" t="n">
         <v>65</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4146,6 +5039,19 @@
       <c r="Q67" t="n">
         <v>66</v>
       </c>
+      <c r="R67" t="n">
+        <v>3</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4163,7 +5069,7 @@
         <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2490578181632769</v>
+        <v>0.2490578181632768</v>
       </c>
       <c r="F68" t="n">
         <v>0.2610629061535713</v>
@@ -4200,6 +5106,20 @@
       </c>
       <c r="Q68" t="n">
         <v>67</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4218,7 +5138,7 @@
         <v>62</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2469358718357633</v>
+        <v>0.2469358718357632</v>
       </c>
       <c r="F69" t="n">
         <v>0.2696508491833992</v>
@@ -4255,6 +5175,19 @@
       </c>
       <c r="Q69" t="n">
         <v>68</v>
+      </c>
+      <c r="R69" t="n">
+        <v>3</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -4273,7 +5206,7 @@
         <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>0.2460954433154154</v>
+        <v>0.2460954433154153</v>
       </c>
       <c r="F70" t="n">
         <v>0.2530160559083151</v>
@@ -4310,6 +5243,19 @@
       </c>
       <c r="Q70" t="n">
         <v>69</v>
+      </c>
+      <c r="R70" t="n">
+        <v>3</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -4328,7 +5274,7 @@
         <v>9</v>
       </c>
       <c r="E71" t="n">
-        <v>0.2457610080753873</v>
+        <v>0.2457610080753872</v>
       </c>
       <c r="F71" t="n">
         <v>0.2692170950598729</v>
@@ -4365,6 +5311,19 @@
       </c>
       <c r="Q71" t="n">
         <v>70</v>
+      </c>
+      <c r="R71" t="n">
+        <v>3</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -4386,7 +5345,7 @@
         <v>0.2439063639467793</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2536900371886314</v>
+        <v>0.2536900371886313</v>
       </c>
       <c r="G72" t="n">
         <v>1525</v>
@@ -4420,6 +5379,20 @@
       </c>
       <c r="Q72" t="n">
         <v>71</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -4438,7 +5411,7 @@
         <v>62</v>
       </c>
       <c r="E73" t="n">
-        <v>0.2402350181414876</v>
+        <v>0.2402350181414875</v>
       </c>
       <c r="F73" t="n">
         <v>0.2700995782626665</v>
@@ -4447,7 +5420,7 @@
         <v>7089</v>
       </c>
       <c r="H73" t="n">
-        <v>9.193717876408225</v>
+        <v>9.193717876408224</v>
       </c>
       <c r="I73" t="n">
         <v>1.95751971269507</v>
@@ -4475,6 +5448,20 @@
       </c>
       <c r="Q73" t="n">
         <v>72</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -4502,7 +5489,7 @@
         <v>2195</v>
       </c>
       <c r="H74" t="n">
-        <v>10.96605137457069</v>
+        <v>10.9660513745707</v>
       </c>
       <c r="I74" t="n">
         <v>1.742380730782222</v>
@@ -4530,6 +5517,20 @@
       </c>
       <c r="Q74" t="n">
         <v>73</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -4548,7 +5549,7 @@
         <v>71</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2369742042200651</v>
+        <v>0.236974204220065</v>
       </c>
       <c r="F75" t="n">
         <v>0.2851689009175338</v>
@@ -4560,7 +5561,7 @@
         <v>10.61183082925706</v>
       </c>
       <c r="I75" t="n">
-        <v>1.891663382201203</v>
+        <v>1.891663382201204</v>
       </c>
       <c r="J75" t="n">
         <v>9551</v>
@@ -4585,6 +5586,20 @@
       </c>
       <c r="Q75" t="n">
         <v>74</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -4641,6 +5656,20 @@
       <c r="Q76" t="n">
         <v>75</v>
       </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4661,7 +5690,7 @@
         <v>0.236251118751374</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2409059178943452</v>
+        <v>0.2409059178943451</v>
       </c>
       <c r="G77" t="n">
         <v>1178</v>
@@ -4695,6 +5724,20 @@
       </c>
       <c r="Q77" t="n">
         <v>76</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -4713,16 +5756,16 @@
         <v>108</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2354255000886919</v>
+        <v>0.2354255000886918</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2680932299256181</v>
+        <v>0.268093229925618</v>
       </c>
       <c r="G78" t="n">
         <v>12311</v>
       </c>
       <c r="H78" t="n">
-        <v>9.107014779433383</v>
+        <v>9.107014779433385</v>
       </c>
       <c r="I78" t="n">
         <v>1.957443178092112</v>
@@ -4743,13 +5786,27 @@
         <v>38.87657487962964</v>
       </c>
       <c r="O78" t="n">
-        <v>-6.963507805555555</v>
+        <v>-6.963507805555556</v>
       </c>
       <c r="P78" t="n">
         <v>608</v>
       </c>
       <c r="Q78" t="n">
         <v>77</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -4768,7 +5825,7 @@
         <v>34</v>
       </c>
       <c r="E79" t="n">
-        <v>0.2343558795306929</v>
+        <v>0.2343558795306928</v>
       </c>
       <c r="F79" t="n">
         <v>0.2598752619403884</v>
@@ -4805,6 +5862,20 @@
       </c>
       <c r="Q79" t="n">
         <v>78</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -4861,6 +5932,19 @@
       <c r="Q80" t="n">
         <v>79</v>
       </c>
+      <c r="R80" t="n">
+        <v>3</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4887,7 +5971,7 @@
         <v>1549</v>
       </c>
       <c r="H81" t="n">
-        <v>3.683394567439636</v>
+        <v>3.683394567439637</v>
       </c>
       <c r="I81" t="n">
         <v>1.6986823196142</v>
@@ -4915,6 +5999,20 @@
       </c>
       <c r="Q81" t="n">
         <v>80</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -4971,6 +6069,20 @@
       <c r="Q82" t="n">
         <v>81</v>
       </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5026,6 +6138,20 @@
       <c r="Q83" t="n">
         <v>82</v>
       </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5081,6 +6207,20 @@
       <c r="Q84" t="n">
         <v>83</v>
       </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5098,16 +6238,16 @@
         <v>41</v>
       </c>
       <c r="E85" t="n">
-        <v>0.2265130189469047</v>
+        <v>0.2265130189469046</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2455867832465682</v>
+        <v>0.2455867832465681</v>
       </c>
       <c r="G85" t="n">
         <v>4546</v>
       </c>
       <c r="H85" t="n">
-        <v>9.702953459517799</v>
+        <v>9.702953459517801</v>
       </c>
       <c r="I85" t="n">
         <v>1.945314501210929</v>
@@ -5135,6 +6275,20 @@
       </c>
       <c r="Q85" t="n">
         <v>84</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -5153,10 +6307,10 @@
         <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2261139775717508</v>
+        <v>0.2261139775717507</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2307307993714182</v>
+        <v>0.2307307993714181</v>
       </c>
       <c r="G86" t="n">
         <v>616</v>
@@ -5190,6 +6344,20 @@
       </c>
       <c r="Q86" t="n">
         <v>85</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -5208,7 +6376,7 @@
         <v>54</v>
       </c>
       <c r="E87" t="n">
-        <v>0.2237114862150722</v>
+        <v>0.2237114862150721</v>
       </c>
       <c r="F87" t="n">
         <v>0.2487326769172505</v>
@@ -5245,6 +6413,19 @@
       </c>
       <c r="Q87" t="n">
         <v>86</v>
+      </c>
+      <c r="R87" t="n">
+        <v>3</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -5263,7 +6444,7 @@
         <v>106</v>
       </c>
       <c r="E88" t="n">
-        <v>0.2231065254634674</v>
+        <v>0.2231065254634673</v>
       </c>
       <c r="F88" t="n">
         <v>0.2475974916986188</v>
@@ -5300,6 +6481,19 @@
       </c>
       <c r="Q88" t="n">
         <v>87</v>
+      </c>
+      <c r="R88" t="n">
+        <v>3</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -5356,6 +6550,20 @@
       <c r="Q89" t="n">
         <v>88</v>
       </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5411,6 +6619,19 @@
       <c r="Q90" t="n">
         <v>89</v>
       </c>
+      <c r="R90" t="n">
+        <v>1</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gran ciudad</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5437,7 +6658,7 @@
         <v>20201</v>
       </c>
       <c r="H91" t="n">
-        <v>12.93121152996033</v>
+        <v>12.93121152996034</v>
       </c>
       <c r="I91" t="n">
         <v>2.068184471263653</v>
@@ -5465,6 +6686,19 @@
       </c>
       <c r="Q91" t="n">
         <v>90</v>
+      </c>
+      <c r="R91" t="n">
+        <v>3</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -5513,13 +6747,27 @@
         <v>41.05397163636363</v>
       </c>
       <c r="O92" t="n">
-        <v>-0.1372174545454546</v>
+        <v>-0.1372174545454545</v>
       </c>
       <c r="P92" t="n">
         <v>770</v>
       </c>
       <c r="Q92" t="n">
         <v>91</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -5576,6 +6824,20 @@
       <c r="Q93" t="n">
         <v>92</v>
       </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5631,6 +6893,20 @@
       <c r="Q94" t="n">
         <v>93</v>
       </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5686,6 +6962,20 @@
       <c r="Q95" t="n">
         <v>94</v>
       </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5703,10 +6993,10 @@
         <v>11</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2113690068368507</v>
+        <v>0.2113690068368506</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2252903060282671</v>
+        <v>0.225290306028267</v>
       </c>
       <c r="G96" t="n">
         <v>1554</v>
@@ -5733,13 +7023,27 @@
         <v>40.04939972727273</v>
       </c>
       <c r="O96" t="n">
-        <v>0.05386563636363637</v>
+        <v>0.0538656363636363</v>
       </c>
       <c r="P96" t="n">
         <v>845</v>
       </c>
       <c r="Q96" t="n">
         <v>95</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -5758,7 +7062,7 @@
         <v>121</v>
       </c>
       <c r="E97" t="n">
-        <v>0.2108250831995349</v>
+        <v>0.2108250831995348</v>
       </c>
       <c r="F97" t="n">
         <v>0.2436379186157203</v>
@@ -5795,6 +7099,19 @@
       </c>
       <c r="Q97" t="n">
         <v>96</v>
+      </c>
+      <c r="R97" t="n">
+        <v>3</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -5813,7 +7130,7 @@
         <v>36</v>
       </c>
       <c r="E98" t="n">
-        <v>0.2096047968588958</v>
+        <v>0.2096047968588957</v>
       </c>
       <c r="F98" t="n">
         <v>0.2448428587832888</v>
@@ -5850,6 +7167,20 @@
       </c>
       <c r="Q98" t="n">
         <v>97</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -5898,13 +7229,27 @@
         <v>38.98999095614035</v>
       </c>
       <c r="O99" t="n">
-        <v>-1.862771228070175</v>
+        <v>-1.862771228070176</v>
       </c>
       <c r="P99" t="n">
         <v>879</v>
       </c>
       <c r="Q99" t="n">
         <v>98</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Solvencia
+ajustada</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -5926,7 +7271,7 @@
         <v>0.2077701726035451</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2287241259315196</v>
+        <v>0.2287241259315195</v>
       </c>
       <c r="G100" t="n">
         <v>4573</v>
@@ -5960,6 +7305,19 @@
       </c>
       <c r="Q100" t="n">
         <v>99</v>
+      </c>
+      <c r="R100" t="n">
+        <v>3</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -5981,7 +7339,7 @@
         <v>0.2066810717600926</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2255429831798123</v>
+        <v>0.2255429831798122</v>
       </c>
       <c r="G101" t="n">
         <v>6418</v>
@@ -6015,6 +7373,19 @@
       </c>
       <c r="Q101" t="n">
         <v>100</v>
+      </c>
+      <c r="R101" t="n">
+        <v>3</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Estándar</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6211,7 +7582,7 @@
         <v>40.41240833333333</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.888334666666666</v>
+        <v>-3.888334666666665</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -6288,7 +7659,7 @@
         <v>0.4867620595131572</v>
       </c>
       <c r="F5" t="n">
-        <v>0.49692141613931</v>
+        <v>0.4969214161393099</v>
       </c>
       <c r="G5" t="n">
         <v>1446</v>
@@ -6340,7 +7711,7 @@
         <v>0.4710962657811085</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4992752984995301</v>
+        <v>0.49927529849953</v>
       </c>
       <c r="G6" t="n">
         <v>5967</v>
@@ -6392,7 +7763,7 @@
         <v>0.4432404023831725</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4498010966345256</v>
+        <v>0.4498010966345255</v>
       </c>
       <c r="G7" t="n">
         <v>757</v>
@@ -6493,16 +7864,16 @@
         <v>49</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4086989257071956</v>
+        <v>0.4086989257071955</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4470889819533945</v>
+        <v>0.4470889819533944</v>
       </c>
       <c r="G9" t="n">
         <v>5571</v>
       </c>
       <c r="H9" t="n">
-        <v>6.056076162310791</v>
+        <v>6.056076162310792</v>
       </c>
       <c r="I9" t="n">
         <v>1.749123352635103</v>
@@ -6545,10 +7916,10 @@
         <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4068771970727668</v>
+        <v>0.4068771970727667</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4300106893861274</v>
+        <v>0.4300106893861273</v>
       </c>
       <c r="G10" t="n">
         <v>5434</v>
@@ -6597,10 +7968,10 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4053203527289863</v>
+        <v>0.4053203527289862</v>
       </c>
       <c r="F11" t="n">
-        <v>0.410786721190727</v>
+        <v>0.4107867211907269</v>
       </c>
       <c r="G11" t="n">
         <v>584</v>
@@ -6649,10 +8020,10 @@
         <v>1068</v>
       </c>
       <c r="E12" t="n">
-        <v>0.401498965065583</v>
+        <v>0.4014989650655829</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4691542693260115</v>
+        <v>0.4691542693260114</v>
       </c>
       <c r="G12" t="n">
         <v>186908</v>
@@ -6860,7 +8231,7 @@
         <v>0.3941226268878416</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4021365394814556</v>
+        <v>0.4021365394814555</v>
       </c>
       <c r="G16" t="n">
         <v>945</v>
@@ -7068,13 +8439,13 @@
         <v>0.3863138269178498</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4112600700301837</v>
+        <v>0.4112600700301836</v>
       </c>
       <c r="G20" t="n">
         <v>1737</v>
       </c>
       <c r="H20" t="n">
-        <v>9.035307829716203</v>
+        <v>9.035307829716205</v>
       </c>
       <c r="I20" t="n">
         <v>1.435204762679754</v>
@@ -7328,7 +8699,7 @@
         <v>0.3802304785351845</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3845362052887935</v>
+        <v>0.3845362052887934</v>
       </c>
       <c r="G25" t="n">
         <v>189</v>
@@ -7377,7 +8748,7 @@
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3789363084635659</v>
+        <v>0.3789363084635658</v>
       </c>
       <c r="F26" t="n">
         <v>0.3847681441172223</v>
@@ -7481,7 +8852,7 @@
         <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3778055629095217</v>
+        <v>0.3778055629095216</v>
       </c>
       <c r="F28" t="n">
         <v>0.4263013193234038</v>
@@ -7689,10 +9060,10 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3755072893225526</v>
+        <v>0.3755072893225525</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3755072893225526</v>
+        <v>0.3755072893225525</v>
       </c>
       <c r="G32" t="n">
         <v>28</v>
@@ -7796,7 +9167,7 @@
         <v>0.3744210777512569</v>
       </c>
       <c r="F34" t="n">
-        <v>0.39051561980705</v>
+        <v>0.3905156198070499</v>
       </c>
       <c r="G34" t="n">
         <v>5846</v>
@@ -7961,7 +9332,7 @@
         <v>10.7536513216607</v>
       </c>
       <c r="I37" t="n">
-        <v>1.662399414212095</v>
+        <v>1.662399414212096</v>
       </c>
       <c r="J37" t="n">
         <v>19881</v>
@@ -8053,7 +9424,7 @@
         <v>50</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3726222532493442</v>
+        <v>0.3726222532493441</v>
       </c>
       <c r="F39" t="n">
         <v>0.3971098558493839</v>
@@ -8108,7 +9479,7 @@
         <v>0.3725854381252511</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3861017794790249</v>
+        <v>0.3861017794790248</v>
       </c>
       <c r="G40" t="n">
         <v>609</v>
@@ -8273,7 +9644,7 @@
         <v>10.46124360510631</v>
       </c>
       <c r="I43" t="n">
-        <v>1.831254807970087</v>
+        <v>1.831254807970086</v>
       </c>
       <c r="J43" t="n">
         <v>7910</v>
@@ -8313,7 +9684,7 @@
         <v>25</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3688767999304705</v>
+        <v>0.3688767999304704</v>
       </c>
       <c r="F44" t="n">
         <v>0.3985459396348998</v>
@@ -8368,7 +9739,7 @@
         <v>0.3686241903370875</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4095360414630089</v>
+        <v>0.4095360414630088</v>
       </c>
       <c r="G45" t="n">
         <v>19697</v>
@@ -8524,7 +9895,7 @@
         <v>0.3675421361933909</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3783324886072617</v>
+        <v>0.3783324886072616</v>
       </c>
       <c r="G48" t="n">
         <v>3547</v>
@@ -8576,7 +9947,7 @@
         <v>0.3675286005892998</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3913350148843566</v>
+        <v>0.3913350148843565</v>
       </c>
       <c r="G49" t="n">
         <v>3431</v>
@@ -8729,7 +10100,7 @@
         <v>137</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3672311801013181</v>
+        <v>0.367231180101318</v>
       </c>
       <c r="F52" t="n">
         <v>0.3905275516797807</v>
@@ -8781,7 +10152,7 @@
         <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3663356949889223</v>
+        <v>0.3663356949889222</v>
       </c>
       <c r="F53" t="n">
         <v>0.3696223762747567</v>
@@ -8940,7 +10311,7 @@
         <v>0.3631944759612847</v>
       </c>
       <c r="F56" t="n">
-        <v>0.389315833971747</v>
+        <v>0.3893158339717469</v>
       </c>
       <c r="G56" t="n">
         <v>19899</v>
@@ -9148,7 +10519,7 @@
         <v>0.3616028761387864</v>
       </c>
       <c r="F60" t="n">
-        <v>0.400838788979459</v>
+        <v>0.4008387889794589</v>
       </c>
       <c r="G60" t="n">
         <v>11063</v>
@@ -9197,7 +10568,7 @@
         <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3614332135262697</v>
+        <v>0.3614332135262696</v>
       </c>
       <c r="F61" t="n">
         <v>0.3768652117849108</v>
@@ -9356,7 +10727,7 @@
         <v>0.3588465022656704</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3848568061913885</v>
+        <v>0.3848568061913884</v>
       </c>
       <c r="G64" t="n">
         <v>2915</v>
@@ -9457,10 +10828,10 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3575489017906269</v>
+        <v>0.3575489017906268</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3575489017906269</v>
+        <v>0.3575489017906268</v>
       </c>
       <c r="G66" t="n">
         <v>56</v>
@@ -9591,7 +10962,7 @@
         <v>40.68065216666667</v>
       </c>
       <c r="O68" t="n">
-        <v>-3.622887166666667</v>
+        <v>-3.622887166666666</v>
       </c>
       <c r="P68" t="n">
         <v>67</v>
@@ -9613,10 +10984,10 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3546010877501926</v>
+        <v>0.3546010877501925</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3546010877501926</v>
+        <v>0.3546010877501925</v>
       </c>
       <c r="G69" t="n">
         <v>11</v>
@@ -9717,10 +11088,10 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3536689480891542</v>
+        <v>0.3536689480891541</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3536689480891542</v>
+        <v>0.3536689480891541</v>
       </c>
       <c r="G71" t="n">
         <v>145</v>
@@ -10081,10 +11452,10 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0.3493196167888241</v>
+        <v>0.349319616788824</v>
       </c>
       <c r="F78" t="n">
-        <v>0.3493196167888241</v>
+        <v>0.349319616788824</v>
       </c>
       <c r="G78" t="n">
         <v>64</v>
@@ -10133,7 +11504,7 @@
         <v>11</v>
       </c>
       <c r="E79" t="n">
-        <v>0.3483150878372812</v>
+        <v>0.3483150878372811</v>
       </c>
       <c r="F79" t="n">
         <v>0.3649002396986485</v>
@@ -10913,10 +12284,10 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3376984075841855</v>
+        <v>0.3376984075841854</v>
       </c>
       <c r="F94" t="n">
-        <v>0.3376984075841855</v>
+        <v>0.3376984075841854</v>
       </c>
       <c r="G94" t="n">
         <v>148</v>
@@ -10968,7 +12339,7 @@
         <v>0.3376499331680249</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3495176367790904</v>
+        <v>0.3495176367790903</v>
       </c>
       <c r="G95" t="n">
         <v>864</v>
@@ -11020,7 +12391,7 @@
         <v>0.3364881867936597</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3662772494496274</v>
+        <v>0.3662772494496273</v>
       </c>
       <c r="G96" t="n">
         <v>5554</v>
@@ -11029,7 +12400,7 @@
         <v>4.491093050992502</v>
       </c>
       <c r="I96" t="n">
-        <v>1.762816364595053</v>
+        <v>1.762816364595052</v>
       </c>
       <c r="J96" t="n">
         <v>11419</v>
@@ -11072,13 +12443,13 @@
         <v>0.3340247320393086</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3445166640741513</v>
+        <v>0.3445166640741512</v>
       </c>
       <c r="G97" t="n">
         <v>2049</v>
       </c>
       <c r="H97" t="n">
-        <v>9.830101557888101</v>
+        <v>9.830101557888099</v>
       </c>
       <c r="I97" t="n">
         <v>1.672165547340094</v>
@@ -11121,10 +12492,10 @@
         <v>37</v>
       </c>
       <c r="E98" t="n">
-        <v>0.332736857154214</v>
+        <v>0.3327368571542139</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3479096819484123</v>
+        <v>0.3479096819484122</v>
       </c>
       <c r="G98" t="n">
         <v>4782</v>
@@ -11173,7 +12544,7 @@
         <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>0.3310918196934469</v>
+        <v>0.3310918196934468</v>
       </c>
       <c r="F99" t="n">
         <v>0.3349759255503766</v>
@@ -11329,7 +12700,7 @@
         <v>5</v>
       </c>
       <c r="E102" t="n">
-        <v>0.3299524751087358</v>
+        <v>0.3299524751087357</v>
       </c>
       <c r="F102" t="n">
         <v>0.3468988428215399</v>
@@ -11485,7 +12856,7 @@
         <v>4</v>
       </c>
       <c r="E105" t="n">
-        <v>0.3277797059819813</v>
+        <v>0.3277797059819812</v>
       </c>
       <c r="F105" t="n">
         <v>0.3293011764783866</v>
@@ -11797,7 +13168,7 @@
         <v>2</v>
       </c>
       <c r="E111" t="n">
-        <v>0.3253011183404511</v>
+        <v>0.325301118340451</v>
       </c>
       <c r="F111" t="n">
         <v>0.3256734028582429</v>
@@ -11824,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>41.64672299999999</v>
+        <v>41.646723</v>
       </c>
       <c r="O111" t="n">
         <v>2.2246395</v>
@@ -12005,7 +13376,7 @@
         <v>5</v>
       </c>
       <c r="E115" t="n">
-        <v>0.3233477543861433</v>
+        <v>0.3233477543861432</v>
       </c>
       <c r="F115" t="n">
         <v>0.329675831205399</v>
@@ -12060,7 +13431,7 @@
         <v>0.3231208336477707</v>
       </c>
       <c r="F116" t="n">
-        <v>0.3418037454656909</v>
+        <v>0.3418037454656908</v>
       </c>
       <c r="G116" t="n">
         <v>2659</v>
@@ -12372,7 +13743,7 @@
         <v>0.321849777773098</v>
       </c>
       <c r="F122" t="n">
-        <v>0.3300926887700593</v>
+        <v>0.3300926887700592</v>
       </c>
       <c r="G122" t="n">
         <v>1061</v>
@@ -12528,7 +13899,7 @@
         <v>0.3212573901654088</v>
       </c>
       <c r="F125" t="n">
-        <v>0.3300404395254081</v>
+        <v>0.330040439525408</v>
       </c>
       <c r="G125" t="n">
         <v>360</v>
@@ -12589,7 +13960,7 @@
         <v>6.602240457057126</v>
       </c>
       <c r="I126" t="n">
-        <v>1.787901702412742</v>
+        <v>1.787901702412741</v>
       </c>
       <c r="J126" t="n">
         <v>4009</v>
@@ -12837,10 +14208,10 @@
         <v>8</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3199155144915902</v>
+        <v>0.3199155144915901</v>
       </c>
       <c r="F131" t="n">
-        <v>0.3409921410794423</v>
+        <v>0.3409921410794422</v>
       </c>
       <c r="G131" t="n">
         <v>1059</v>
@@ -12889,7 +14260,7 @@
         <v>4</v>
       </c>
       <c r="E132" t="n">
-        <v>0.3190806767152756</v>
+        <v>0.3190806767152755</v>
       </c>
       <c r="F132" t="n">
         <v>0.3262425248479662</v>
@@ -13048,7 +14419,7 @@
         <v>0.3184589257421322</v>
       </c>
       <c r="F135" t="n">
-        <v>0.3266067559199055</v>
+        <v>0.3266067559199054</v>
       </c>
       <c r="G135" t="n">
         <v>794</v>
@@ -13201,7 +14572,7 @@
         <v>4</v>
       </c>
       <c r="E138" t="n">
-        <v>0.3179933298139979</v>
+        <v>0.3179933298139978</v>
       </c>
       <c r="F138" t="n">
         <v>0.3258657974543523</v>
@@ -13461,7 +14832,7 @@
         <v>144</v>
       </c>
       <c r="E143" t="n">
-        <v>0.3170504917120007</v>
+        <v>0.3170504917120006</v>
       </c>
       <c r="F143" t="n">
         <v>0.3414396819797916</v>
@@ -13470,7 +14841,7 @@
         <v>23273</v>
       </c>
       <c r="H143" t="n">
-        <v>13.06230010984515</v>
+        <v>13.06230010984514</v>
       </c>
       <c r="I143" t="n">
         <v>2.182128026570019</v>
@@ -13669,10 +15040,10 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3158925388378742</v>
+        <v>0.3158925388378741</v>
       </c>
       <c r="F147" t="n">
-        <v>0.3158925388378742</v>
+        <v>0.3158925388378741</v>
       </c>
       <c r="G147" t="n">
         <v>29</v>
@@ -13733,7 +15104,7 @@
         <v>9.80337986995522</v>
       </c>
       <c r="I148" t="n">
-        <v>1.655468035167283</v>
+        <v>1.655468035167284</v>
       </c>
       <c r="J148" t="n">
         <v>699</v>
@@ -13929,7 +15300,7 @@
         <v>4</v>
       </c>
       <c r="E152" t="n">
-        <v>0.314980121038947</v>
+        <v>0.3149801210389469</v>
       </c>
       <c r="F152" t="n">
         <v>0.3151902967306422</v>
@@ -14033,10 +15404,10 @@
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>0.3147864508913397</v>
+        <v>0.3147864508913396</v>
       </c>
       <c r="F154" t="n">
-        <v>0.3147864508913397</v>
+        <v>0.3147864508913396</v>
       </c>
       <c r="G154" t="n">
         <v>293</v>
@@ -14085,7 +15456,7 @@
         <v>10</v>
       </c>
       <c r="E155" t="n">
-        <v>0.3147858854043287</v>
+        <v>0.3147858854043286</v>
       </c>
       <c r="F155" t="n">
         <v>0.3265598551047191</v>
@@ -14097,7 +15468,7 @@
         <v>8.025755109182287</v>
       </c>
       <c r="I155" t="n">
-        <v>1.834735224426882</v>
+        <v>1.834735224426881</v>
       </c>
       <c r="J155" t="n">
         <v>1640</v>
@@ -14241,16 +15612,16 @@
         <v>2</v>
       </c>
       <c r="E158" t="n">
-        <v>0.3143026413571646</v>
+        <v>0.3143026413571645</v>
       </c>
       <c r="F158" t="n">
-        <v>0.3144266781269273</v>
+        <v>0.3144266781269272</v>
       </c>
       <c r="G158" t="n">
         <v>439</v>
       </c>
       <c r="H158" t="n">
-        <v>9.685651153807747</v>
+        <v>9.685651153807749</v>
       </c>
       <c r="I158" t="n">
         <v>1.844155844155844</v>
@@ -14293,7 +15664,7 @@
         <v>8</v>
       </c>
       <c r="E159" t="n">
-        <v>0.3142327266844369</v>
+        <v>0.3142327266844368</v>
       </c>
       <c r="F159" t="n">
         <v>0.3222712100282858</v>
@@ -14400,7 +15771,7 @@
         <v>0.3138627977557403</v>
       </c>
       <c r="F161" t="n">
-        <v>0.3301154830298924</v>
+        <v>0.3301154830298923</v>
       </c>
       <c r="G161" t="n">
         <v>4252</v>
@@ -14501,10 +15872,10 @@
         <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>0.3127524134188349</v>
+        <v>0.3127524134188348</v>
       </c>
       <c r="F163" t="n">
-        <v>0.3127524134188349</v>
+        <v>0.3127524134188348</v>
       </c>
       <c r="G163" t="n">
         <v>67</v>
@@ -14605,10 +15976,10 @@
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>0.3125775015351022</v>
+        <v>0.3125775015351021</v>
       </c>
       <c r="F165" t="n">
-        <v>0.3125775015351022</v>
+        <v>0.3125775015351021</v>
       </c>
       <c r="G165" t="n">
         <v>74</v>
@@ -14709,7 +16080,7 @@
         <v>5</v>
       </c>
       <c r="E167" t="n">
-        <v>0.3124312239299558</v>
+        <v>0.3124312239299557</v>
       </c>
       <c r="F167" t="n">
         <v>0.3200643871399932</v>
@@ -14917,7 +16288,7 @@
         <v>9</v>
       </c>
       <c r="E171" t="n">
-        <v>0.3115191164819183</v>
+        <v>0.3115191164819182</v>
       </c>
       <c r="F171" t="n">
         <v>0.3230307086112208</v>
@@ -14981,7 +16352,7 @@
         <v>13.05752970235189</v>
       </c>
       <c r="I172" t="n">
-        <v>1.703760406389883</v>
+        <v>1.703760406389884</v>
       </c>
       <c r="J172" t="n">
         <v>642</v>
@@ -15024,13 +16395,13 @@
         <v>0.3113486862202973</v>
       </c>
       <c r="F173" t="n">
-        <v>0.3128284899086998</v>
+        <v>0.3128284899086997</v>
       </c>
       <c r="G173" t="n">
         <v>332</v>
       </c>
       <c r="H173" t="n">
-        <v>9.317843498537417</v>
+        <v>9.317843498537416</v>
       </c>
       <c r="I173" t="n">
         <v>1.487108013937282</v>
@@ -15073,7 +16444,7 @@
         <v>10</v>
       </c>
       <c r="E174" t="n">
-        <v>0.311341004029404</v>
+        <v>0.3113410040294039</v>
       </c>
       <c r="F174" t="n">
         <v>0.3253630857885889</v>
@@ -15128,7 +16499,7 @@
         <v>0.3111352224903344</v>
       </c>
       <c r="F175" t="n">
-        <v>0.316827732809899</v>
+        <v>0.3168277328098989</v>
       </c>
       <c r="G175" t="n">
         <v>740</v>
@@ -15229,10 +16600,10 @@
         <v>14</v>
       </c>
       <c r="E177" t="n">
-        <v>0.3108887317261487</v>
+        <v>0.3108887317261486</v>
       </c>
       <c r="F177" t="n">
-        <v>0.3331337955509343</v>
+        <v>0.3331337955509342</v>
       </c>
       <c r="G177" t="n">
         <v>1880</v>
@@ -15385,7 +16756,7 @@
         <v>8</v>
       </c>
       <c r="E180" t="n">
-        <v>0.310269965595443</v>
+        <v>0.3102699655954429</v>
       </c>
       <c r="F180" t="n">
         <v>0.326517336397332</v>
@@ -15449,7 +16820,7 @@
         <v>7.098020391957707</v>
       </c>
       <c r="I181" t="n">
-        <v>1.584300132050557</v>
+        <v>1.584300132050556</v>
       </c>
       <c r="J181" t="n">
         <v>557</v>
@@ -15593,10 +16964,10 @@
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>0.3094031871891482</v>
+        <v>0.3094031871891481</v>
       </c>
       <c r="F184" t="n">
-        <v>0.3094031871891482</v>
+        <v>0.3094031871891481</v>
       </c>
       <c r="G184" t="n">
         <v>18</v>
@@ -15654,7 +17025,7 @@
         <v>453</v>
       </c>
       <c r="H185" t="n">
-        <v>7.42014488582875</v>
+        <v>7.420144885828749</v>
       </c>
       <c r="I185" t="n">
         <v>1.744852941176471</v>
@@ -15697,7 +17068,7 @@
         <v>4</v>
       </c>
       <c r="E186" t="n">
-        <v>0.3084172705685893</v>
+        <v>0.3084172705685892</v>
       </c>
       <c r="F186" t="n">
         <v>0.3105994168096773</v>
@@ -16009,7 +17380,7 @@
         <v>5</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3074962096071652</v>
+        <v>0.3074962096071651</v>
       </c>
       <c r="F192" t="n">
         <v>0.3118389468512351</v>
@@ -16091,7 +17462,7 @@
         <v>39.67150431707317</v>
       </c>
       <c r="O193" t="n">
-        <v>-0.2472086585365854</v>
+        <v>-0.2472086585365853</v>
       </c>
       <c r="P193" t="n">
         <v>192</v>
@@ -16113,10 +17484,10 @@
         <v>1</v>
       </c>
       <c r="E194" t="n">
-        <v>0.307328664681069</v>
+        <v>0.3073286646810689</v>
       </c>
       <c r="F194" t="n">
-        <v>0.307328664681069</v>
+        <v>0.3073286646810689</v>
       </c>
       <c r="G194" t="n">
         <v>186</v>
@@ -16382,7 +17753,7 @@
         <v>1222</v>
       </c>
       <c r="H199" t="n">
-        <v>7.865038304036037</v>
+        <v>7.865038304036035</v>
       </c>
       <c r="I199" t="n">
         <v>1.461013641648754</v>
@@ -16529,10 +17900,10 @@
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3059413261753938</v>
+        <v>0.3059413261753937</v>
       </c>
       <c r="F202" t="n">
-        <v>0.3059413261753938</v>
+        <v>0.3059413261753937</v>
       </c>
       <c r="G202" t="n">
         <v>67</v>
@@ -16590,7 +17961,7 @@
         <v>285</v>
       </c>
       <c r="H203" t="n">
-        <v>9.127212594191393</v>
+        <v>9.127212594191391</v>
       </c>
       <c r="I203" t="n">
         <v>1.588806660499537</v>
@@ -16841,7 +18212,7 @@
         <v>16</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3055225565063786</v>
+        <v>0.3055225565063785</v>
       </c>
       <c r="F208" t="n">
         <v>0.3150184960643478</v>
@@ -16893,10 +18264,10 @@
         <v>9</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3053546960393249</v>
+        <v>0.3053546960393248</v>
       </c>
       <c r="F209" t="n">
-        <v>0.3171513364163551</v>
+        <v>0.317151336416355</v>
       </c>
       <c r="G209" t="n">
         <v>1800</v>
@@ -16954,7 +18325,7 @@
         <v>1372</v>
       </c>
       <c r="H210" t="n">
-        <v>9.689084092686647</v>
+        <v>9.689084092686649</v>
       </c>
       <c r="I210" t="n">
         <v>1.876049117562184</v>
@@ -17052,7 +18423,7 @@
         <v>0.3051023166073145</v>
       </c>
       <c r="F212" t="n">
-        <v>0.310054112026926</v>
+        <v>0.3100541120269259</v>
       </c>
       <c r="G212" t="n">
         <v>847</v>
@@ -17361,7 +18732,7 @@
         <v>2</v>
       </c>
       <c r="E218" t="n">
-        <v>0.3042287716929573</v>
+        <v>0.3042287716929572</v>
       </c>
       <c r="F218" t="n">
         <v>0.3081216125806609</v>
@@ -17477,7 +18848,7 @@
         <v>14.05672251361634</v>
       </c>
       <c r="I220" t="n">
-        <v>1.826211405553511</v>
+        <v>1.82621140555351</v>
       </c>
       <c r="J220" t="n">
         <v>842</v>
@@ -17838,7 +19209,7 @@
         <v>265</v>
       </c>
       <c r="H227" t="n">
-        <v>10.93152762946477</v>
+        <v>10.93152762946478</v>
       </c>
       <c r="I227" t="n">
         <v>1.946949602122016</v>
@@ -17933,7 +19304,7 @@
         <v>2</v>
       </c>
       <c r="E229" t="n">
-        <v>0.3028753776721234</v>
+        <v>0.3028753776721233</v>
       </c>
       <c r="F229" t="n">
         <v>0.3083094336242654</v>
@@ -17960,7 +19331,7 @@
         <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>41.50019349999999</v>
+        <v>41.5001935</v>
       </c>
       <c r="O229" t="n">
         <v>1.8107835</v>
@@ -18141,7 +19512,7 @@
         <v>13</v>
       </c>
       <c r="E233" t="n">
-        <v>0.3020496236136052</v>
+        <v>0.3020496236136051</v>
       </c>
       <c r="F233" t="n">
         <v>0.3424089031161846</v>
@@ -18171,7 +19542,7 @@
         <v>38.40051353846154</v>
       </c>
       <c r="O233" t="n">
-        <v>-0.4339552307692308</v>
+        <v>-0.4339552307692307</v>
       </c>
       <c r="P233" t="n">
         <v>232</v>
@@ -18352,7 +19723,7 @@
         <v>0.3015859678611488</v>
       </c>
       <c r="F237" t="n">
-        <v>0.3325271833683439</v>
+        <v>0.3325271833683438</v>
       </c>
       <c r="G237" t="n">
         <v>45720</v>
@@ -18361,7 +19732,7 @@
         <v>13.70222885208217</v>
       </c>
       <c r="I237" t="n">
-        <v>2.187028161933439</v>
+        <v>2.18702816193344</v>
       </c>
       <c r="J237" t="n">
         <v>40724</v>
@@ -18404,7 +19775,7 @@
         <v>0.3014766765390694</v>
       </c>
       <c r="F238" t="n">
-        <v>0.3048129892783427</v>
+        <v>0.3048129892783426</v>
       </c>
       <c r="G238" t="n">
         <v>768</v>
@@ -18514,7 +19885,7 @@
         <v>597</v>
       </c>
       <c r="H240" t="n">
-        <v>9.275179886400501</v>
+        <v>9.275179886400499</v>
       </c>
       <c r="I240" t="n">
         <v>2.012082228116711</v>
@@ -18560,7 +19931,7 @@
         <v>0.3010972378526791</v>
       </c>
       <c r="F241" t="n">
-        <v>0.3075026150379399</v>
+        <v>0.3075026150379398</v>
       </c>
       <c r="G241" t="n">
         <v>338</v>
@@ -18569,7 +19940,7 @@
         <v>6.155503853201426</v>
       </c>
       <c r="I241" t="n">
-        <v>1.777033492822967</v>
+        <v>1.777033492822966</v>
       </c>
       <c r="J241" t="n">
         <v>503</v>
@@ -18664,7 +20035,7 @@
         <v>0.3010109738600424</v>
       </c>
       <c r="F243" t="n">
-        <v>0.3053968809971415</v>
+        <v>0.3053968809971414</v>
       </c>
       <c r="G243" t="n">
         <v>306</v>
@@ -18673,7 +20044,7 @@
         <v>10.1736516433682</v>
       </c>
       <c r="I243" t="n">
-        <v>1.558938746438747</v>
+        <v>1.558938746438746</v>
       </c>
       <c r="J243" t="n">
         <v>341</v>
@@ -18765,7 +20136,7 @@
         <v>5</v>
       </c>
       <c r="E245" t="n">
-        <v>0.3008335829395897</v>
+        <v>0.3008335829395896</v>
       </c>
       <c r="F245" t="n">
         <v>0.3109777437168491</v>
@@ -18817,10 +20188,10 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>0.3005956271804439</v>
+        <v>0.3005956271804438</v>
       </c>
       <c r="F246" t="n">
-        <v>0.3005956271804439</v>
+        <v>0.3005956271804438</v>
       </c>
       <c r="G246" t="n">
         <v>34</v>
@@ -18924,7 +20295,7 @@
         <v>0.3004339173566021</v>
       </c>
       <c r="F248" t="n">
-        <v>0.3034816388862072</v>
+        <v>0.3034816388862071</v>
       </c>
       <c r="G248" t="n">
         <v>1046</v>
@@ -19245,7 +20616,7 @@
         <v>13.96103243382594</v>
       </c>
       <c r="I254" t="n">
-        <v>1.898077010938699</v>
+        <v>1.898077010938698</v>
       </c>
       <c r="J254" t="n">
         <v>645</v>
@@ -19285,10 +20656,10 @@
         <v>1</v>
       </c>
       <c r="E255" t="n">
-        <v>0.299989568699818</v>
+        <v>0.2999895686998179</v>
       </c>
       <c r="F255" t="n">
-        <v>0.299989568699818</v>
+        <v>0.2999895686998179</v>
       </c>
       <c r="G255" t="n">
         <v>38</v>
@@ -19337,10 +20708,10 @@
         <v>1</v>
       </c>
       <c r="E256" t="n">
-        <v>0.2999745756237375</v>
+        <v>0.2999745756237374</v>
       </c>
       <c r="F256" t="n">
-        <v>0.2999745756237375</v>
+        <v>0.2999745756237374</v>
       </c>
       <c r="G256" t="n">
         <v>198</v>
@@ -19389,10 +20760,10 @@
         <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>0.2999593631501413</v>
+        <v>0.2999593631501412</v>
       </c>
       <c r="F257" t="n">
-        <v>0.2999593631501413</v>
+        <v>0.2999593631501412</v>
       </c>
       <c r="G257" t="n">
         <v>86</v>
@@ -19453,7 +20824,7 @@
         <v>10.00600764545793</v>
       </c>
       <c r="I258" t="n">
-        <v>1.890317567736923</v>
+        <v>1.890317567736922</v>
       </c>
       <c r="J258" t="n">
         <v>334</v>
@@ -19753,10 +21124,10 @@
         <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0.299425252604935</v>
+        <v>0.2994252526049349</v>
       </c>
       <c r="F264" t="n">
-        <v>0.299425252604935</v>
+        <v>0.2994252526049349</v>
       </c>
       <c r="G264" t="n">
         <v>104</v>
@@ -19805,7 +21176,7 @@
         <v>4</v>
       </c>
       <c r="E265" t="n">
-        <v>0.2994201415730972</v>
+        <v>0.2994201415730971</v>
       </c>
       <c r="F265" t="n">
         <v>0.3047975616689427</v>
@@ -19866,7 +21237,7 @@
         <v>2506</v>
       </c>
       <c r="H266" t="n">
-        <v>7.910923727941269</v>
+        <v>7.910923727941268</v>
       </c>
       <c r="I266" t="n">
         <v>1.738632581223976</v>
@@ -19961,10 +21332,10 @@
         <v>2</v>
       </c>
       <c r="E268" t="n">
-        <v>0.298873623930186</v>
+        <v>0.2988736239301859</v>
       </c>
       <c r="F268" t="n">
-        <v>0.300921030786</v>
+        <v>0.3009210307859999</v>
       </c>
       <c r="G268" t="n">
         <v>229</v>
@@ -20221,10 +21592,10 @@
         <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>0.2985372120749165</v>
+        <v>0.2985372120749164</v>
       </c>
       <c r="F273" t="n">
-        <v>0.2985372120749165</v>
+        <v>0.2985372120749164</v>
       </c>
       <c r="G273" t="n">
         <v>123</v>
@@ -20303,7 +21674,7 @@
         <v>39.53594933333333</v>
       </c>
       <c r="O274" t="n">
-        <v>-0.4131933333333334</v>
+        <v>-0.4131933333333333</v>
       </c>
       <c r="P274" t="n">
         <v>273</v>
@@ -20377,7 +21748,7 @@
         <v>40</v>
       </c>
       <c r="E276" t="n">
-        <v>0.2982863808715343</v>
+        <v>0.2982863808715342</v>
       </c>
       <c r="F276" t="n">
         <v>0.3176604317453909</v>
@@ -20389,7 +21760,7 @@
         <v>8.953676983482755</v>
       </c>
       <c r="I276" t="n">
-        <v>1.814177735640599</v>
+        <v>1.8141777356406</v>
       </c>
       <c r="J276" t="n">
         <v>7299</v>
@@ -20481,7 +21852,7 @@
         <v>3</v>
       </c>
       <c r="E278" t="n">
-        <v>0.298263290478454</v>
+        <v>0.2982632904784539</v>
       </c>
       <c r="F278" t="n">
         <v>0.3088758220598595</v>
@@ -20536,7 +21907,7 @@
         <v>0.298232326750708</v>
       </c>
       <c r="F279" t="n">
-        <v>0.3060897249386432</v>
+        <v>0.3060897249386431</v>
       </c>
       <c r="G279" t="n">
         <v>453</v>
@@ -20612,7 +21983,7 @@
         <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>41.62632163636363</v>
+        <v>41.62632163636364</v>
       </c>
       <c r="O280" t="n">
         <v>2.299966</v>
@@ -20692,7 +22063,7 @@
         <v>0.2980211804196554</v>
       </c>
       <c r="F282" t="n">
-        <v>0.3208067241669219</v>
+        <v>0.3208067241669218</v>
       </c>
       <c r="G282" t="n">
         <v>6378</v>
@@ -20741,7 +22112,7 @@
         <v>20</v>
       </c>
       <c r="E283" t="n">
-        <v>0.2977528970867199</v>
+        <v>0.2977528970867198</v>
       </c>
       <c r="F283" t="n">
         <v>0.3135713933168563</v>
@@ -20848,7 +22219,7 @@
         <v>0.2974296329775986</v>
       </c>
       <c r="F285" t="n">
-        <v>0.3250105481455343</v>
+        <v>0.3250105481455342</v>
       </c>
       <c r="G285" t="n">
         <v>1619</v>
@@ -21001,10 +22372,10 @@
         <v>1</v>
       </c>
       <c r="E288" t="n">
-        <v>0.2969372806868186</v>
+        <v>0.2969372806868185</v>
       </c>
       <c r="F288" t="n">
-        <v>0.2969372806868186</v>
+        <v>0.2969372806868185</v>
       </c>
       <c r="G288" t="n">
         <v>321</v>
@@ -21053,7 +22424,7 @@
         <v>16</v>
       </c>
       <c r="E289" t="n">
-        <v>0.2966431839630813</v>
+        <v>0.2966431839630812</v>
       </c>
       <c r="F289" t="n">
         <v>0.3108903661453434</v>
@@ -21108,7 +22479,7 @@
         <v>0.2963707084819222</v>
       </c>
       <c r="F290" t="n">
-        <v>0.30682681162181</v>
+        <v>0.3068268116218099</v>
       </c>
       <c r="G290" t="n">
         <v>2320</v>
@@ -21212,7 +22583,7 @@
         <v>0.2963469193921627</v>
       </c>
       <c r="F292" t="n">
-        <v>0.3005050269085233</v>
+        <v>0.3005050269085232</v>
       </c>
       <c r="G292" t="n">
         <v>486</v>
@@ -21261,10 +22632,10 @@
         <v>4</v>
       </c>
       <c r="E293" t="n">
-        <v>0.2962779943230162</v>
+        <v>0.2962779943230161</v>
       </c>
       <c r="F293" t="n">
-        <v>0.3039636524920665</v>
+        <v>0.3039636524920664</v>
       </c>
       <c r="G293" t="n">
         <v>544</v>
@@ -21469,7 +22840,7 @@
         <v>2</v>
       </c>
       <c r="E297" t="n">
-        <v>0.2954116924847843</v>
+        <v>0.2954116924847842</v>
       </c>
       <c r="F297" t="n">
         <v>0.3001864796726731</v>
@@ -21628,7 +22999,7 @@
         <v>0.2951935003511251</v>
       </c>
       <c r="F300" t="n">
-        <v>0.3078604466924986</v>
+        <v>0.3078604466924985</v>
       </c>
       <c r="G300" t="n">
         <v>2980</v>
@@ -21677,10 +23048,10 @@
         <v>14</v>
       </c>
       <c r="E301" t="n">
-        <v>0.2949629010599275</v>
+        <v>0.2949629010599274</v>
       </c>
       <c r="F301" t="n">
-        <v>0.3283578813750501</v>
+        <v>0.32835788137505</v>
       </c>
       <c r="G301" t="n">
         <v>1981</v>
@@ -21836,7 +23207,7 @@
         <v>0.2945452951768361</v>
       </c>
       <c r="F304" t="n">
-        <v>0.3037337973790386</v>
+        <v>0.3037337973790385</v>
       </c>
       <c r="G304" t="n">
         <v>375</v>
@@ -21888,7 +23259,7 @@
         <v>0.2945392900069795</v>
       </c>
       <c r="F305" t="n">
-        <v>0.3049109419115819</v>
+        <v>0.3049109419115818</v>
       </c>
       <c r="G305" t="n">
         <v>1106</v>
@@ -21989,10 +23360,10 @@
         <v>5</v>
       </c>
       <c r="E307" t="n">
-        <v>0.2943433155135197</v>
+        <v>0.2943433155135196</v>
       </c>
       <c r="F307" t="n">
-        <v>0.2967447892702219</v>
+        <v>0.2967447892702218</v>
       </c>
       <c r="G307" t="n">
         <v>396</v>
@@ -22041,10 +23412,10 @@
         <v>1</v>
       </c>
       <c r="E308" t="n">
-        <v>0.2942807803013429</v>
+        <v>0.2942807803013428</v>
       </c>
       <c r="F308" t="n">
-        <v>0.2942807803013429</v>
+        <v>0.2942807803013428</v>
       </c>
       <c r="G308" t="n">
         <v>34</v>
@@ -22093,10 +23464,10 @@
         <v>1</v>
       </c>
       <c r="E309" t="n">
-        <v>0.2939605699373301</v>
+        <v>0.29396056993733</v>
       </c>
       <c r="F309" t="n">
-        <v>0.2939605699373301</v>
+        <v>0.29396056993733</v>
       </c>
       <c r="G309" t="n">
         <v>85</v>
@@ -22200,7 +23571,7 @@
         <v>0.2938826384822414</v>
       </c>
       <c r="F311" t="n">
-        <v>0.2971275245437776</v>
+        <v>0.2971275245437775</v>
       </c>
       <c r="G311" t="n">
         <v>409</v>
@@ -22249,10 +23620,10 @@
         <v>1</v>
       </c>
       <c r="E312" t="n">
-        <v>0.2937890184478985</v>
+        <v>0.2937890184478984</v>
       </c>
       <c r="F312" t="n">
-        <v>0.2937890184478985</v>
+        <v>0.2937890184478984</v>
       </c>
       <c r="G312" t="n">
         <v>28</v>
@@ -22304,7 +23675,7 @@
         <v>0.293693696648106</v>
       </c>
       <c r="F313" t="n">
-        <v>0.3012431814533945</v>
+        <v>0.3012431814533944</v>
       </c>
       <c r="G313" t="n">
         <v>239</v>
@@ -22457,7 +23828,7 @@
         <v>65</v>
       </c>
       <c r="E316" t="n">
-        <v>0.2934009808848798</v>
+        <v>0.2934009808848797</v>
       </c>
       <c r="F316" t="n">
         <v>0.3195758064046609</v>
@@ -22613,10 +23984,10 @@
         <v>1</v>
       </c>
       <c r="E319" t="n">
-        <v>0.2930339494893556</v>
+        <v>0.2930339494893555</v>
       </c>
       <c r="F319" t="n">
-        <v>0.2930339494893556</v>
+        <v>0.2930339494893555</v>
       </c>
       <c r="G319" t="n">
         <v>89</v>
@@ -22692,7 +24063,7 @@
         <v>1</v>
       </c>
       <c r="N320" t="n">
-        <v>38.35649095918367</v>
+        <v>38.35649095918368</v>
       </c>
       <c r="O320" t="n">
         <v>-0.4861343714285714</v>
@@ -22717,10 +24088,10 @@
         <v>532</v>
       </c>
       <c r="E321" t="n">
-        <v>0.292574516389671</v>
+        <v>0.2925745163896709</v>
       </c>
       <c r="F321" t="n">
-        <v>0.3394754208877948</v>
+        <v>0.3394754208877947</v>
       </c>
       <c r="G321" t="n">
         <v>66968</v>
@@ -22729,7 +24100,7 @@
         <v>10.59990746047573</v>
       </c>
       <c r="I321" t="n">
-        <v>2.146141140670535</v>
+        <v>2.146141140670536</v>
       </c>
       <c r="J321" t="n">
         <v>73233</v>
@@ -22769,10 +24140,10 @@
         <v>1</v>
       </c>
       <c r="E322" t="n">
-        <v>0.2924449081908577</v>
+        <v>0.2924449081908576</v>
       </c>
       <c r="F322" t="n">
-        <v>0.2924449081908577</v>
+        <v>0.2924449081908576</v>
       </c>
       <c r="G322" t="n">
         <v>206</v>
@@ -22928,7 +24299,7 @@
         <v>0.2918684299778437</v>
       </c>
       <c r="F325" t="n">
-        <v>0.3085187376369971</v>
+        <v>0.308518737636997</v>
       </c>
       <c r="G325" t="n">
         <v>5638</v>
@@ -22980,7 +24351,7 @@
         <v>0.291791570311732</v>
       </c>
       <c r="F326" t="n">
-        <v>0.2975297366545036</v>
+        <v>0.2975297366545035</v>
       </c>
       <c r="G326" t="n">
         <v>361</v>
@@ -23029,7 +24400,7 @@
         <v>5</v>
       </c>
       <c r="E327" t="n">
-        <v>0.2916501675448476</v>
+        <v>0.2916501675448475</v>
       </c>
       <c r="F327" t="n">
         <v>0.294261710476501</v>
@@ -23041,7 +24412,7 @@
         <v>11.76383295469065</v>
       </c>
       <c r="I327" t="n">
-        <v>1.746942221864822</v>
+        <v>1.746942221864823</v>
       </c>
       <c r="J327" t="n">
         <v>672</v>
@@ -23081,7 +24452,7 @@
         <v>2</v>
       </c>
       <c r="E328" t="n">
-        <v>0.2914087497335868</v>
+        <v>0.2914087497335867</v>
       </c>
       <c r="F328" t="n">
         <v>0.2953008340313514</v>
@@ -23133,7 +24504,7 @@
         <v>10</v>
       </c>
       <c r="E329" t="n">
-        <v>0.2912864305612816</v>
+        <v>0.2912864305612815</v>
       </c>
       <c r="F329" t="n">
         <v>0.3012981276633631</v>
@@ -23185,7 +24556,7 @@
         <v>6</v>
       </c>
       <c r="E330" t="n">
-        <v>0.2911681737605477</v>
+        <v>0.2911681737605476</v>
       </c>
       <c r="F330" t="n">
         <v>0.2989295278487792</v>
@@ -23301,7 +24672,7 @@
         <v>6.318060469808222</v>
       </c>
       <c r="I332" t="n">
-        <v>1.890796197336291</v>
+        <v>1.89079619733629</v>
       </c>
       <c r="J332" t="n">
         <v>4103</v>
@@ -23350,7 +24721,7 @@
         <v>252</v>
       </c>
       <c r="H333" t="n">
-        <v>7.008775052383259</v>
+        <v>7.00877505238326</v>
       </c>
       <c r="I333" t="n">
         <v>1.246612466124661</v>
@@ -23500,7 +24871,7 @@
         <v>0.2903719867788724</v>
       </c>
       <c r="F336" t="n">
-        <v>0.3852801044787885</v>
+        <v>0.3852801044787884</v>
       </c>
       <c r="G336" t="n">
         <v>23793</v>
@@ -23604,7 +24975,7 @@
         <v>0.2901227368501619</v>
       </c>
       <c r="F338" t="n">
-        <v>0.291685979751082</v>
+        <v>0.2916859797510819</v>
       </c>
       <c r="G338" t="n">
         <v>310</v>
@@ -23653,10 +25024,10 @@
         <v>1</v>
       </c>
       <c r="E339" t="n">
-        <v>0.2898682009069196</v>
+        <v>0.2898682009069195</v>
       </c>
       <c r="F339" t="n">
-        <v>0.2898682009069196</v>
+        <v>0.2898682009069195</v>
       </c>
       <c r="G339" t="n">
         <v>31</v>
@@ -23705,10 +25076,10 @@
         <v>1</v>
       </c>
       <c r="E340" t="n">
-        <v>0.2897787219781591</v>
+        <v>0.289778721978159</v>
       </c>
       <c r="F340" t="n">
-        <v>0.2897787219781591</v>
+        <v>0.289778721978159</v>
       </c>
       <c r="G340" t="n">
         <v>66</v>
@@ -23861,7 +25232,7 @@
         <v>23</v>
       </c>
       <c r="E343" t="n">
-        <v>0.2890530997211929</v>
+        <v>0.2890530997211928</v>
       </c>
       <c r="F343" t="n">
         <v>0.3128573763929978</v>
@@ -24130,7 +25501,7 @@
         <v>967</v>
       </c>
       <c r="H348" t="n">
-        <v>10.05342216980451</v>
+        <v>10.05342216980452</v>
       </c>
       <c r="I348" t="n">
         <v>2.075693360898736</v>
@@ -24173,10 +25544,10 @@
         <v>1</v>
       </c>
       <c r="E349" t="n">
-        <v>0.2876427127755911</v>
+        <v>0.287642712775591</v>
       </c>
       <c r="F349" t="n">
-        <v>0.2876427127755911</v>
+        <v>0.287642712775591</v>
       </c>
       <c r="G349" t="n">
         <v>205</v>
@@ -24644,7 +26015,7 @@
         <v>0.2870191905504742</v>
       </c>
       <c r="F358" t="n">
-        <v>0.2926788445681887</v>
+        <v>0.2926788445681886</v>
       </c>
       <c r="G358" t="n">
         <v>274</v>
@@ -24693,10 +26064,10 @@
         <v>2</v>
       </c>
       <c r="E359" t="n">
-        <v>0.2866956712451673</v>
+        <v>0.2866956712451672</v>
       </c>
       <c r="F359" t="n">
-        <v>0.2926543868209565</v>
+        <v>0.2926543868209564</v>
       </c>
       <c r="G359" t="n">
         <v>308</v>
@@ -24705,7 +26076,7 @@
         <v>7.913010461386512</v>
       </c>
       <c r="I359" t="n">
-        <v>1.75103519668737</v>
+        <v>1.751035196687371</v>
       </c>
       <c r="J359" t="n">
         <v>381</v>
@@ -24748,7 +26119,7 @@
         <v>0.2866675803197221</v>
       </c>
       <c r="F360" t="n">
-        <v>0.2921467593036489</v>
+        <v>0.2921467593036488</v>
       </c>
       <c r="G360" t="n">
         <v>351</v>
@@ -24797,7 +26168,7 @@
         <v>10</v>
       </c>
       <c r="E361" t="n">
-        <v>0.2865631332824685</v>
+        <v>0.2865631332824684</v>
       </c>
       <c r="F361" t="n">
         <v>0.2926480837704843</v>
@@ -25161,7 +26532,7 @@
         <v>2</v>
       </c>
       <c r="E368" t="n">
-        <v>0.2858212843418365</v>
+        <v>0.2858212843418364</v>
       </c>
       <c r="F368" t="n">
         <v>0.2900177606508222</v>
@@ -25473,7 +26844,7 @@
         <v>2</v>
       </c>
       <c r="E374" t="n">
-        <v>0.2846460833037707</v>
+        <v>0.2846460833037706</v>
       </c>
       <c r="F374" t="n">
         <v>0.2920090063095045</v>
@@ -25632,7 +27003,7 @@
         <v>0.2842912695782928</v>
       </c>
       <c r="F377" t="n">
-        <v>0.2939630080910535</v>
+        <v>0.2939630080910534</v>
       </c>
       <c r="G377" t="n">
         <v>1155</v>
@@ -25681,7 +27052,7 @@
         <v>20</v>
       </c>
       <c r="E378" t="n">
-        <v>0.2841942061207499</v>
+        <v>0.2841942061207498</v>
       </c>
       <c r="F378" t="n">
         <v>0.2975094312379721</v>
@@ -25785,10 +27156,10 @@
         <v>1</v>
       </c>
       <c r="E380" t="n">
-        <v>0.284169013687731</v>
+        <v>0.2841690136877309</v>
       </c>
       <c r="F380" t="n">
-        <v>0.284169013687731</v>
+        <v>0.2841690136877309</v>
       </c>
       <c r="G380" t="n">
         <v>75</v>
@@ -25901,7 +27272,7 @@
         <v>12.08517876777488</v>
       </c>
       <c r="I382" t="n">
-        <v>2.193999061190571</v>
+        <v>2.19399906119057</v>
       </c>
       <c r="J382" t="n">
         <v>15372</v>
@@ -25944,7 +27315,7 @@
         <v>0.2837109874366653</v>
       </c>
       <c r="F383" t="n">
-        <v>0.2941229874781419</v>
+        <v>0.2941229874781418</v>
       </c>
       <c r="G383" t="n">
         <v>1499</v>
@@ -26149,10 +27520,10 @@
         <v>1</v>
       </c>
       <c r="E387" t="n">
-        <v>0.2828184392943777</v>
+        <v>0.2828184392943776</v>
       </c>
       <c r="F387" t="n">
-        <v>0.2828184392943777</v>
+        <v>0.2828184392943776</v>
       </c>
       <c r="G387" t="n">
         <v>37</v>
@@ -26461,7 +27832,7 @@
         <v>24</v>
       </c>
       <c r="E393" t="n">
-        <v>0.2823413106234776</v>
+        <v>0.2823413106234775</v>
       </c>
       <c r="F393" t="n">
         <v>0.2978501148085362</v>
@@ -26669,10 +28040,10 @@
         <v>1</v>
       </c>
       <c r="E397" t="n">
-        <v>0.2822039476077866</v>
+        <v>0.2822039476077865</v>
       </c>
       <c r="F397" t="n">
-        <v>0.2822039476077866</v>
+        <v>0.2822039476077865</v>
       </c>
       <c r="G397" t="n">
         <v>210</v>
@@ -26877,7 +28248,7 @@
         <v>3</v>
       </c>
       <c r="E401" t="n">
-        <v>0.281966817327279</v>
+        <v>0.2819668173272789</v>
       </c>
       <c r="F401" t="n">
         <v>0.2943618808753476</v>
@@ -27115,7 +28486,7 @@
         <v>35.28889113636364</v>
       </c>
       <c r="O405" t="n">
-        <v>-2.946369295454546</v>
+        <v>-2.946369295454545</v>
       </c>
       <c r="P405" t="n">
         <v>404</v>
@@ -27192,7 +28563,7 @@
         <v>0.2806372250529809</v>
       </c>
       <c r="F407" t="n">
-        <v>0.290692455065837</v>
+        <v>0.2906924550658369</v>
       </c>
       <c r="G407" t="n">
         <v>315</v>
@@ -27345,10 +28716,10 @@
         <v>1</v>
       </c>
       <c r="E410" t="n">
-        <v>0.2800782273924459</v>
+        <v>0.2800782273924458</v>
       </c>
       <c r="F410" t="n">
-        <v>0.2800782273924459</v>
+        <v>0.2800782273924458</v>
       </c>
       <c r="G410" t="n">
         <v>85</v>
@@ -27501,7 +28872,7 @@
         <v>179</v>
       </c>
       <c r="E413" t="n">
-        <v>0.2793792296023777</v>
+        <v>0.2793792296023776</v>
       </c>
       <c r="F413" t="n">
         <v>0.3115778203873842</v>
@@ -28024,7 +29395,7 @@
         <v>0.2779316207501539</v>
       </c>
       <c r="F423" t="n">
-        <v>0.308395459516959</v>
+        <v>0.3083954595169589</v>
       </c>
       <c r="G423" t="n">
         <v>25182</v>
@@ -28076,7 +29447,7 @@
         <v>0.2779157972239722</v>
       </c>
       <c r="F424" t="n">
-        <v>0.2940426135448309</v>
+        <v>0.2940426135448308</v>
       </c>
       <c r="G424" t="n">
         <v>2805</v>
@@ -28180,7 +29551,7 @@
         <v>0.2776214475019464</v>
       </c>
       <c r="F426" t="n">
-        <v>0.2826853347211151</v>
+        <v>0.282685334721115</v>
       </c>
       <c r="G426" t="n">
         <v>628</v>
@@ -28388,7 +29759,7 @@
         <v>0.2766704595752876</v>
       </c>
       <c r="F430" t="n">
-        <v>0.3114974119429014</v>
+        <v>0.3114974119429013</v>
       </c>
       <c r="G430" t="n">
         <v>11971</v>
@@ -28397,7 +29768,7 @@
         <v>12.37696682640618</v>
       </c>
       <c r="I430" t="n">
-        <v>2.039484942171522</v>
+        <v>2.039484942171521</v>
       </c>
       <c r="J430" t="n">
         <v>12258</v>
@@ -28437,7 +29808,7 @@
         <v>7</v>
       </c>
       <c r="E431" t="n">
-        <v>0.2763491609341541</v>
+        <v>0.276349160934154</v>
       </c>
       <c r="F431" t="n">
         <v>0.2832553952354751</v>
@@ -28489,10 +29860,10 @@
         <v>1</v>
       </c>
       <c r="E432" t="n">
-        <v>0.2762084156236511</v>
+        <v>0.276208415623651</v>
       </c>
       <c r="F432" t="n">
-        <v>0.2762084156236511</v>
+        <v>0.276208415623651</v>
       </c>
       <c r="G432" t="n">
         <v>37</v>
@@ -28752,7 +30123,7 @@
         <v>0.2757250455738016</v>
       </c>
       <c r="F437" t="n">
-        <v>0.2762058091363994</v>
+        <v>0.2762058091363993</v>
       </c>
       <c r="G437" t="n">
         <v>466</v>
@@ -29012,7 +30383,7 @@
         <v>0.2743419755076222</v>
       </c>
       <c r="F442" t="n">
-        <v>0.327642651569287</v>
+        <v>0.3276426515692869</v>
       </c>
       <c r="G442" t="n">
         <v>34198</v>
@@ -29061,7 +30432,7 @@
         <v>4</v>
       </c>
       <c r="E443" t="n">
-        <v>0.2742454366689006</v>
+        <v>0.2742454366689005</v>
       </c>
       <c r="F443" t="n">
         <v>0.2899257123321703</v>
@@ -29269,10 +30640,10 @@
         <v>1</v>
       </c>
       <c r="E447" t="n">
-        <v>0.2738034253578746</v>
+        <v>0.2738034253578745</v>
       </c>
       <c r="F447" t="n">
-        <v>0.2738034253578746</v>
+        <v>0.2738034253578745</v>
       </c>
       <c r="G447" t="n">
         <v>127</v>
@@ -29376,7 +30747,7 @@
         <v>0.2734983978667447</v>
       </c>
       <c r="F449" t="n">
-        <v>0.2845027972905885</v>
+        <v>0.2845027972905884</v>
       </c>
       <c r="G449" t="n">
         <v>1041</v>
@@ -29477,7 +30848,7 @@
         <v>61</v>
       </c>
       <c r="E451" t="n">
-        <v>0.2732458117957992</v>
+        <v>0.2732458117957991</v>
       </c>
       <c r="F451" t="n">
         <v>0.2949950326455233</v>
@@ -29633,10 +31004,10 @@
         <v>1</v>
       </c>
       <c r="E454" t="n">
-        <v>0.2729975440481027</v>
+        <v>0.2729975440481026</v>
       </c>
       <c r="F454" t="n">
-        <v>0.2729975440481027</v>
+        <v>0.2729975440481026</v>
       </c>
       <c r="G454" t="n">
         <v>112</v>
@@ -29737,10 +31108,10 @@
         <v>1</v>
       </c>
       <c r="E456" t="n">
-        <v>0.2724297472363563</v>
+        <v>0.2724297472363562</v>
       </c>
       <c r="F456" t="n">
-        <v>0.2724297472363563</v>
+        <v>0.2724297472363562</v>
       </c>
       <c r="G456" t="n">
         <v>26</v>
@@ -29789,7 +31160,7 @@
         <v>202</v>
       </c>
       <c r="E457" t="n">
-        <v>0.272327917571045</v>
+        <v>0.2723279175710449</v>
       </c>
       <c r="F457" t="n">
         <v>0.2953535504799218</v>
@@ -30052,7 +31423,7 @@
         <v>0.2711086808682969</v>
       </c>
       <c r="F462" t="n">
-        <v>0.3106297849484551</v>
+        <v>0.310629784948455</v>
       </c>
       <c r="G462" t="n">
         <v>10296</v>
@@ -30232,7 +31603,7 @@
         <v>0</v>
       </c>
       <c r="N465" t="n">
-        <v>42.77355799999999</v>
+        <v>42.773558</v>
       </c>
       <c r="O465" t="n">
         <v>-1.70731</v>
@@ -30260,7 +31631,7 @@
         <v>0.2704075581477351</v>
       </c>
       <c r="F466" t="n">
-        <v>0.2884375284193627</v>
+        <v>0.2884375284193626</v>
       </c>
       <c r="G466" t="n">
         <v>2638</v>
@@ -30361,7 +31732,7 @@
         <v>75</v>
       </c>
       <c r="E468" t="n">
-        <v>0.2697507469230077</v>
+        <v>0.2697507469230076</v>
       </c>
       <c r="F468" t="n">
         <v>0.2937662965017688</v>
@@ -30413,10 +31784,10 @@
         <v>1</v>
       </c>
       <c r="E469" t="n">
-        <v>0.2697168830217566</v>
+        <v>0.2697168830217565</v>
       </c>
       <c r="F469" t="n">
-        <v>0.2697168830217566</v>
+        <v>0.2697168830217565</v>
       </c>
       <c r="G469" t="n">
         <v>87</v>
@@ -30517,10 +31888,10 @@
         <v>1</v>
       </c>
       <c r="E471" t="n">
-        <v>0.2694926687253336</v>
+        <v>0.2694926687253335</v>
       </c>
       <c r="F471" t="n">
-        <v>0.2694926687253336</v>
+        <v>0.2694926687253335</v>
       </c>
       <c r="G471" t="n">
         <v>30</v>
@@ -30569,10 +31940,10 @@
         <v>164</v>
       </c>
       <c r="E472" t="n">
-        <v>0.2694057956761921</v>
+        <v>0.269405795676192</v>
       </c>
       <c r="F472" t="n">
-        <v>0.2942936117384761</v>
+        <v>0.294293611738476</v>
       </c>
       <c r="G472" t="n">
         <v>20025</v>
@@ -30621,7 +31992,7 @@
         <v>68</v>
       </c>
       <c r="E473" t="n">
-        <v>0.2693699458446919</v>
+        <v>0.2693699458446918</v>
       </c>
       <c r="F473" t="n">
         <v>0.3060378272639468</v>
@@ -30780,7 +32151,7 @@
         <v>0.2688628535329193</v>
       </c>
       <c r="F476" t="n">
-        <v>0.2748466054434314</v>
+        <v>0.2748466054434313</v>
       </c>
       <c r="G476" t="n">
         <v>603</v>
@@ -30832,7 +32203,7 @@
         <v>0.2683708490455727</v>
       </c>
       <c r="F477" t="n">
-        <v>0.2889261173411353</v>
+        <v>0.2889261173411352</v>
       </c>
       <c r="G477" t="n">
         <v>2530</v>
@@ -30881,10 +32252,10 @@
         <v>1</v>
       </c>
       <c r="E478" t="n">
-        <v>0.2680180326988573</v>
+        <v>0.2680180326988572</v>
       </c>
       <c r="F478" t="n">
-        <v>0.2680180326988573</v>
+        <v>0.2680180326988572</v>
       </c>
       <c r="G478" t="n">
         <v>95</v>
@@ -31037,7 +32408,7 @@
         <v>166</v>
       </c>
       <c r="E481" t="n">
-        <v>0.2676487736542129</v>
+        <v>0.2676487736542128</v>
       </c>
       <c r="F481" t="n">
         <v>0.3103149517109111</v>
@@ -31049,7 +32420,7 @@
         <v>11.65582751425326</v>
       </c>
       <c r="I481" t="n">
-        <v>1.740500258576811</v>
+        <v>1.740500258576812</v>
       </c>
       <c r="J481" t="n">
         <v>29207</v>
@@ -31067,7 +32438,7 @@
         <v>42.85095603614458</v>
       </c>
       <c r="O481" t="n">
-        <v>-2.677920487951807</v>
+        <v>-2.677920487951808</v>
       </c>
       <c r="P481" t="n">
         <v>480</v>
@@ -31144,7 +32515,7 @@
         <v>0.267218218527344</v>
       </c>
       <c r="F483" t="n">
-        <v>0.2791977230829014</v>
+        <v>0.2791977230829013</v>
       </c>
       <c r="G483" t="n">
         <v>1745</v>
@@ -31193,10 +32564,10 @@
         <v>21</v>
       </c>
       <c r="E484" t="n">
-        <v>0.2671068487828123</v>
+        <v>0.2671068487828122</v>
       </c>
       <c r="F484" t="n">
-        <v>0.2864107414894768</v>
+        <v>0.2864107414894767</v>
       </c>
       <c r="G484" t="n">
         <v>3634</v>
@@ -31404,7 +32775,7 @@
         <v>0.2665283776815991</v>
       </c>
       <c r="F488" t="n">
-        <v>0.2927397652522232</v>
+        <v>0.2927397652522231</v>
       </c>
       <c r="G488" t="n">
         <v>1676</v>
@@ -31413,7 +32784,7 @@
         <v>12.41265615146908</v>
       </c>
       <c r="I488" t="n">
-        <v>1.756206548892383</v>
+        <v>1.756206548892384</v>
       </c>
       <c r="J488" t="n">
         <v>1791</v>
@@ -31609,7 +32980,7 @@
         <v>3</v>
       </c>
       <c r="E492" t="n">
-        <v>0.2660496889440158</v>
+        <v>0.2660496889440157</v>
       </c>
       <c r="F492" t="n">
         <v>0.2778515348217613</v>
@@ -31713,7 +33084,7 @@
         <v>186</v>
       </c>
       <c r="E494" t="n">
-        <v>0.2658883647369945</v>
+        <v>0.2658883647369944</v>
       </c>
       <c r="F494" t="n">
         <v>0.3005120395760801</v>
@@ -32179,7 +33550,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4404046217456826</v>
+        <v>0.4404046217456825</v>
       </c>
       <c r="D3" t="n">
         <v>12158</v>
@@ -32417,7 +33788,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2692936794206539</v>
+        <v>0.2692936794206538</v>
       </c>
       <c r="D17" t="n">
         <v>43002</v>
@@ -32485,7 +33856,7 @@
         <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2676879580532479</v>
+        <v>0.2676879580532478</v>
       </c>
       <c r="D21" t="n">
         <v>15062</v>
@@ -32502,7 +33873,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2676487736542129</v>
+        <v>0.2676487736542128</v>
       </c>
       <c r="D22" t="n">
         <v>26970</v>
@@ -32553,7 +33924,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2638860625801551</v>
+        <v>0.263886062580155</v>
       </c>
       <c r="D25" t="n">
         <v>24291</v>
@@ -32604,7 +33975,7 @@
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2523978776291874</v>
+        <v>0.2523978776291873</v>
       </c>
       <c r="D28" t="n">
         <v>16619</v>
@@ -32638,7 +34009,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2505313237909779</v>
+        <v>0.2505313237909778</v>
       </c>
       <c r="D30" t="n">
         <v>76436</v>
@@ -32672,7 +34043,7 @@
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2429516481812994</v>
+        <v>0.2429516481812993</v>
       </c>
       <c r="D32" t="n">
         <v>14624</v>
@@ -32706,7 +34077,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2402350181414876</v>
+        <v>0.2402350181414875</v>
       </c>
       <c r="D34" t="n">
         <v>7089</v>
@@ -32791,7 +34162,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2277915576433505</v>
+        <v>0.2277915576433504</v>
       </c>
       <c r="D39" t="n">
         <v>5329</v>
@@ -32808,7 +34179,7 @@
         <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2238505300074536</v>
+        <v>0.2238505300074535</v>
       </c>
       <c r="D40" t="n">
         <v>18941</v>
@@ -32825,7 +34196,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2237114862150722</v>
+        <v>0.2237114862150721</v>
       </c>
       <c r="D41" t="n">
         <v>6506</v>
@@ -32842,7 +34213,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2231065254634674</v>
+        <v>0.2231065254634673</v>
       </c>
       <c r="D42" t="n">
         <v>18018</v>
@@ -32910,7 +34281,7 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2108250831995349</v>
+        <v>0.2108250831995348</v>
       </c>
       <c r="D46" t="n">
         <v>21939</v>
@@ -32927,7 +34298,7 @@
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2096047968588958</v>
+        <v>0.2096047968588957</v>
       </c>
       <c r="D47" t="n">
         <v>5320</v>
@@ -32985,6 +34356,233 @@
       </c>
       <c r="E50" t="n">
         <v>30203</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>perfil</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>municipios</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>renta_media</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>vol_75plus</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fofm_medio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gran ciudad — mercado masivo</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30033.64</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47895.82</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Municipio equilibrado — perfil estándar</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C3" t="n">
+        <v>31317.33</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13527.63</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Zona envejecida — solvencia ajustada</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>54</v>
+      </c>
+      <c r="C4" t="n">
+        <v>30270.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4488.78</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Zona premium — máxima solvencia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>67280</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4462.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Para qué sirve</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mapa_top100.html</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mapa interactivo — abrir en navegador, clicar en cada punto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>grafico_perfiles.png</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gráfico de barras con los 4 perfiles estratégicos — meter en slides</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>grafico_top20.png</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ranking visual del top 20 municipios — meter en slides</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>grafico_solvencia_mercado.png</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Scatter solvencia vs mercado — meter en slides</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>resultados_akademia.xlsx</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Excel con todas las pestañas de resultados</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>top100_con_clusters.csv</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Datos completos del top 100 con perfil asignado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dataset_maestro.csv</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dataset central con todas las variables calculadas</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/resultados_akademia.xlsx
+++ b/resultados_akademia.xlsx
@@ -10,8 +10,6 @@
     <sheet name="Top 100 ubicaciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Ranking municipios" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Resumen por provincia" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Perfiles estratégicos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Guía de archivos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T101"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,21 +516,6 @@
           <t>posicion_final</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>cluster</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>perfil</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>perfil_corto</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -588,19 +571,6 @@
       <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Zona premium — máxima solvencia</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -648,26 +618,13 @@
         <v>40.41240833333333</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.888334666666665</v>
+        <v>-3.888334666666666</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Zona premium — máxima solvencia</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -724,19 +681,6 @@
       <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Zona premium — máxima solvencia</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -757,7 +701,7 @@
         <v>0.4710962657811085</v>
       </c>
       <c r="F5" t="n">
-        <v>0.49927529849953</v>
+        <v>0.4992752984995301</v>
       </c>
       <c r="G5" t="n">
         <v>5967</v>
@@ -791,19 +735,6 @@
       </c>
       <c r="Q5" t="n">
         <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Zona premium — máxima solvencia</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -825,7 +756,7 @@
         <v>0.4432404023831725</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4498010966345255</v>
+        <v>0.4498010966345256</v>
       </c>
       <c r="G6" t="n">
         <v>757</v>
@@ -859,19 +790,6 @@
       </c>
       <c r="Q6" t="n">
         <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Zona premium — máxima solvencia</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -890,10 +808,10 @@
         <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4068771970727667</v>
+        <v>0.4068771970727668</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4300106893861273</v>
+        <v>0.4300106893861274</v>
       </c>
       <c r="G7" t="n">
         <v>5434</v>
@@ -927,20 +845,6 @@
       </c>
       <c r="Q7" t="n">
         <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -997,19 +901,6 @@
       <c r="Q8" t="n">
         <v>7</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1027,7 +918,7 @@
         <v>144</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3170504917120006</v>
+        <v>0.3170504917120007</v>
       </c>
       <c r="F9" t="n">
         <v>0.3414396819797916</v>
@@ -1036,7 +927,7 @@
         <v>23273</v>
       </c>
       <c r="H9" t="n">
-        <v>13.06230010984514</v>
+        <v>13.06230010984515</v>
       </c>
       <c r="I9" t="n">
         <v>2.182128026570019</v>
@@ -1064,19 +955,6 @@
       </c>
       <c r="Q9" t="n">
         <v>8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -1125,27 +1003,13 @@
         <v>39.67150431707317</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2472086585365853</v>
+        <v>-0.2472086585365854</v>
       </c>
       <c r="P10" t="n">
         <v>192</v>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -1202,20 +1066,6 @@
       <c r="Q11" t="n">
         <v>10</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1271,20 +1121,6 @@
       <c r="Q12" t="n">
         <v>11</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1302,7 +1138,7 @@
         <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3020496236136051</v>
+        <v>0.3020496236136052</v>
       </c>
       <c r="F13" t="n">
         <v>0.3424089031161846</v>
@@ -1332,27 +1168,13 @@
         <v>38.40051353846154</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4339552307692307</v>
+        <v>-0.4339552307692308</v>
       </c>
       <c r="P13" t="n">
         <v>232</v>
       </c>
       <c r="Q13" t="n">
         <v>12</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -1374,7 +1196,7 @@
         <v>0.3015859678611488</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3325271833683438</v>
+        <v>0.3325271833683439</v>
       </c>
       <c r="G14" t="n">
         <v>45720</v>
@@ -1383,7 +1205,7 @@
         <v>13.70222885208217</v>
       </c>
       <c r="I14" t="n">
-        <v>2.18702816193344</v>
+        <v>2.187028161933439</v>
       </c>
       <c r="J14" t="n">
         <v>40724</v>
@@ -1408,19 +1230,6 @@
       </c>
       <c r="Q14" t="n">
         <v>13</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -1477,19 +1286,6 @@
       <c r="Q15" t="n">
         <v>14</v>
       </c>
-      <c r="R15" t="n">
-        <v>3</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1510,7 +1306,7 @@
         <v>0.2951935003511251</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3078604466924985</v>
+        <v>0.3078604466924986</v>
       </c>
       <c r="G16" t="n">
         <v>2980</v>
@@ -1544,20 +1340,6 @@
       </c>
       <c r="Q16" t="n">
         <v>15</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -1603,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>38.35649095918368</v>
+        <v>38.35649095918367</v>
       </c>
       <c r="O17" t="n">
         <v>-0.4861343714285714</v>
@@ -1613,19 +1395,6 @@
       </c>
       <c r="Q17" t="n">
         <v>16</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -1644,10 +1413,10 @@
         <v>532</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2925745163896709</v>
+        <v>0.292574516389671</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3394754208877947</v>
+        <v>0.3394754208877948</v>
       </c>
       <c r="G18" t="n">
         <v>66968</v>
@@ -1656,7 +1425,7 @@
         <v>10.59990746047573</v>
       </c>
       <c r="I18" t="n">
-        <v>2.146141140670536</v>
+        <v>2.146141140670535</v>
       </c>
       <c r="J18" t="n">
         <v>73233</v>
@@ -1681,19 +1450,6 @@
       </c>
       <c r="Q18" t="n">
         <v>17</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
       </c>
     </row>
     <row r="19">
@@ -1715,7 +1471,7 @@
         <v>0.2903719867788724</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3852801044787884</v>
+        <v>0.3852801044787885</v>
       </c>
       <c r="G19" t="n">
         <v>23793</v>
@@ -1749,19 +1505,6 @@
       </c>
       <c r="Q19" t="n">
         <v>18</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="20">
@@ -1818,20 +1561,6 @@
       <c r="Q20" t="n">
         <v>19</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1861,7 +1590,7 @@
         <v>12.08517876777488</v>
       </c>
       <c r="I21" t="n">
-        <v>2.19399906119057</v>
+        <v>2.193999061190571</v>
       </c>
       <c r="J21" t="n">
         <v>15372</v>
@@ -1886,19 +1615,6 @@
       </c>
       <c r="Q21" t="n">
         <v>20</v>
-      </c>
-      <c r="R21" t="n">
-        <v>3</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -1955,19 +1671,6 @@
       <c r="Q22" t="n">
         <v>21</v>
       </c>
-      <c r="R22" t="n">
-        <v>3</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2023,19 +1726,6 @@
       <c r="Q23" t="n">
         <v>22</v>
       </c>
-      <c r="R23" t="n">
-        <v>3</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2083,27 +1773,13 @@
         <v>35.28889113636364</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.946369295454545</v>
+        <v>-2.946369295454546</v>
       </c>
       <c r="P24" t="n">
         <v>404</v>
       </c>
       <c r="Q24" t="n">
         <v>23</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -2122,7 +1798,7 @@
         <v>179</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2793792296023776</v>
+        <v>0.2793792296023777</v>
       </c>
       <c r="F25" t="n">
         <v>0.3115778203873842</v>
@@ -2159,19 +1835,6 @@
       </c>
       <c r="Q25" t="n">
         <v>24</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="26">
@@ -2228,20 +1891,6 @@
       <c r="Q26" t="n">
         <v>25</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2297,19 +1946,6 @@
       <c r="Q27" t="n">
         <v>26</v>
       </c>
-      <c r="R27" t="n">
-        <v>3</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2365,19 +2001,6 @@
       <c r="Q28" t="n">
         <v>27</v>
       </c>
-      <c r="R28" t="n">
-        <v>3</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2433,19 +2056,6 @@
       <c r="Q29" t="n">
         <v>28</v>
       </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2466,7 +2076,7 @@
         <v>0.2779316207501539</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3083954595169589</v>
+        <v>0.308395459516959</v>
       </c>
       <c r="G30" t="n">
         <v>25182</v>
@@ -2500,19 +2110,6 @@
       </c>
       <c r="Q30" t="n">
         <v>29</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="31">
@@ -2534,7 +2131,7 @@
         <v>0.2779157972239722</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2940426135448308</v>
+        <v>0.2940426135448309</v>
       </c>
       <c r="G31" t="n">
         <v>2805</v>
@@ -2568,20 +2165,6 @@
       </c>
       <c r="Q31" t="n">
         <v>30</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="32">
@@ -2638,20 +2221,6 @@
       <c r="Q32" t="n">
         <v>31</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2672,7 +2241,7 @@
         <v>0.2743419755076222</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3276426515692869</v>
+        <v>0.327642651569287</v>
       </c>
       <c r="G33" t="n">
         <v>34198</v>
@@ -2706,19 +2275,6 @@
       </c>
       <c r="Q33" t="n">
         <v>32</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
       </c>
     </row>
     <row r="34">
@@ -2775,20 +2331,6 @@
       <c r="Q34" t="n">
         <v>33</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2806,7 +2348,7 @@
         <v>61</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2732458117957991</v>
+        <v>0.2732458117957992</v>
       </c>
       <c r="F35" t="n">
         <v>0.2949950326455233</v>
@@ -2843,20 +2385,6 @@
       </c>
       <c r="Q35" t="n">
         <v>34</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="36">
@@ -2913,19 +2441,6 @@
       <c r="Q36" t="n">
         <v>35</v>
       </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2981,20 +2496,6 @@
       <c r="Q37" t="n">
         <v>36</v>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3015,7 +2516,7 @@
         <v>0.2711086808682969</v>
       </c>
       <c r="F38" t="n">
-        <v>0.310629784948455</v>
+        <v>0.3106297849484551</v>
       </c>
       <c r="G38" t="n">
         <v>10296</v>
@@ -3049,19 +2550,6 @@
       </c>
       <c r="Q38" t="n">
         <v>37</v>
-      </c>
-      <c r="R38" t="n">
-        <v>3</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="39">
@@ -3118,20 +2606,6 @@
       <c r="Q39" t="n">
         <v>38</v>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3149,7 +2623,7 @@
         <v>75</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2697507469230076</v>
+        <v>0.2697507469230077</v>
       </c>
       <c r="F40" t="n">
         <v>0.2937662965017688</v>
@@ -3186,19 +2660,6 @@
       </c>
       <c r="Q40" t="n">
         <v>39</v>
-      </c>
-      <c r="R40" t="n">
-        <v>3</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="41">
@@ -3217,10 +2678,10 @@
         <v>164</v>
       </c>
       <c r="E41" t="n">
-        <v>0.269405795676192</v>
+        <v>0.2694057956761921</v>
       </c>
       <c r="F41" t="n">
-        <v>0.294293611738476</v>
+        <v>0.2942936117384761</v>
       </c>
       <c r="G41" t="n">
         <v>20025</v>
@@ -3254,19 +2715,6 @@
       </c>
       <c r="Q41" t="n">
         <v>40</v>
-      </c>
-      <c r="R41" t="n">
-        <v>3</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="42">
@@ -3288,7 +2736,7 @@
         <v>0.2683708490455727</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2889261173411352</v>
+        <v>0.2889261173411353</v>
       </c>
       <c r="G42" t="n">
         <v>2530</v>
@@ -3322,20 +2770,6 @@
       </c>
       <c r="Q42" t="n">
         <v>41</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="43">
@@ -3392,20 +2826,6 @@
       <c r="Q43" t="n">
         <v>42</v>
       </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3461,20 +2881,6 @@
       <c r="Q44" t="n">
         <v>43</v>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3492,7 +2898,7 @@
         <v>166</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2676487736542128</v>
+        <v>0.2676487736542129</v>
       </c>
       <c r="F45" t="n">
         <v>0.3103149517109111</v>
@@ -3504,7 +2910,7 @@
         <v>11.65582751425326</v>
       </c>
       <c r="I45" t="n">
-        <v>1.740500258576812</v>
+        <v>1.740500258576811</v>
       </c>
       <c r="J45" t="n">
         <v>29207</v>
@@ -3522,26 +2928,13 @@
         <v>42.85095603614458</v>
       </c>
       <c r="O45" t="n">
-        <v>-2.677920487951808</v>
+        <v>-2.677920487951807</v>
       </c>
       <c r="P45" t="n">
         <v>480</v>
       </c>
       <c r="Q45" t="n">
         <v>44</v>
-      </c>
-      <c r="R45" t="n">
-        <v>3</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="46">
@@ -3563,7 +2956,7 @@
         <v>0.267218218527344</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2791977230829013</v>
+        <v>0.2791977230829014</v>
       </c>
       <c r="G46" t="n">
         <v>1745</v>
@@ -3597,20 +2990,6 @@
       </c>
       <c r="Q46" t="n">
         <v>45</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="47">
@@ -3629,10 +3008,10 @@
         <v>21</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2671068487828122</v>
+        <v>0.2671068487828123</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2864107414894767</v>
+        <v>0.2864107414894768</v>
       </c>
       <c r="G47" t="n">
         <v>3634</v>
@@ -3666,20 +3045,6 @@
       </c>
       <c r="Q47" t="n">
         <v>46</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="48">
@@ -3736,19 +3101,6 @@
       <c r="Q48" t="n">
         <v>47</v>
       </c>
-      <c r="R48" t="n">
-        <v>3</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3769,7 +3121,7 @@
         <v>0.2665283776815991</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2927397652522231</v>
+        <v>0.2927397652522232</v>
       </c>
       <c r="G49" t="n">
         <v>1676</v>
@@ -3778,7 +3130,7 @@
         <v>12.41265615146908</v>
       </c>
       <c r="I49" t="n">
-        <v>1.756206548892384</v>
+        <v>1.756206548892383</v>
       </c>
       <c r="J49" t="n">
         <v>1791</v>
@@ -3803,20 +3155,6 @@
       </c>
       <c r="Q49" t="n">
         <v>48</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="50">
@@ -3835,7 +3173,7 @@
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2660496889440157</v>
+        <v>0.2660496889440158</v>
       </c>
       <c r="F50" t="n">
         <v>0.2778515348217613</v>
@@ -3872,20 +3210,6 @@
       </c>
       <c r="Q50" t="n">
         <v>49</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="51">
@@ -3904,7 +3228,7 @@
         <v>186</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2658883647369944</v>
+        <v>0.2658883647369945</v>
       </c>
       <c r="F51" t="n">
         <v>0.3005120395760801</v>
@@ -3941,19 +3265,6 @@
       </c>
       <c r="Q51" t="n">
         <v>50</v>
-      </c>
-      <c r="R51" t="n">
-        <v>3</v>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="52">
@@ -4010,19 +3321,6 @@
       <c r="Q52" t="n">
         <v>51</v>
       </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4078,20 +3376,6 @@
       <c r="Q53" t="n">
         <v>52</v>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4109,10 +3393,10 @@
         <v>62</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2642453833336854</v>
+        <v>0.2642453833336855</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2945133054663711</v>
+        <v>0.2945133054663712</v>
       </c>
       <c r="G54" t="n">
         <v>8804</v>
@@ -4146,19 +3430,6 @@
       </c>
       <c r="Q54" t="n">
         <v>53</v>
-      </c>
-      <c r="R54" t="n">
-        <v>3</v>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="55">
@@ -4215,20 +3486,6 @@
       <c r="Q55" t="n">
         <v>54</v>
       </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4284,20 +3541,6 @@
       <c r="Q56" t="n">
         <v>55</v>
       </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4353,20 +3596,6 @@
       <c r="Q57" t="n">
         <v>56</v>
       </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4422,19 +3651,6 @@
       <c r="Q58" t="n">
         <v>57</v>
       </c>
-      <c r="R58" t="n">
-        <v>1</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4490,20 +3706,6 @@
       <c r="Q59" t="n">
         <v>58</v>
       </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4559,19 +3761,6 @@
       <c r="Q60" t="n">
         <v>59</v>
       </c>
-      <c r="R60" t="n">
-        <v>3</v>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4601,7 +3790,7 @@
         <v>8.024810093925742</v>
       </c>
       <c r="I61" t="n">
-        <v>1.698042052441506</v>
+        <v>1.698042052441507</v>
       </c>
       <c r="J61" t="n">
         <v>11687</v>
@@ -4626,20 +3815,6 @@
       </c>
       <c r="Q61" t="n">
         <v>60</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="62">
@@ -4661,7 +3836,7 @@
         <v>0.2594338939384877</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2806870560028687</v>
+        <v>0.2806870560028688</v>
       </c>
       <c r="G62" t="n">
         <v>4118</v>
@@ -4695,20 +3870,6 @@
       </c>
       <c r="Q62" t="n">
         <v>61</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="63">
@@ -4765,19 +3926,6 @@
       <c r="Q63" t="n">
         <v>62</v>
       </c>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4833,20 +3981,6 @@
       <c r="Q64" t="n">
         <v>63</v>
       </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4864,10 +3998,10 @@
         <v>74</v>
       </c>
       <c r="E65" t="n">
-        <v>0.2531958964058651</v>
+        <v>0.2531958964058652</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2781220238591695</v>
+        <v>0.2781220238591696</v>
       </c>
       <c r="G65" t="n">
         <v>11665</v>
@@ -4901,19 +4035,6 @@
       </c>
       <c r="Q65" t="n">
         <v>64</v>
-      </c>
-      <c r="R65" t="n">
-        <v>3</v>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="66">
@@ -4932,7 +4053,7 @@
         <v>81</v>
       </c>
       <c r="E66" t="n">
-        <v>0.2519216566113766</v>
+        <v>0.2519216566113767</v>
       </c>
       <c r="F66" t="n">
         <v>0.2751768598416108</v>
@@ -4969,20 +4090,6 @@
       </c>
       <c r="Q66" t="n">
         <v>65</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="67">
@@ -5039,19 +4146,6 @@
       <c r="Q67" t="n">
         <v>66</v>
       </c>
-      <c r="R67" t="n">
-        <v>3</v>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5069,7 +4163,7 @@
         <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2490578181632768</v>
+        <v>0.2490578181632769</v>
       </c>
       <c r="F68" t="n">
         <v>0.2610629061535713</v>
@@ -5106,20 +4200,6 @@
       </c>
       <c r="Q68" t="n">
         <v>67</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="69">
@@ -5138,7 +4218,7 @@
         <v>62</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2469358718357632</v>
+        <v>0.2469358718357633</v>
       </c>
       <c r="F69" t="n">
         <v>0.2696508491833992</v>
@@ -5175,19 +4255,6 @@
       </c>
       <c r="Q69" t="n">
         <v>68</v>
-      </c>
-      <c r="R69" t="n">
-        <v>3</v>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="70">
@@ -5206,7 +4273,7 @@
         <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>0.2460954433154153</v>
+        <v>0.2460954433154154</v>
       </c>
       <c r="F70" t="n">
         <v>0.2530160559083151</v>
@@ -5243,19 +4310,6 @@
       </c>
       <c r="Q70" t="n">
         <v>69</v>
-      </c>
-      <c r="R70" t="n">
-        <v>3</v>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="71">
@@ -5274,7 +4328,7 @@
         <v>9</v>
       </c>
       <c r="E71" t="n">
-        <v>0.2457610080753872</v>
+        <v>0.2457610080753873</v>
       </c>
       <c r="F71" t="n">
         <v>0.2692170950598729</v>
@@ -5311,19 +4365,6 @@
       </c>
       <c r="Q71" t="n">
         <v>70</v>
-      </c>
-      <c r="R71" t="n">
-        <v>3</v>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="72">
@@ -5345,7 +4386,7 @@
         <v>0.2439063639467793</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2536900371886313</v>
+        <v>0.2536900371886314</v>
       </c>
       <c r="G72" t="n">
         <v>1525</v>
@@ -5379,20 +4420,6 @@
       </c>
       <c r="Q72" t="n">
         <v>71</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="73">
@@ -5411,7 +4438,7 @@
         <v>62</v>
       </c>
       <c r="E73" t="n">
-        <v>0.2402350181414875</v>
+        <v>0.2402350181414876</v>
       </c>
       <c r="F73" t="n">
         <v>0.2700995782626665</v>
@@ -5420,7 +4447,7 @@
         <v>7089</v>
       </c>
       <c r="H73" t="n">
-        <v>9.193717876408224</v>
+        <v>9.193717876408225</v>
       </c>
       <c r="I73" t="n">
         <v>1.95751971269507</v>
@@ -5448,20 +4475,6 @@
       </c>
       <c r="Q73" t="n">
         <v>72</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="74">
@@ -5489,7 +4502,7 @@
         <v>2195</v>
       </c>
       <c r="H74" t="n">
-        <v>10.9660513745707</v>
+        <v>10.96605137457069</v>
       </c>
       <c r="I74" t="n">
         <v>1.742380730782222</v>
@@ -5517,20 +4530,6 @@
       </c>
       <c r="Q74" t="n">
         <v>73</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="75">
@@ -5549,7 +4548,7 @@
         <v>71</v>
       </c>
       <c r="E75" t="n">
-        <v>0.236974204220065</v>
+        <v>0.2369742042200651</v>
       </c>
       <c r="F75" t="n">
         <v>0.2851689009175338</v>
@@ -5561,7 +4560,7 @@
         <v>10.61183082925706</v>
       </c>
       <c r="I75" t="n">
-        <v>1.891663382201204</v>
+        <v>1.891663382201203</v>
       </c>
       <c r="J75" t="n">
         <v>9551</v>
@@ -5586,20 +4585,6 @@
       </c>
       <c r="Q75" t="n">
         <v>74</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="76">
@@ -5656,20 +4641,6 @@
       <c r="Q76" t="n">
         <v>75</v>
       </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5690,7 +4661,7 @@
         <v>0.236251118751374</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2409059178943451</v>
+        <v>0.2409059178943452</v>
       </c>
       <c r="G77" t="n">
         <v>1178</v>
@@ -5724,20 +4695,6 @@
       </c>
       <c r="Q77" t="n">
         <v>76</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="78">
@@ -5756,16 +4713,16 @@
         <v>108</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2354255000886918</v>
+        <v>0.2354255000886919</v>
       </c>
       <c r="F78" t="n">
-        <v>0.268093229925618</v>
+        <v>0.2680932299256181</v>
       </c>
       <c r="G78" t="n">
         <v>12311</v>
       </c>
       <c r="H78" t="n">
-        <v>9.107014779433385</v>
+        <v>9.107014779433383</v>
       </c>
       <c r="I78" t="n">
         <v>1.957443178092112</v>
@@ -5786,27 +4743,13 @@
         <v>38.87657487962964</v>
       </c>
       <c r="O78" t="n">
-        <v>-6.963507805555556</v>
+        <v>-6.963507805555555</v>
       </c>
       <c r="P78" t="n">
         <v>608</v>
       </c>
       <c r="Q78" t="n">
         <v>77</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="79">
@@ -5825,7 +4768,7 @@
         <v>34</v>
       </c>
       <c r="E79" t="n">
-        <v>0.2343558795306928</v>
+        <v>0.2343558795306929</v>
       </c>
       <c r="F79" t="n">
         <v>0.2598752619403884</v>
@@ -5862,20 +4805,6 @@
       </c>
       <c r="Q79" t="n">
         <v>78</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="80">
@@ -5932,19 +4861,6 @@
       <c r="Q80" t="n">
         <v>79</v>
       </c>
-      <c r="R80" t="n">
-        <v>3</v>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5971,7 +4887,7 @@
         <v>1549</v>
       </c>
       <c r="H81" t="n">
-        <v>3.683394567439637</v>
+        <v>3.683394567439636</v>
       </c>
       <c r="I81" t="n">
         <v>1.6986823196142</v>
@@ -5999,20 +4915,6 @@
       </c>
       <c r="Q81" t="n">
         <v>80</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="82">
@@ -6069,20 +4971,6 @@
       <c r="Q82" t="n">
         <v>81</v>
       </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6138,20 +5026,6 @@
       <c r="Q83" t="n">
         <v>82</v>
       </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6207,20 +5081,6 @@
       <c r="Q84" t="n">
         <v>83</v>
       </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6238,16 +5098,16 @@
         <v>41</v>
       </c>
       <c r="E85" t="n">
-        <v>0.2265130189469046</v>
+        <v>0.2265130189469047</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2455867832465681</v>
+        <v>0.2455867832465682</v>
       </c>
       <c r="G85" t="n">
         <v>4546</v>
       </c>
       <c r="H85" t="n">
-        <v>9.702953459517801</v>
+        <v>9.702953459517799</v>
       </c>
       <c r="I85" t="n">
         <v>1.945314501210929</v>
@@ -6275,20 +5135,6 @@
       </c>
       <c r="Q85" t="n">
         <v>84</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="86">
@@ -6307,10 +5153,10 @@
         <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2261139775717507</v>
+        <v>0.2261139775717508</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2307307993714181</v>
+        <v>0.2307307993714182</v>
       </c>
       <c r="G86" t="n">
         <v>616</v>
@@ -6344,20 +5190,6 @@
       </c>
       <c r="Q86" t="n">
         <v>85</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="87">
@@ -6376,7 +5208,7 @@
         <v>54</v>
       </c>
       <c r="E87" t="n">
-        <v>0.2237114862150721</v>
+        <v>0.2237114862150722</v>
       </c>
       <c r="F87" t="n">
         <v>0.2487326769172505</v>
@@ -6413,19 +5245,6 @@
       </c>
       <c r="Q87" t="n">
         <v>86</v>
-      </c>
-      <c r="R87" t="n">
-        <v>3</v>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="88">
@@ -6444,7 +5263,7 @@
         <v>106</v>
       </c>
       <c r="E88" t="n">
-        <v>0.2231065254634673</v>
+        <v>0.2231065254634674</v>
       </c>
       <c r="F88" t="n">
         <v>0.2475974916986188</v>
@@ -6481,19 +5300,6 @@
       </c>
       <c r="Q88" t="n">
         <v>87</v>
-      </c>
-      <c r="R88" t="n">
-        <v>3</v>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="89">
@@ -6550,20 +5356,6 @@
       <c r="Q89" t="n">
         <v>88</v>
       </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6619,19 +5411,6 @@
       <c r="Q90" t="n">
         <v>89</v>
       </c>
-      <c r="R90" t="n">
-        <v>1</v>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6658,7 +5437,7 @@
         <v>20201</v>
       </c>
       <c r="H91" t="n">
-        <v>12.93121152996034</v>
+        <v>12.93121152996033</v>
       </c>
       <c r="I91" t="n">
         <v>2.068184471263653</v>
@@ -6686,19 +5465,6 @@
       </c>
       <c r="Q91" t="n">
         <v>90</v>
-      </c>
-      <c r="R91" t="n">
-        <v>3</v>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="92">
@@ -6747,27 +5513,13 @@
         <v>41.05397163636363</v>
       </c>
       <c r="O92" t="n">
-        <v>-0.1372174545454545</v>
+        <v>-0.1372174545454546</v>
       </c>
       <c r="P92" t="n">
         <v>770</v>
       </c>
       <c r="Q92" t="n">
         <v>91</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="93">
@@ -6824,20 +5576,6 @@
       <c r="Q93" t="n">
         <v>92</v>
       </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6893,20 +5631,6 @@
       <c r="Q94" t="n">
         <v>93</v>
       </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6962,20 +5686,6 @@
       <c r="Q95" t="n">
         <v>94</v>
       </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6993,10 +5703,10 @@
         <v>11</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2113690068368506</v>
+        <v>0.2113690068368507</v>
       </c>
       <c r="F96" t="n">
-        <v>0.225290306028267</v>
+        <v>0.2252903060282671</v>
       </c>
       <c r="G96" t="n">
         <v>1554</v>
@@ -7023,27 +5733,13 @@
         <v>40.04939972727273</v>
       </c>
       <c r="O96" t="n">
-        <v>0.0538656363636363</v>
+        <v>0.05386563636363637</v>
       </c>
       <c r="P96" t="n">
         <v>845</v>
       </c>
       <c r="Q96" t="n">
         <v>95</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="97">
@@ -7062,7 +5758,7 @@
         <v>121</v>
       </c>
       <c r="E97" t="n">
-        <v>0.2108250831995348</v>
+        <v>0.2108250831995349</v>
       </c>
       <c r="F97" t="n">
         <v>0.2436379186157203</v>
@@ -7099,19 +5795,6 @@
       </c>
       <c r="Q97" t="n">
         <v>96</v>
-      </c>
-      <c r="R97" t="n">
-        <v>3</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="98">
@@ -7130,7 +5813,7 @@
         <v>36</v>
       </c>
       <c r="E98" t="n">
-        <v>0.2096047968588957</v>
+        <v>0.2096047968588958</v>
       </c>
       <c r="F98" t="n">
         <v>0.2448428587832888</v>
@@ -7167,20 +5850,6 @@
       </c>
       <c r="Q98" t="n">
         <v>97</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="99">
@@ -7229,27 +5898,13 @@
         <v>38.98999095614035</v>
       </c>
       <c r="O99" t="n">
-        <v>-1.862771228070176</v>
+        <v>-1.862771228070175</v>
       </c>
       <c r="P99" t="n">
         <v>879</v>
       </c>
       <c r="Q99" t="n">
         <v>98</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
       </c>
     </row>
     <row r="100">
@@ -7271,7 +5926,7 @@
         <v>0.2077701726035451</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2287241259315195</v>
+        <v>0.2287241259315196</v>
       </c>
       <c r="G100" t="n">
         <v>4573</v>
@@ -7305,19 +5960,6 @@
       </c>
       <c r="Q100" t="n">
         <v>99</v>
-      </c>
-      <c r="R100" t="n">
-        <v>3</v>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
     <row r="101">
@@ -7339,7 +5981,7 @@
         <v>0.2066810717600926</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2255429831798122</v>
+        <v>0.2255429831798123</v>
       </c>
       <c r="G101" t="n">
         <v>6418</v>
@@ -7373,19 +6015,6 @@
       </c>
       <c r="Q101" t="n">
         <v>100</v>
-      </c>
-      <c r="R101" t="n">
-        <v>3</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Estándar</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -7582,7 +6211,7 @@
         <v>40.41240833333333</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.888334666666665</v>
+        <v>-3.888334666666666</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -7659,7 +6288,7 @@
         <v>0.4867620595131572</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4969214161393099</v>
+        <v>0.49692141613931</v>
       </c>
       <c r="G5" t="n">
         <v>1446</v>
@@ -7711,7 +6340,7 @@
         <v>0.4710962657811085</v>
       </c>
       <c r="F6" t="n">
-        <v>0.49927529849953</v>
+        <v>0.4992752984995301</v>
       </c>
       <c r="G6" t="n">
         <v>5967</v>
@@ -7763,7 +6392,7 @@
         <v>0.4432404023831725</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4498010966345255</v>
+        <v>0.4498010966345256</v>
       </c>
       <c r="G7" t="n">
         <v>757</v>
@@ -7864,16 +6493,16 @@
         <v>49</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4086989257071955</v>
+        <v>0.4086989257071956</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4470889819533944</v>
+        <v>0.4470889819533945</v>
       </c>
       <c r="G9" t="n">
         <v>5571</v>
       </c>
       <c r="H9" t="n">
-        <v>6.056076162310792</v>
+        <v>6.056076162310791</v>
       </c>
       <c r="I9" t="n">
         <v>1.749123352635103</v>
@@ -7916,10 +6545,10 @@
         <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4068771970727667</v>
+        <v>0.4068771970727668</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4300106893861273</v>
+        <v>0.4300106893861274</v>
       </c>
       <c r="G10" t="n">
         <v>5434</v>
@@ -7968,10 +6597,10 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4053203527289862</v>
+        <v>0.4053203527289863</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4107867211907269</v>
+        <v>0.410786721190727</v>
       </c>
       <c r="G11" t="n">
         <v>584</v>
@@ -8020,10 +6649,10 @@
         <v>1068</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4014989650655829</v>
+        <v>0.401498965065583</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4691542693260114</v>
+        <v>0.4691542693260115</v>
       </c>
       <c r="G12" t="n">
         <v>186908</v>
@@ -8231,7 +6860,7 @@
         <v>0.3941226268878416</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4021365394814555</v>
+        <v>0.4021365394814556</v>
       </c>
       <c r="G16" t="n">
         <v>945</v>
@@ -8439,13 +7068,13 @@
         <v>0.3863138269178498</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4112600700301836</v>
+        <v>0.4112600700301837</v>
       </c>
       <c r="G20" t="n">
         <v>1737</v>
       </c>
       <c r="H20" t="n">
-        <v>9.035307829716205</v>
+        <v>9.035307829716203</v>
       </c>
       <c r="I20" t="n">
         <v>1.435204762679754</v>
@@ -8699,7 +7328,7 @@
         <v>0.3802304785351845</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3845362052887934</v>
+        <v>0.3845362052887935</v>
       </c>
       <c r="G25" t="n">
         <v>189</v>
@@ -8748,7 +7377,7 @@
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3789363084635658</v>
+        <v>0.3789363084635659</v>
       </c>
       <c r="F26" t="n">
         <v>0.3847681441172223</v>
@@ -8852,7 +7481,7 @@
         <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3778055629095216</v>
+        <v>0.3778055629095217</v>
       </c>
       <c r="F28" t="n">
         <v>0.4263013193234038</v>
@@ -9060,10 +7689,10 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3755072893225525</v>
+        <v>0.3755072893225526</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3755072893225525</v>
+        <v>0.3755072893225526</v>
       </c>
       <c r="G32" t="n">
         <v>28</v>
@@ -9167,7 +7796,7 @@
         <v>0.3744210777512569</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3905156198070499</v>
+        <v>0.39051561980705</v>
       </c>
       <c r="G34" t="n">
         <v>5846</v>
@@ -9332,7 +7961,7 @@
         <v>10.7536513216607</v>
       </c>
       <c r="I37" t="n">
-        <v>1.662399414212096</v>
+        <v>1.662399414212095</v>
       </c>
       <c r="J37" t="n">
         <v>19881</v>
@@ -9424,7 +8053,7 @@
         <v>50</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3726222532493441</v>
+        <v>0.3726222532493442</v>
       </c>
       <c r="F39" t="n">
         <v>0.3971098558493839</v>
@@ -9479,7 +8108,7 @@
         <v>0.3725854381252511</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3861017794790248</v>
+        <v>0.3861017794790249</v>
       </c>
       <c r="G40" t="n">
         <v>609</v>
@@ -9644,7 +8273,7 @@
         <v>10.46124360510631</v>
       </c>
       <c r="I43" t="n">
-        <v>1.831254807970086</v>
+        <v>1.831254807970087</v>
       </c>
       <c r="J43" t="n">
         <v>7910</v>
@@ -9684,7 +8313,7 @@
         <v>25</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3688767999304704</v>
+        <v>0.3688767999304705</v>
       </c>
       <c r="F44" t="n">
         <v>0.3985459396348998</v>
@@ -9739,7 +8368,7 @@
         <v>0.3686241903370875</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4095360414630088</v>
+        <v>0.4095360414630089</v>
       </c>
       <c r="G45" t="n">
         <v>19697</v>
@@ -9895,7 +8524,7 @@
         <v>0.3675421361933909</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3783324886072616</v>
+        <v>0.3783324886072617</v>
       </c>
       <c r="G48" t="n">
         <v>3547</v>
@@ -9947,7 +8576,7 @@
         <v>0.3675286005892998</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3913350148843565</v>
+        <v>0.3913350148843566</v>
       </c>
       <c r="G49" t="n">
         <v>3431</v>
@@ -10100,7 +8729,7 @@
         <v>137</v>
       </c>
       <c r="E52" t="n">
-        <v>0.367231180101318</v>
+        <v>0.3672311801013181</v>
       </c>
       <c r="F52" t="n">
         <v>0.3905275516797807</v>
@@ -10152,7 +8781,7 @@
         <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3663356949889222</v>
+        <v>0.3663356949889223</v>
       </c>
       <c r="F53" t="n">
         <v>0.3696223762747567</v>
@@ -10311,7 +8940,7 @@
         <v>0.3631944759612847</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3893158339717469</v>
+        <v>0.389315833971747</v>
       </c>
       <c r="G56" t="n">
         <v>19899</v>
@@ -10519,7 +9148,7 @@
         <v>0.3616028761387864</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4008387889794589</v>
+        <v>0.400838788979459</v>
       </c>
       <c r="G60" t="n">
         <v>11063</v>
@@ -10568,7 +9197,7 @@
         <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3614332135262696</v>
+        <v>0.3614332135262697</v>
       </c>
       <c r="F61" t="n">
         <v>0.3768652117849108</v>
@@ -10727,7 +9356,7 @@
         <v>0.3588465022656704</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3848568061913884</v>
+        <v>0.3848568061913885</v>
       </c>
       <c r="G64" t="n">
         <v>2915</v>
@@ -10828,10 +9457,10 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3575489017906268</v>
+        <v>0.3575489017906269</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3575489017906268</v>
+        <v>0.3575489017906269</v>
       </c>
       <c r="G66" t="n">
         <v>56</v>
@@ -10962,7 +9591,7 @@
         <v>40.68065216666667</v>
       </c>
       <c r="O68" t="n">
-        <v>-3.622887166666666</v>
+        <v>-3.622887166666667</v>
       </c>
       <c r="P68" t="n">
         <v>67</v>
@@ -10984,10 +9613,10 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3546010877501925</v>
+        <v>0.3546010877501926</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3546010877501925</v>
+        <v>0.3546010877501926</v>
       </c>
       <c r="G69" t="n">
         <v>11</v>
@@ -11088,10 +9717,10 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3536689480891541</v>
+        <v>0.3536689480891542</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3536689480891541</v>
+        <v>0.3536689480891542</v>
       </c>
       <c r="G71" t="n">
         <v>145</v>
@@ -11452,10 +10081,10 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0.349319616788824</v>
+        <v>0.3493196167888241</v>
       </c>
       <c r="F78" t="n">
-        <v>0.349319616788824</v>
+        <v>0.3493196167888241</v>
       </c>
       <c r="G78" t="n">
         <v>64</v>
@@ -11504,7 +10133,7 @@
         <v>11</v>
       </c>
       <c r="E79" t="n">
-        <v>0.3483150878372811</v>
+        <v>0.3483150878372812</v>
       </c>
       <c r="F79" t="n">
         <v>0.3649002396986485</v>
@@ -12284,10 +10913,10 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3376984075841854</v>
+        <v>0.3376984075841855</v>
       </c>
       <c r="F94" t="n">
-        <v>0.3376984075841854</v>
+        <v>0.3376984075841855</v>
       </c>
       <c r="G94" t="n">
         <v>148</v>
@@ -12339,7 +10968,7 @@
         <v>0.3376499331680249</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3495176367790903</v>
+        <v>0.3495176367790904</v>
       </c>
       <c r="G95" t="n">
         <v>864</v>
@@ -12391,7 +11020,7 @@
         <v>0.3364881867936597</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3662772494496273</v>
+        <v>0.3662772494496274</v>
       </c>
       <c r="G96" t="n">
         <v>5554</v>
@@ -12400,7 +11029,7 @@
         <v>4.491093050992502</v>
       </c>
       <c r="I96" t="n">
-        <v>1.762816364595052</v>
+        <v>1.762816364595053</v>
       </c>
       <c r="J96" t="n">
         <v>11419</v>
@@ -12443,13 +11072,13 @@
         <v>0.3340247320393086</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3445166640741512</v>
+        <v>0.3445166640741513</v>
       </c>
       <c r="G97" t="n">
         <v>2049</v>
       </c>
       <c r="H97" t="n">
-        <v>9.830101557888099</v>
+        <v>9.830101557888101</v>
       </c>
       <c r="I97" t="n">
         <v>1.672165547340094</v>
@@ -12492,10 +11121,10 @@
         <v>37</v>
       </c>
       <c r="E98" t="n">
-        <v>0.3327368571542139</v>
+        <v>0.332736857154214</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3479096819484122</v>
+        <v>0.3479096819484123</v>
       </c>
       <c r="G98" t="n">
         <v>4782</v>
@@ -12544,7 +11173,7 @@
         <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>0.3310918196934468</v>
+        <v>0.3310918196934469</v>
       </c>
       <c r="F99" t="n">
         <v>0.3349759255503766</v>
@@ -12700,7 +11329,7 @@
         <v>5</v>
       </c>
       <c r="E102" t="n">
-        <v>0.3299524751087357</v>
+        <v>0.3299524751087358</v>
       </c>
       <c r="F102" t="n">
         <v>0.3468988428215399</v>
@@ -12856,7 +11485,7 @@
         <v>4</v>
       </c>
       <c r="E105" t="n">
-        <v>0.3277797059819812</v>
+        <v>0.3277797059819813</v>
       </c>
       <c r="F105" t="n">
         <v>0.3293011764783866</v>
@@ -13168,7 +11797,7 @@
         <v>2</v>
       </c>
       <c r="E111" t="n">
-        <v>0.325301118340451</v>
+        <v>0.3253011183404511</v>
       </c>
       <c r="F111" t="n">
         <v>0.3256734028582429</v>
@@ -13195,7 +11824,7 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>41.646723</v>
+        <v>41.64672299999999</v>
       </c>
       <c r="O111" t="n">
         <v>2.2246395</v>
@@ -13376,7 +12005,7 @@
         <v>5</v>
       </c>
       <c r="E115" t="n">
-        <v>0.3233477543861432</v>
+        <v>0.3233477543861433</v>
       </c>
       <c r="F115" t="n">
         <v>0.329675831205399</v>
@@ -13431,7 +12060,7 @@
         <v>0.3231208336477707</v>
       </c>
       <c r="F116" t="n">
-        <v>0.3418037454656908</v>
+        <v>0.3418037454656909</v>
       </c>
       <c r="G116" t="n">
         <v>2659</v>
@@ -13743,7 +12372,7 @@
         <v>0.321849777773098</v>
       </c>
       <c r="F122" t="n">
-        <v>0.3300926887700592</v>
+        <v>0.3300926887700593</v>
       </c>
       <c r="G122" t="n">
         <v>1061</v>
@@ -13899,7 +12528,7 @@
         <v>0.3212573901654088</v>
       </c>
       <c r="F125" t="n">
-        <v>0.330040439525408</v>
+        <v>0.3300404395254081</v>
       </c>
       <c r="G125" t="n">
         <v>360</v>
@@ -13960,7 +12589,7 @@
         <v>6.602240457057126</v>
       </c>
       <c r="I126" t="n">
-        <v>1.787901702412741</v>
+        <v>1.787901702412742</v>
       </c>
       <c r="J126" t="n">
         <v>4009</v>
@@ -14208,10 +12837,10 @@
         <v>8</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3199155144915901</v>
+        <v>0.3199155144915902</v>
       </c>
       <c r="F131" t="n">
-        <v>0.3409921410794422</v>
+        <v>0.3409921410794423</v>
       </c>
       <c r="G131" t="n">
         <v>1059</v>
@@ -14260,7 +12889,7 @@
         <v>4</v>
       </c>
       <c r="E132" t="n">
-        <v>0.3190806767152755</v>
+        <v>0.3190806767152756</v>
       </c>
       <c r="F132" t="n">
         <v>0.3262425248479662</v>
@@ -14419,7 +13048,7 @@
         <v>0.3184589257421322</v>
       </c>
       <c r="F135" t="n">
-        <v>0.3266067559199054</v>
+        <v>0.3266067559199055</v>
       </c>
       <c r="G135" t="n">
         <v>794</v>
@@ -14572,7 +13201,7 @@
         <v>4</v>
       </c>
       <c r="E138" t="n">
-        <v>0.3179933298139978</v>
+        <v>0.3179933298139979</v>
       </c>
       <c r="F138" t="n">
         <v>0.3258657974543523</v>
@@ -14832,7 +13461,7 @@
         <v>144</v>
       </c>
       <c r="E143" t="n">
-        <v>0.3170504917120006</v>
+        <v>0.3170504917120007</v>
       </c>
       <c r="F143" t="n">
         <v>0.3414396819797916</v>
@@ -14841,7 +13470,7 @@
         <v>23273</v>
       </c>
       <c r="H143" t="n">
-        <v>13.06230010984514</v>
+        <v>13.06230010984515</v>
       </c>
       <c r="I143" t="n">
         <v>2.182128026570019</v>
@@ -15040,10 +13669,10 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3158925388378741</v>
+        <v>0.3158925388378742</v>
       </c>
       <c r="F147" t="n">
-        <v>0.3158925388378741</v>
+        <v>0.3158925388378742</v>
       </c>
       <c r="G147" t="n">
         <v>29</v>
@@ -15104,7 +13733,7 @@
         <v>9.80337986995522</v>
       </c>
       <c r="I148" t="n">
-        <v>1.655468035167284</v>
+        <v>1.655468035167283</v>
       </c>
       <c r="J148" t="n">
         <v>699</v>
@@ -15300,7 +13929,7 @@
         <v>4</v>
       </c>
       <c r="E152" t="n">
-        <v>0.3149801210389469</v>
+        <v>0.314980121038947</v>
       </c>
       <c r="F152" t="n">
         <v>0.3151902967306422</v>
@@ -15404,10 +14033,10 @@
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>0.3147864508913396</v>
+        <v>0.3147864508913397</v>
       </c>
       <c r="F154" t="n">
-        <v>0.3147864508913396</v>
+        <v>0.3147864508913397</v>
       </c>
       <c r="G154" t="n">
         <v>293</v>
@@ -15456,7 +14085,7 @@
         <v>10</v>
       </c>
       <c r="E155" t="n">
-        <v>0.3147858854043286</v>
+        <v>0.3147858854043287</v>
       </c>
       <c r="F155" t="n">
         <v>0.3265598551047191</v>
@@ -15468,7 +14097,7 @@
         <v>8.025755109182287</v>
       </c>
       <c r="I155" t="n">
-        <v>1.834735224426881</v>
+        <v>1.834735224426882</v>
       </c>
       <c r="J155" t="n">
         <v>1640</v>
@@ -15612,16 +14241,16 @@
         <v>2</v>
       </c>
       <c r="E158" t="n">
-        <v>0.3143026413571645</v>
+        <v>0.3143026413571646</v>
       </c>
       <c r="F158" t="n">
-        <v>0.3144266781269272</v>
+        <v>0.3144266781269273</v>
       </c>
       <c r="G158" t="n">
         <v>439</v>
       </c>
       <c r="H158" t="n">
-        <v>9.685651153807749</v>
+        <v>9.685651153807747</v>
       </c>
       <c r="I158" t="n">
         <v>1.844155844155844</v>
@@ -15664,7 +14293,7 @@
         <v>8</v>
       </c>
       <c r="E159" t="n">
-        <v>0.3142327266844368</v>
+        <v>0.3142327266844369</v>
       </c>
       <c r="F159" t="n">
         <v>0.3222712100282858</v>
@@ -15771,7 +14400,7 @@
         <v>0.3138627977557403</v>
       </c>
       <c r="F161" t="n">
-        <v>0.3301154830298923</v>
+        <v>0.3301154830298924</v>
       </c>
       <c r="G161" t="n">
         <v>4252</v>
@@ -15872,10 +14501,10 @@
         <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>0.3127524134188348</v>
+        <v>0.3127524134188349</v>
       </c>
       <c r="F163" t="n">
-        <v>0.3127524134188348</v>
+        <v>0.3127524134188349</v>
       </c>
       <c r="G163" t="n">
         <v>67</v>
@@ -15976,10 +14605,10 @@
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>0.3125775015351021</v>
+        <v>0.3125775015351022</v>
       </c>
       <c r="F165" t="n">
-        <v>0.3125775015351021</v>
+        <v>0.3125775015351022</v>
       </c>
       <c r="G165" t="n">
         <v>74</v>
@@ -16080,7 +14709,7 @@
         <v>5</v>
       </c>
       <c r="E167" t="n">
-        <v>0.3124312239299557</v>
+        <v>0.3124312239299558</v>
       </c>
       <c r="F167" t="n">
         <v>0.3200643871399932</v>
@@ -16288,7 +14917,7 @@
         <v>9</v>
       </c>
       <c r="E171" t="n">
-        <v>0.3115191164819182</v>
+        <v>0.3115191164819183</v>
       </c>
       <c r="F171" t="n">
         <v>0.3230307086112208</v>
@@ -16352,7 +14981,7 @@
         <v>13.05752970235189</v>
       </c>
       <c r="I172" t="n">
-        <v>1.703760406389884</v>
+        <v>1.703760406389883</v>
       </c>
       <c r="J172" t="n">
         <v>642</v>
@@ -16395,13 +15024,13 @@
         <v>0.3113486862202973</v>
       </c>
       <c r="F173" t="n">
-        <v>0.3128284899086997</v>
+        <v>0.3128284899086998</v>
       </c>
       <c r="G173" t="n">
         <v>332</v>
       </c>
       <c r="H173" t="n">
-        <v>9.317843498537416</v>
+        <v>9.317843498537417</v>
       </c>
       <c r="I173" t="n">
         <v>1.487108013937282</v>
@@ -16444,7 +15073,7 @@
         <v>10</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3113410040294039</v>
+        <v>0.311341004029404</v>
       </c>
       <c r="F174" t="n">
         <v>0.3253630857885889</v>
@@ -16499,7 +15128,7 @@
         <v>0.3111352224903344</v>
       </c>
       <c r="F175" t="n">
-        <v>0.3168277328098989</v>
+        <v>0.316827732809899</v>
       </c>
       <c r="G175" t="n">
         <v>740</v>
@@ -16600,10 +15229,10 @@
         <v>14</v>
       </c>
       <c r="E177" t="n">
-        <v>0.3108887317261486</v>
+        <v>0.3108887317261487</v>
       </c>
       <c r="F177" t="n">
-        <v>0.3331337955509342</v>
+        <v>0.3331337955509343</v>
       </c>
       <c r="G177" t="n">
         <v>1880</v>
@@ -16756,7 +15385,7 @@
         <v>8</v>
       </c>
       <c r="E180" t="n">
-        <v>0.3102699655954429</v>
+        <v>0.310269965595443</v>
       </c>
       <c r="F180" t="n">
         <v>0.326517336397332</v>
@@ -16820,7 +15449,7 @@
         <v>7.098020391957707</v>
       </c>
       <c r="I181" t="n">
-        <v>1.584300132050556</v>
+        <v>1.584300132050557</v>
       </c>
       <c r="J181" t="n">
         <v>557</v>
@@ -16964,10 +15593,10 @@
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>0.3094031871891481</v>
+        <v>0.3094031871891482</v>
       </c>
       <c r="F184" t="n">
-        <v>0.3094031871891481</v>
+        <v>0.3094031871891482</v>
       </c>
       <c r="G184" t="n">
         <v>18</v>
@@ -17025,7 +15654,7 @@
         <v>453</v>
       </c>
       <c r="H185" t="n">
-        <v>7.420144885828749</v>
+        <v>7.42014488582875</v>
       </c>
       <c r="I185" t="n">
         <v>1.744852941176471</v>
@@ -17068,7 +15697,7 @@
         <v>4</v>
       </c>
       <c r="E186" t="n">
-        <v>0.3084172705685892</v>
+        <v>0.3084172705685893</v>
       </c>
       <c r="F186" t="n">
         <v>0.3105994168096773</v>
@@ -17380,7 +16009,7 @@
         <v>5</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3074962096071651</v>
+        <v>0.3074962096071652</v>
       </c>
       <c r="F192" t="n">
         <v>0.3118389468512351</v>
@@ -17462,7 +16091,7 @@
         <v>39.67150431707317</v>
       </c>
       <c r="O193" t="n">
-        <v>-0.2472086585365853</v>
+        <v>-0.2472086585365854</v>
       </c>
       <c r="P193" t="n">
         <v>192</v>
@@ -17484,10 +16113,10 @@
         <v>1</v>
       </c>
       <c r="E194" t="n">
-        <v>0.3073286646810689</v>
+        <v>0.307328664681069</v>
       </c>
       <c r="F194" t="n">
-        <v>0.3073286646810689</v>
+        <v>0.307328664681069</v>
       </c>
       <c r="G194" t="n">
         <v>186</v>
@@ -17753,7 +16382,7 @@
         <v>1222</v>
       </c>
       <c r="H199" t="n">
-        <v>7.865038304036035</v>
+        <v>7.865038304036037</v>
       </c>
       <c r="I199" t="n">
         <v>1.461013641648754</v>
@@ -17900,10 +16529,10 @@
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3059413261753937</v>
+        <v>0.3059413261753938</v>
       </c>
       <c r="F202" t="n">
-        <v>0.3059413261753937</v>
+        <v>0.3059413261753938</v>
       </c>
       <c r="G202" t="n">
         <v>67</v>
@@ -17961,7 +16590,7 @@
         <v>285</v>
       </c>
       <c r="H203" t="n">
-        <v>9.127212594191391</v>
+        <v>9.127212594191393</v>
       </c>
       <c r="I203" t="n">
         <v>1.588806660499537</v>
@@ -18212,7 +16841,7 @@
         <v>16</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3055225565063785</v>
+        <v>0.3055225565063786</v>
       </c>
       <c r="F208" t="n">
         <v>0.3150184960643478</v>
@@ -18264,10 +16893,10 @@
         <v>9</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3053546960393248</v>
+        <v>0.3053546960393249</v>
       </c>
       <c r="F209" t="n">
-        <v>0.317151336416355</v>
+        <v>0.3171513364163551</v>
       </c>
       <c r="G209" t="n">
         <v>1800</v>
@@ -18325,7 +16954,7 @@
         <v>1372</v>
       </c>
       <c r="H210" t="n">
-        <v>9.689084092686649</v>
+        <v>9.689084092686647</v>
       </c>
       <c r="I210" t="n">
         <v>1.876049117562184</v>
@@ -18423,7 +17052,7 @@
         <v>0.3051023166073145</v>
       </c>
       <c r="F212" t="n">
-        <v>0.3100541120269259</v>
+        <v>0.310054112026926</v>
       </c>
       <c r="G212" t="n">
         <v>847</v>
@@ -18732,7 +17361,7 @@
         <v>2</v>
       </c>
       <c r="E218" t="n">
-        <v>0.3042287716929572</v>
+        <v>0.3042287716929573</v>
       </c>
       <c r="F218" t="n">
         <v>0.3081216125806609</v>
@@ -18848,7 +17477,7 @@
         <v>14.05672251361634</v>
       </c>
       <c r="I220" t="n">
-        <v>1.82621140555351</v>
+        <v>1.826211405553511</v>
       </c>
       <c r="J220" t="n">
         <v>842</v>
@@ -19209,7 +17838,7 @@
         <v>265</v>
       </c>
       <c r="H227" t="n">
-        <v>10.93152762946478</v>
+        <v>10.93152762946477</v>
       </c>
       <c r="I227" t="n">
         <v>1.946949602122016</v>
@@ -19304,7 +17933,7 @@
         <v>2</v>
       </c>
       <c r="E229" t="n">
-        <v>0.3028753776721233</v>
+        <v>0.3028753776721234</v>
       </c>
       <c r="F229" t="n">
         <v>0.3083094336242654</v>
@@ -19331,7 +17960,7 @@
         <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>41.5001935</v>
+        <v>41.50019349999999</v>
       </c>
       <c r="O229" t="n">
         <v>1.8107835</v>
@@ -19512,7 +18141,7 @@
         <v>13</v>
       </c>
       <c r="E233" t="n">
-        <v>0.3020496236136051</v>
+        <v>0.3020496236136052</v>
       </c>
       <c r="F233" t="n">
         <v>0.3424089031161846</v>
@@ -19542,7 +18171,7 @@
         <v>38.40051353846154</v>
       </c>
       <c r="O233" t="n">
-        <v>-0.4339552307692307</v>
+        <v>-0.4339552307692308</v>
       </c>
       <c r="P233" t="n">
         <v>232</v>
@@ -19723,7 +18352,7 @@
         <v>0.3015859678611488</v>
       </c>
       <c r="F237" t="n">
-        <v>0.3325271833683438</v>
+        <v>0.3325271833683439</v>
       </c>
       <c r="G237" t="n">
         <v>45720</v>
@@ -19732,7 +18361,7 @@
         <v>13.70222885208217</v>
       </c>
       <c r="I237" t="n">
-        <v>2.18702816193344</v>
+        <v>2.187028161933439</v>
       </c>
       <c r="J237" t="n">
         <v>40724</v>
@@ -19775,7 +18404,7 @@
         <v>0.3014766765390694</v>
       </c>
       <c r="F238" t="n">
-        <v>0.3048129892783426</v>
+        <v>0.3048129892783427</v>
       </c>
       <c r="G238" t="n">
         <v>768</v>
@@ -19885,7 +18514,7 @@
         <v>597</v>
       </c>
       <c r="H240" t="n">
-        <v>9.275179886400499</v>
+        <v>9.275179886400501</v>
       </c>
       <c r="I240" t="n">
         <v>2.012082228116711</v>
@@ -19931,7 +18560,7 @@
         <v>0.3010972378526791</v>
       </c>
       <c r="F241" t="n">
-        <v>0.3075026150379398</v>
+        <v>0.3075026150379399</v>
       </c>
       <c r="G241" t="n">
         <v>338</v>
@@ -19940,7 +18569,7 @@
         <v>6.155503853201426</v>
       </c>
       <c r="I241" t="n">
-        <v>1.777033492822966</v>
+        <v>1.777033492822967</v>
       </c>
       <c r="J241" t="n">
         <v>503</v>
@@ -20035,7 +18664,7 @@
         <v>0.3010109738600424</v>
       </c>
       <c r="F243" t="n">
-        <v>0.3053968809971414</v>
+        <v>0.3053968809971415</v>
       </c>
       <c r="G243" t="n">
         <v>306</v>
@@ -20044,7 +18673,7 @@
         <v>10.1736516433682</v>
       </c>
       <c r="I243" t="n">
-        <v>1.558938746438746</v>
+        <v>1.558938746438747</v>
       </c>
       <c r="J243" t="n">
         <v>341</v>
@@ -20136,7 +18765,7 @@
         <v>5</v>
       </c>
       <c r="E245" t="n">
-        <v>0.3008335829395896</v>
+        <v>0.3008335829395897</v>
       </c>
       <c r="F245" t="n">
         <v>0.3109777437168491</v>
@@ -20188,10 +18817,10 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>0.3005956271804438</v>
+        <v>0.3005956271804439</v>
       </c>
       <c r="F246" t="n">
-        <v>0.3005956271804438</v>
+        <v>0.3005956271804439</v>
       </c>
       <c r="G246" t="n">
         <v>34</v>
@@ -20295,7 +18924,7 @@
         <v>0.3004339173566021</v>
       </c>
       <c r="F248" t="n">
-        <v>0.3034816388862071</v>
+        <v>0.3034816388862072</v>
       </c>
       <c r="G248" t="n">
         <v>1046</v>
@@ -20616,7 +19245,7 @@
         <v>13.96103243382594</v>
       </c>
       <c r="I254" t="n">
-        <v>1.898077010938698</v>
+        <v>1.898077010938699</v>
       </c>
       <c r="J254" t="n">
         <v>645</v>
@@ -20656,10 +19285,10 @@
         <v>1</v>
       </c>
       <c r="E255" t="n">
-        <v>0.2999895686998179</v>
+        <v>0.299989568699818</v>
       </c>
       <c r="F255" t="n">
-        <v>0.2999895686998179</v>
+        <v>0.299989568699818</v>
       </c>
       <c r="G255" t="n">
         <v>38</v>
@@ -20708,10 +19337,10 @@
         <v>1</v>
       </c>
       <c r="E256" t="n">
-        <v>0.2999745756237374</v>
+        <v>0.2999745756237375</v>
       </c>
       <c r="F256" t="n">
-        <v>0.2999745756237374</v>
+        <v>0.2999745756237375</v>
       </c>
       <c r="G256" t="n">
         <v>198</v>
@@ -20760,10 +19389,10 @@
         <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>0.2999593631501412</v>
+        <v>0.2999593631501413</v>
       </c>
       <c r="F257" t="n">
-        <v>0.2999593631501412</v>
+        <v>0.2999593631501413</v>
       </c>
       <c r="G257" t="n">
         <v>86</v>
@@ -20824,7 +19453,7 @@
         <v>10.00600764545793</v>
       </c>
       <c r="I258" t="n">
-        <v>1.890317567736922</v>
+        <v>1.890317567736923</v>
       </c>
       <c r="J258" t="n">
         <v>334</v>
@@ -21124,10 +19753,10 @@
         <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0.2994252526049349</v>
+        <v>0.299425252604935</v>
       </c>
       <c r="F264" t="n">
-        <v>0.2994252526049349</v>
+        <v>0.299425252604935</v>
       </c>
       <c r="G264" t="n">
         <v>104</v>
@@ -21176,7 +19805,7 @@
         <v>4</v>
       </c>
       <c r="E265" t="n">
-        <v>0.2994201415730971</v>
+        <v>0.2994201415730972</v>
       </c>
       <c r="F265" t="n">
         <v>0.3047975616689427</v>
@@ -21237,7 +19866,7 @@
         <v>2506</v>
       </c>
       <c r="H266" t="n">
-        <v>7.910923727941268</v>
+        <v>7.910923727941269</v>
       </c>
       <c r="I266" t="n">
         <v>1.738632581223976</v>
@@ -21332,10 +19961,10 @@
         <v>2</v>
       </c>
       <c r="E268" t="n">
-        <v>0.2988736239301859</v>
+        <v>0.298873623930186</v>
       </c>
       <c r="F268" t="n">
-        <v>0.3009210307859999</v>
+        <v>0.300921030786</v>
       </c>
       <c r="G268" t="n">
         <v>229</v>
@@ -21592,10 +20221,10 @@
         <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>0.2985372120749164</v>
+        <v>0.2985372120749165</v>
       </c>
       <c r="F273" t="n">
-        <v>0.2985372120749164</v>
+        <v>0.2985372120749165</v>
       </c>
       <c r="G273" t="n">
         <v>123</v>
@@ -21674,7 +20303,7 @@
         <v>39.53594933333333</v>
       </c>
       <c r="O274" t="n">
-        <v>-0.4131933333333333</v>
+        <v>-0.4131933333333334</v>
       </c>
       <c r="P274" t="n">
         <v>273</v>
@@ -21748,7 +20377,7 @@
         <v>40</v>
       </c>
       <c r="E276" t="n">
-        <v>0.2982863808715342</v>
+        <v>0.2982863808715343</v>
       </c>
       <c r="F276" t="n">
         <v>0.3176604317453909</v>
@@ -21760,7 +20389,7 @@
         <v>8.953676983482755</v>
       </c>
       <c r="I276" t="n">
-        <v>1.8141777356406</v>
+        <v>1.814177735640599</v>
       </c>
       <c r="J276" t="n">
         <v>7299</v>
@@ -21852,7 +20481,7 @@
         <v>3</v>
       </c>
       <c r="E278" t="n">
-        <v>0.2982632904784539</v>
+        <v>0.298263290478454</v>
       </c>
       <c r="F278" t="n">
         <v>0.3088758220598595</v>
@@ -21907,7 +20536,7 @@
         <v>0.298232326750708</v>
       </c>
       <c r="F279" t="n">
-        <v>0.3060897249386431</v>
+        <v>0.3060897249386432</v>
       </c>
       <c r="G279" t="n">
         <v>453</v>
@@ -21983,7 +20612,7 @@
         <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>41.62632163636364</v>
+        <v>41.62632163636363</v>
       </c>
       <c r="O280" t="n">
         <v>2.299966</v>
@@ -22063,7 +20692,7 @@
         <v>0.2980211804196554</v>
       </c>
       <c r="F282" t="n">
-        <v>0.3208067241669218</v>
+        <v>0.3208067241669219</v>
       </c>
       <c r="G282" t="n">
         <v>6378</v>
@@ -22112,7 +20741,7 @@
         <v>20</v>
       </c>
       <c r="E283" t="n">
-        <v>0.2977528970867198</v>
+        <v>0.2977528970867199</v>
       </c>
       <c r="F283" t="n">
         <v>0.3135713933168563</v>
@@ -22219,7 +20848,7 @@
         <v>0.2974296329775986</v>
       </c>
       <c r="F285" t="n">
-        <v>0.3250105481455342</v>
+        <v>0.3250105481455343</v>
       </c>
       <c r="G285" t="n">
         <v>1619</v>
@@ -22372,10 +21001,10 @@
         <v>1</v>
       </c>
       <c r="E288" t="n">
-        <v>0.2969372806868185</v>
+        <v>0.2969372806868186</v>
       </c>
       <c r="F288" t="n">
-        <v>0.2969372806868185</v>
+        <v>0.2969372806868186</v>
       </c>
       <c r="G288" t="n">
         <v>321</v>
@@ -22424,7 +21053,7 @@
         <v>16</v>
       </c>
       <c r="E289" t="n">
-        <v>0.2966431839630812</v>
+        <v>0.2966431839630813</v>
       </c>
       <c r="F289" t="n">
         <v>0.3108903661453434</v>
@@ -22479,7 +21108,7 @@
         <v>0.2963707084819222</v>
       </c>
       <c r="F290" t="n">
-        <v>0.3068268116218099</v>
+        <v>0.30682681162181</v>
       </c>
       <c r="G290" t="n">
         <v>2320</v>
@@ -22583,7 +21212,7 @@
         <v>0.2963469193921627</v>
       </c>
       <c r="F292" t="n">
-        <v>0.3005050269085232</v>
+        <v>0.3005050269085233</v>
       </c>
       <c r="G292" t="n">
         <v>486</v>
@@ -22632,10 +21261,10 @@
         <v>4</v>
       </c>
       <c r="E293" t="n">
-        <v>0.2962779943230161</v>
+        <v>0.2962779943230162</v>
       </c>
       <c r="F293" t="n">
-        <v>0.3039636524920664</v>
+        <v>0.3039636524920665</v>
       </c>
       <c r="G293" t="n">
         <v>544</v>
@@ -22840,7 +21469,7 @@
         <v>2</v>
       </c>
       <c r="E297" t="n">
-        <v>0.2954116924847842</v>
+        <v>0.2954116924847843</v>
       </c>
       <c r="F297" t="n">
         <v>0.3001864796726731</v>
@@ -22999,7 +21628,7 @@
         <v>0.2951935003511251</v>
       </c>
       <c r="F300" t="n">
-        <v>0.3078604466924985</v>
+        <v>0.3078604466924986</v>
       </c>
       <c r="G300" t="n">
         <v>2980</v>
@@ -23048,10 +21677,10 @@
         <v>14</v>
       </c>
       <c r="E301" t="n">
-        <v>0.2949629010599274</v>
+        <v>0.2949629010599275</v>
       </c>
       <c r="F301" t="n">
-        <v>0.32835788137505</v>
+        <v>0.3283578813750501</v>
       </c>
       <c r="G301" t="n">
         <v>1981</v>
@@ -23207,7 +21836,7 @@
         <v>0.2945452951768361</v>
       </c>
       <c r="F304" t="n">
-        <v>0.3037337973790385</v>
+        <v>0.3037337973790386</v>
       </c>
       <c r="G304" t="n">
         <v>375</v>
@@ -23259,7 +21888,7 @@
         <v>0.2945392900069795</v>
       </c>
       <c r="F305" t="n">
-        <v>0.3049109419115818</v>
+        <v>0.3049109419115819</v>
       </c>
       <c r="G305" t="n">
         <v>1106</v>
@@ -23360,10 +21989,10 @@
         <v>5</v>
       </c>
       <c r="E307" t="n">
-        <v>0.2943433155135196</v>
+        <v>0.2943433155135197</v>
       </c>
       <c r="F307" t="n">
-        <v>0.2967447892702218</v>
+        <v>0.2967447892702219</v>
       </c>
       <c r="G307" t="n">
         <v>396</v>
@@ -23412,10 +22041,10 @@
         <v>1</v>
       </c>
       <c r="E308" t="n">
-        <v>0.2942807803013428</v>
+        <v>0.2942807803013429</v>
       </c>
       <c r="F308" t="n">
-        <v>0.2942807803013428</v>
+        <v>0.2942807803013429</v>
       </c>
       <c r="G308" t="n">
         <v>34</v>
@@ -23464,10 +22093,10 @@
         <v>1</v>
       </c>
       <c r="E309" t="n">
-        <v>0.29396056993733</v>
+        <v>0.2939605699373301</v>
       </c>
       <c r="F309" t="n">
-        <v>0.29396056993733</v>
+        <v>0.2939605699373301</v>
       </c>
       <c r="G309" t="n">
         <v>85</v>
@@ -23571,7 +22200,7 @@
         <v>0.2938826384822414</v>
       </c>
       <c r="F311" t="n">
-        <v>0.2971275245437775</v>
+        <v>0.2971275245437776</v>
       </c>
       <c r="G311" t="n">
         <v>409</v>
@@ -23620,10 +22249,10 @@
         <v>1</v>
       </c>
       <c r="E312" t="n">
-        <v>0.2937890184478984</v>
+        <v>0.2937890184478985</v>
       </c>
       <c r="F312" t="n">
-        <v>0.2937890184478984</v>
+        <v>0.2937890184478985</v>
       </c>
       <c r="G312" t="n">
         <v>28</v>
@@ -23675,7 +22304,7 @@
         <v>0.293693696648106</v>
       </c>
       <c r="F313" t="n">
-        <v>0.3012431814533944</v>
+        <v>0.3012431814533945</v>
       </c>
       <c r="G313" t="n">
         <v>239</v>
@@ -23828,7 +22457,7 @@
         <v>65</v>
       </c>
       <c r="E316" t="n">
-        <v>0.2934009808848797</v>
+        <v>0.2934009808848798</v>
       </c>
       <c r="F316" t="n">
         <v>0.3195758064046609</v>
@@ -23984,10 +22613,10 @@
         <v>1</v>
       </c>
       <c r="E319" t="n">
-        <v>0.2930339494893555</v>
+        <v>0.2930339494893556</v>
       </c>
       <c r="F319" t="n">
-        <v>0.2930339494893555</v>
+        <v>0.2930339494893556</v>
       </c>
       <c r="G319" t="n">
         <v>89</v>
@@ -24063,7 +22692,7 @@
         <v>1</v>
       </c>
       <c r="N320" t="n">
-        <v>38.35649095918368</v>
+        <v>38.35649095918367</v>
       </c>
       <c r="O320" t="n">
         <v>-0.4861343714285714</v>
@@ -24088,10 +22717,10 @@
         <v>532</v>
       </c>
       <c r="E321" t="n">
-        <v>0.2925745163896709</v>
+        <v>0.292574516389671</v>
       </c>
       <c r="F321" t="n">
-        <v>0.3394754208877947</v>
+        <v>0.3394754208877948</v>
       </c>
       <c r="G321" t="n">
         <v>66968</v>
@@ -24100,7 +22729,7 @@
         <v>10.59990746047573</v>
       </c>
       <c r="I321" t="n">
-        <v>2.146141140670536</v>
+        <v>2.146141140670535</v>
       </c>
       <c r="J321" t="n">
         <v>73233</v>
@@ -24140,10 +22769,10 @@
         <v>1</v>
       </c>
       <c r="E322" t="n">
-        <v>0.2924449081908576</v>
+        <v>0.2924449081908577</v>
       </c>
       <c r="F322" t="n">
-        <v>0.2924449081908576</v>
+        <v>0.2924449081908577</v>
       </c>
       <c r="G322" t="n">
         <v>206</v>
@@ -24299,7 +22928,7 @@
         <v>0.2918684299778437</v>
       </c>
       <c r="F325" t="n">
-        <v>0.308518737636997</v>
+        <v>0.3085187376369971</v>
       </c>
       <c r="G325" t="n">
         <v>5638</v>
@@ -24351,7 +22980,7 @@
         <v>0.291791570311732</v>
       </c>
       <c r="F326" t="n">
-        <v>0.2975297366545035</v>
+        <v>0.2975297366545036</v>
       </c>
       <c r="G326" t="n">
         <v>361</v>
@@ -24400,7 +23029,7 @@
         <v>5</v>
       </c>
       <c r="E327" t="n">
-        <v>0.2916501675448475</v>
+        <v>0.2916501675448476</v>
       </c>
       <c r="F327" t="n">
         <v>0.294261710476501</v>
@@ -24412,7 +23041,7 @@
         <v>11.76383295469065</v>
       </c>
       <c r="I327" t="n">
-        <v>1.746942221864823</v>
+        <v>1.746942221864822</v>
       </c>
       <c r="J327" t="n">
         <v>672</v>
@@ -24452,7 +23081,7 @@
         <v>2</v>
       </c>
       <c r="E328" t="n">
-        <v>0.2914087497335867</v>
+        <v>0.2914087497335868</v>
       </c>
       <c r="F328" t="n">
         <v>0.2953008340313514</v>
@@ -24504,7 +23133,7 @@
         <v>10</v>
       </c>
       <c r="E329" t="n">
-        <v>0.2912864305612815</v>
+        <v>0.2912864305612816</v>
       </c>
       <c r="F329" t="n">
         <v>0.3012981276633631</v>
@@ -24556,7 +23185,7 @@
         <v>6</v>
       </c>
       <c r="E330" t="n">
-        <v>0.2911681737605476</v>
+        <v>0.2911681737605477</v>
       </c>
       <c r="F330" t="n">
         <v>0.2989295278487792</v>
@@ -24672,7 +23301,7 @@
         <v>6.318060469808222</v>
       </c>
       <c r="I332" t="n">
-        <v>1.89079619733629</v>
+        <v>1.890796197336291</v>
       </c>
       <c r="J332" t="n">
         <v>4103</v>
@@ -24721,7 +23350,7 @@
         <v>252</v>
       </c>
       <c r="H333" t="n">
-        <v>7.00877505238326</v>
+        <v>7.008775052383259</v>
       </c>
       <c r="I333" t="n">
         <v>1.246612466124661</v>
@@ -24871,7 +23500,7 @@
         <v>0.2903719867788724</v>
       </c>
       <c r="F336" t="n">
-        <v>0.3852801044787884</v>
+        <v>0.3852801044787885</v>
       </c>
       <c r="G336" t="n">
         <v>23793</v>
@@ -24975,7 +23604,7 @@
         <v>0.2901227368501619</v>
       </c>
       <c r="F338" t="n">
-        <v>0.2916859797510819</v>
+        <v>0.291685979751082</v>
       </c>
       <c r="G338" t="n">
         <v>310</v>
@@ -25024,10 +23653,10 @@
         <v>1</v>
       </c>
       <c r="E339" t="n">
-        <v>0.2898682009069195</v>
+        <v>0.2898682009069196</v>
       </c>
       <c r="F339" t="n">
-        <v>0.2898682009069195</v>
+        <v>0.2898682009069196</v>
       </c>
       <c r="G339" t="n">
         <v>31</v>
@@ -25076,10 +23705,10 @@
         <v>1</v>
       </c>
       <c r="E340" t="n">
-        <v>0.289778721978159</v>
+        <v>0.2897787219781591</v>
       </c>
       <c r="F340" t="n">
-        <v>0.289778721978159</v>
+        <v>0.2897787219781591</v>
       </c>
       <c r="G340" t="n">
         <v>66</v>
@@ -25232,7 +23861,7 @@
         <v>23</v>
       </c>
       <c r="E343" t="n">
-        <v>0.2890530997211928</v>
+        <v>0.2890530997211929</v>
       </c>
       <c r="F343" t="n">
         <v>0.3128573763929978</v>
@@ -25501,7 +24130,7 @@
         <v>967</v>
       </c>
       <c r="H348" t="n">
-        <v>10.05342216980452</v>
+        <v>10.05342216980451</v>
       </c>
       <c r="I348" t="n">
         <v>2.075693360898736</v>
@@ -25544,10 +24173,10 @@
         <v>1</v>
       </c>
       <c r="E349" t="n">
-        <v>0.287642712775591</v>
+        <v>0.2876427127755911</v>
       </c>
       <c r="F349" t="n">
-        <v>0.287642712775591</v>
+        <v>0.2876427127755911</v>
       </c>
       <c r="G349" t="n">
         <v>205</v>
@@ -26015,7 +24644,7 @@
         <v>0.2870191905504742</v>
       </c>
       <c r="F358" t="n">
-        <v>0.2926788445681886</v>
+        <v>0.2926788445681887</v>
       </c>
       <c r="G358" t="n">
         <v>274</v>
@@ -26064,10 +24693,10 @@
         <v>2</v>
       </c>
       <c r="E359" t="n">
-        <v>0.2866956712451672</v>
+        <v>0.2866956712451673</v>
       </c>
       <c r="F359" t="n">
-        <v>0.2926543868209564</v>
+        <v>0.2926543868209565</v>
       </c>
       <c r="G359" t="n">
         <v>308</v>
@@ -26076,7 +24705,7 @@
         <v>7.913010461386512</v>
       </c>
       <c r="I359" t="n">
-        <v>1.751035196687371</v>
+        <v>1.75103519668737</v>
       </c>
       <c r="J359" t="n">
         <v>381</v>
@@ -26119,7 +24748,7 @@
         <v>0.2866675803197221</v>
       </c>
       <c r="F360" t="n">
-        <v>0.2921467593036488</v>
+        <v>0.2921467593036489</v>
       </c>
       <c r="G360" t="n">
         <v>351</v>
@@ -26168,7 +24797,7 @@
         <v>10</v>
       </c>
       <c r="E361" t="n">
-        <v>0.2865631332824684</v>
+        <v>0.2865631332824685</v>
       </c>
       <c r="F361" t="n">
         <v>0.2926480837704843</v>
@@ -26532,7 +25161,7 @@
         <v>2</v>
       </c>
       <c r="E368" t="n">
-        <v>0.2858212843418364</v>
+        <v>0.2858212843418365</v>
       </c>
       <c r="F368" t="n">
         <v>0.2900177606508222</v>
@@ -26844,7 +25473,7 @@
         <v>2</v>
       </c>
       <c r="E374" t="n">
-        <v>0.2846460833037706</v>
+        <v>0.2846460833037707</v>
       </c>
       <c r="F374" t="n">
         <v>0.2920090063095045</v>
@@ -27003,7 +25632,7 @@
         <v>0.2842912695782928</v>
       </c>
       <c r="F377" t="n">
-        <v>0.2939630080910534</v>
+        <v>0.2939630080910535</v>
       </c>
       <c r="G377" t="n">
         <v>1155</v>
@@ -27052,7 +25681,7 @@
         <v>20</v>
       </c>
       <c r="E378" t="n">
-        <v>0.2841942061207498</v>
+        <v>0.2841942061207499</v>
       </c>
       <c r="F378" t="n">
         <v>0.2975094312379721</v>
@@ -27156,10 +25785,10 @@
         <v>1</v>
       </c>
       <c r="E380" t="n">
-        <v>0.2841690136877309</v>
+        <v>0.284169013687731</v>
       </c>
       <c r="F380" t="n">
-        <v>0.2841690136877309</v>
+        <v>0.284169013687731</v>
       </c>
       <c r="G380" t="n">
         <v>75</v>
@@ -27272,7 +25901,7 @@
         <v>12.08517876777488</v>
       </c>
       <c r="I382" t="n">
-        <v>2.19399906119057</v>
+        <v>2.193999061190571</v>
       </c>
       <c r="J382" t="n">
         <v>15372</v>
@@ -27315,7 +25944,7 @@
         <v>0.2837109874366653</v>
       </c>
       <c r="F383" t="n">
-        <v>0.2941229874781418</v>
+        <v>0.2941229874781419</v>
       </c>
       <c r="G383" t="n">
         <v>1499</v>
@@ -27520,10 +26149,10 @@
         <v>1</v>
       </c>
       <c r="E387" t="n">
-        <v>0.2828184392943776</v>
+        <v>0.2828184392943777</v>
       </c>
       <c r="F387" t="n">
-        <v>0.2828184392943776</v>
+        <v>0.2828184392943777</v>
       </c>
       <c r="G387" t="n">
         <v>37</v>
@@ -27832,7 +26461,7 @@
         <v>24</v>
       </c>
       <c r="E393" t="n">
-        <v>0.2823413106234775</v>
+        <v>0.2823413106234776</v>
       </c>
       <c r="F393" t="n">
         <v>0.2978501148085362</v>
@@ -28040,10 +26669,10 @@
         <v>1</v>
       </c>
       <c r="E397" t="n">
-        <v>0.2822039476077865</v>
+        <v>0.2822039476077866</v>
       </c>
       <c r="F397" t="n">
-        <v>0.2822039476077865</v>
+        <v>0.2822039476077866</v>
       </c>
       <c r="G397" t="n">
         <v>210</v>
@@ -28248,7 +26877,7 @@
         <v>3</v>
       </c>
       <c r="E401" t="n">
-        <v>0.2819668173272789</v>
+        <v>0.281966817327279</v>
       </c>
       <c r="F401" t="n">
         <v>0.2943618808753476</v>
@@ -28486,7 +27115,7 @@
         <v>35.28889113636364</v>
       </c>
       <c r="O405" t="n">
-        <v>-2.946369295454545</v>
+        <v>-2.946369295454546</v>
       </c>
       <c r="P405" t="n">
         <v>404</v>
@@ -28563,7 +27192,7 @@
         <v>0.2806372250529809</v>
       </c>
       <c r="F407" t="n">
-        <v>0.2906924550658369</v>
+        <v>0.290692455065837</v>
       </c>
       <c r="G407" t="n">
         <v>315</v>
@@ -28716,10 +27345,10 @@
         <v>1</v>
       </c>
       <c r="E410" t="n">
-        <v>0.2800782273924458</v>
+        <v>0.2800782273924459</v>
       </c>
       <c r="F410" t="n">
-        <v>0.2800782273924458</v>
+        <v>0.2800782273924459</v>
       </c>
       <c r="G410" t="n">
         <v>85</v>
@@ -28872,7 +27501,7 @@
         <v>179</v>
       </c>
       <c r="E413" t="n">
-        <v>0.2793792296023776</v>
+        <v>0.2793792296023777</v>
       </c>
       <c r="F413" t="n">
         <v>0.3115778203873842</v>
@@ -29395,7 +28024,7 @@
         <v>0.2779316207501539</v>
       </c>
       <c r="F423" t="n">
-        <v>0.3083954595169589</v>
+        <v>0.308395459516959</v>
       </c>
       <c r="G423" t="n">
         <v>25182</v>
@@ -29447,7 +28076,7 @@
         <v>0.2779157972239722</v>
       </c>
       <c r="F424" t="n">
-        <v>0.2940426135448308</v>
+        <v>0.2940426135448309</v>
       </c>
       <c r="G424" t="n">
         <v>2805</v>
@@ -29551,7 +28180,7 @@
         <v>0.2776214475019464</v>
       </c>
       <c r="F426" t="n">
-        <v>0.282685334721115</v>
+        <v>0.2826853347211151</v>
       </c>
       <c r="G426" t="n">
         <v>628</v>
@@ -29759,7 +28388,7 @@
         <v>0.2766704595752876</v>
       </c>
       <c r="F430" t="n">
-        <v>0.3114974119429013</v>
+        <v>0.3114974119429014</v>
       </c>
       <c r="G430" t="n">
         <v>11971</v>
@@ -29768,7 +28397,7 @@
         <v>12.37696682640618</v>
       </c>
       <c r="I430" t="n">
-        <v>2.039484942171521</v>
+        <v>2.039484942171522</v>
       </c>
       <c r="J430" t="n">
         <v>12258</v>
@@ -29808,7 +28437,7 @@
         <v>7</v>
       </c>
       <c r="E431" t="n">
-        <v>0.276349160934154</v>
+        <v>0.2763491609341541</v>
       </c>
       <c r="F431" t="n">
         <v>0.2832553952354751</v>
@@ -29860,10 +28489,10 @@
         <v>1</v>
       </c>
       <c r="E432" t="n">
-        <v>0.276208415623651</v>
+        <v>0.2762084156236511</v>
       </c>
       <c r="F432" t="n">
-        <v>0.276208415623651</v>
+        <v>0.2762084156236511</v>
       </c>
       <c r="G432" t="n">
         <v>37</v>
@@ -30123,7 +28752,7 @@
         <v>0.2757250455738016</v>
       </c>
       <c r="F437" t="n">
-        <v>0.2762058091363993</v>
+        <v>0.2762058091363994</v>
       </c>
       <c r="G437" t="n">
         <v>466</v>
@@ -30383,7 +29012,7 @@
         <v>0.2743419755076222</v>
       </c>
       <c r="F442" t="n">
-        <v>0.3276426515692869</v>
+        <v>0.327642651569287</v>
       </c>
       <c r="G442" t="n">
         <v>34198</v>
@@ -30432,7 +29061,7 @@
         <v>4</v>
       </c>
       <c r="E443" t="n">
-        <v>0.2742454366689005</v>
+        <v>0.2742454366689006</v>
       </c>
       <c r="F443" t="n">
         <v>0.2899257123321703</v>
@@ -30640,10 +29269,10 @@
         <v>1</v>
       </c>
       <c r="E447" t="n">
-        <v>0.2738034253578745</v>
+        <v>0.2738034253578746</v>
       </c>
       <c r="F447" t="n">
-        <v>0.2738034253578745</v>
+        <v>0.2738034253578746</v>
       </c>
       <c r="G447" t="n">
         <v>127</v>
@@ -30747,7 +29376,7 @@
         <v>0.2734983978667447</v>
       </c>
       <c r="F449" t="n">
-        <v>0.2845027972905884</v>
+        <v>0.2845027972905885</v>
       </c>
       <c r="G449" t="n">
         <v>1041</v>
@@ -30848,7 +29477,7 @@
         <v>61</v>
       </c>
       <c r="E451" t="n">
-        <v>0.2732458117957991</v>
+        <v>0.2732458117957992</v>
       </c>
       <c r="F451" t="n">
         <v>0.2949950326455233</v>
@@ -31004,10 +29633,10 @@
         <v>1</v>
       </c>
       <c r="E454" t="n">
-        <v>0.2729975440481026</v>
+        <v>0.2729975440481027</v>
       </c>
       <c r="F454" t="n">
-        <v>0.2729975440481026</v>
+        <v>0.2729975440481027</v>
       </c>
       <c r="G454" t="n">
         <v>112</v>
@@ -31108,10 +29737,10 @@
         <v>1</v>
       </c>
       <c r="E456" t="n">
-        <v>0.2724297472363562</v>
+        <v>0.2724297472363563</v>
       </c>
       <c r="F456" t="n">
-        <v>0.2724297472363562</v>
+        <v>0.2724297472363563</v>
       </c>
       <c r="G456" t="n">
         <v>26</v>
@@ -31160,7 +29789,7 @@
         <v>202</v>
       </c>
       <c r="E457" t="n">
-        <v>0.2723279175710449</v>
+        <v>0.272327917571045</v>
       </c>
       <c r="F457" t="n">
         <v>0.2953535504799218</v>
@@ -31423,7 +30052,7 @@
         <v>0.2711086808682969</v>
       </c>
       <c r="F462" t="n">
-        <v>0.310629784948455</v>
+        <v>0.3106297849484551</v>
       </c>
       <c r="G462" t="n">
         <v>10296</v>
@@ -31603,7 +30232,7 @@
         <v>0</v>
       </c>
       <c r="N465" t="n">
-        <v>42.773558</v>
+        <v>42.77355799999999</v>
       </c>
       <c r="O465" t="n">
         <v>-1.70731</v>
@@ -31631,7 +30260,7 @@
         <v>0.2704075581477351</v>
       </c>
       <c r="F466" t="n">
-        <v>0.2884375284193626</v>
+        <v>0.2884375284193627</v>
       </c>
       <c r="G466" t="n">
         <v>2638</v>
@@ -31732,7 +30361,7 @@
         <v>75</v>
       </c>
       <c r="E468" t="n">
-        <v>0.2697507469230076</v>
+        <v>0.2697507469230077</v>
       </c>
       <c r="F468" t="n">
         <v>0.2937662965017688</v>
@@ -31784,10 +30413,10 @@
         <v>1</v>
       </c>
       <c r="E469" t="n">
-        <v>0.2697168830217565</v>
+        <v>0.2697168830217566</v>
       </c>
       <c r="F469" t="n">
-        <v>0.2697168830217565</v>
+        <v>0.2697168830217566</v>
       </c>
       <c r="G469" t="n">
         <v>87</v>
@@ -31888,10 +30517,10 @@
         <v>1</v>
       </c>
       <c r="E471" t="n">
-        <v>0.2694926687253335</v>
+        <v>0.2694926687253336</v>
       </c>
       <c r="F471" t="n">
-        <v>0.2694926687253335</v>
+        <v>0.2694926687253336</v>
       </c>
       <c r="G471" t="n">
         <v>30</v>
@@ -31940,10 +30569,10 @@
         <v>164</v>
       </c>
       <c r="E472" t="n">
-        <v>0.269405795676192</v>
+        <v>0.2694057956761921</v>
       </c>
       <c r="F472" t="n">
-        <v>0.294293611738476</v>
+        <v>0.2942936117384761</v>
       </c>
       <c r="G472" t="n">
         <v>20025</v>
@@ -31992,7 +30621,7 @@
         <v>68</v>
       </c>
       <c r="E473" t="n">
-        <v>0.2693699458446918</v>
+        <v>0.2693699458446919</v>
       </c>
       <c r="F473" t="n">
         <v>0.3060378272639468</v>
@@ -32151,7 +30780,7 @@
         <v>0.2688628535329193</v>
       </c>
       <c r="F476" t="n">
-        <v>0.2748466054434313</v>
+        <v>0.2748466054434314</v>
       </c>
       <c r="G476" t="n">
         <v>603</v>
@@ -32203,7 +30832,7 @@
         <v>0.2683708490455727</v>
       </c>
       <c r="F477" t="n">
-        <v>0.2889261173411352</v>
+        <v>0.2889261173411353</v>
       </c>
       <c r="G477" t="n">
         <v>2530</v>
@@ -32252,10 +30881,10 @@
         <v>1</v>
       </c>
       <c r="E478" t="n">
-        <v>0.2680180326988572</v>
+        <v>0.2680180326988573</v>
       </c>
       <c r="F478" t="n">
-        <v>0.2680180326988572</v>
+        <v>0.2680180326988573</v>
       </c>
       <c r="G478" t="n">
         <v>95</v>
@@ -32408,7 +31037,7 @@
         <v>166</v>
       </c>
       <c r="E481" t="n">
-        <v>0.2676487736542128</v>
+        <v>0.2676487736542129</v>
       </c>
       <c r="F481" t="n">
         <v>0.3103149517109111</v>
@@ -32420,7 +31049,7 @@
         <v>11.65582751425326</v>
       </c>
       <c r="I481" t="n">
-        <v>1.740500258576812</v>
+        <v>1.740500258576811</v>
       </c>
       <c r="J481" t="n">
         <v>29207</v>
@@ -32438,7 +31067,7 @@
         <v>42.85095603614458</v>
       </c>
       <c r="O481" t="n">
-        <v>-2.677920487951808</v>
+        <v>-2.677920487951807</v>
       </c>
       <c r="P481" t="n">
         <v>480</v>
@@ -32515,7 +31144,7 @@
         <v>0.267218218527344</v>
       </c>
       <c r="F483" t="n">
-        <v>0.2791977230829013</v>
+        <v>0.2791977230829014</v>
       </c>
       <c r="G483" t="n">
         <v>1745</v>
@@ -32564,10 +31193,10 @@
         <v>21</v>
       </c>
       <c r="E484" t="n">
-        <v>0.2671068487828122</v>
+        <v>0.2671068487828123</v>
       </c>
       <c r="F484" t="n">
-        <v>0.2864107414894767</v>
+        <v>0.2864107414894768</v>
       </c>
       <c r="G484" t="n">
         <v>3634</v>
@@ -32775,7 +31404,7 @@
         <v>0.2665283776815991</v>
       </c>
       <c r="F488" t="n">
-        <v>0.2927397652522231</v>
+        <v>0.2927397652522232</v>
       </c>
       <c r="G488" t="n">
         <v>1676</v>
@@ -32784,7 +31413,7 @@
         <v>12.41265615146908</v>
       </c>
       <c r="I488" t="n">
-        <v>1.756206548892384</v>
+        <v>1.756206548892383</v>
       </c>
       <c r="J488" t="n">
         <v>1791</v>
@@ -32980,7 +31609,7 @@
         <v>3</v>
       </c>
       <c r="E492" t="n">
-        <v>0.2660496889440157</v>
+        <v>0.2660496889440158</v>
       </c>
       <c r="F492" t="n">
         <v>0.2778515348217613</v>
@@ -33084,7 +31713,7 @@
         <v>186</v>
       </c>
       <c r="E494" t="n">
-        <v>0.2658883647369944</v>
+        <v>0.2658883647369945</v>
       </c>
       <c r="F494" t="n">
         <v>0.3005120395760801</v>
@@ -33550,7 +32179,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4404046217456825</v>
+        <v>0.4404046217456826</v>
       </c>
       <c r="D3" t="n">
         <v>12158</v>
@@ -33788,7 +32417,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2692936794206538</v>
+        <v>0.2692936794206539</v>
       </c>
       <c r="D17" t="n">
         <v>43002</v>
@@ -33856,7 +32485,7 @@
         <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2676879580532478</v>
+        <v>0.2676879580532479</v>
       </c>
       <c r="D21" t="n">
         <v>15062</v>
@@ -33873,7 +32502,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2676487736542128</v>
+        <v>0.2676487736542129</v>
       </c>
       <c r="D22" t="n">
         <v>26970</v>
@@ -33924,7 +32553,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.263886062580155</v>
+        <v>0.2638860625801551</v>
       </c>
       <c r="D25" t="n">
         <v>24291</v>
@@ -33975,7 +32604,7 @@
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2523978776291873</v>
+        <v>0.2523978776291874</v>
       </c>
       <c r="D28" t="n">
         <v>16619</v>
@@ -34009,7 +32638,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2505313237909778</v>
+        <v>0.2505313237909779</v>
       </c>
       <c r="D30" t="n">
         <v>76436</v>
@@ -34043,7 +32672,7 @@
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2429516481812993</v>
+        <v>0.2429516481812994</v>
       </c>
       <c r="D32" t="n">
         <v>14624</v>
@@ -34077,7 +32706,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2402350181414875</v>
+        <v>0.2402350181414876</v>
       </c>
       <c r="D34" t="n">
         <v>7089</v>
@@ -34162,7 +32791,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2277915576433504</v>
+        <v>0.2277915576433505</v>
       </c>
       <c r="D39" t="n">
         <v>5329</v>
@@ -34179,7 +32808,7 @@
         <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2238505300074535</v>
+        <v>0.2238505300074536</v>
       </c>
       <c r="D40" t="n">
         <v>18941</v>
@@ -34196,7 +32825,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2237114862150721</v>
+        <v>0.2237114862150722</v>
       </c>
       <c r="D41" t="n">
         <v>6506</v>
@@ -34213,7 +32842,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2231065254634673</v>
+        <v>0.2231065254634674</v>
       </c>
       <c r="D42" t="n">
         <v>18018</v>
@@ -34281,7 +32910,7 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2108250831995348</v>
+        <v>0.2108250831995349</v>
       </c>
       <c r="D46" t="n">
         <v>21939</v>
@@ -34298,7 +32927,7 @@
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2096047968588957</v>
+        <v>0.2096047968588958</v>
       </c>
       <c r="D47" t="n">
         <v>5320</v>
@@ -34356,233 +32985,6 @@
       </c>
       <c r="E50" t="n">
         <v>30203</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>perfil</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>municipios</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>renta_media</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>vol_75plus</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>fofm_medio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Gran ciudad — mercado masivo</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30033.64</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47895.82</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Municipio equilibrado — perfil estándar</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>30</v>
-      </c>
-      <c r="C3" t="n">
-        <v>31317.33</v>
-      </c>
-      <c r="D3" t="n">
-        <v>13527.63</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>54</v>
-      </c>
-      <c r="C4" t="n">
-        <v>30270.7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4488.78</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Zona premium — máxima solvencia</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>67280</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4462.2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Archivo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Para qué sirve</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mapa_top100.html</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Mapa interactivo — abrir en navegador, clicar en cada punto</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>grafico_perfiles.png</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Gráfico de barras con los 4 perfiles estratégicos — meter en slides</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>grafico_top20.png</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ranking visual del top 20 municipios — meter en slides</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>grafico_solvencia_mercado.png</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Scatter solvencia vs mercado — meter en slides</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>resultados_akademia.xlsx</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Excel con todas las pestañas de resultados</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>top100_con_clusters.csv</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Datos completos del top 100 con perfil asignado</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dataset_maestro.csv</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Dataset central con todas las variables calculadas</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/resultados_akademia.xlsx
+++ b/resultados_akademia.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X101"/>
+  <dimension ref="A1:W101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,11 +548,6 @@
           <t>perfil</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>perfil_corto</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -628,11 +623,6 @@
           <t>Zona premium — máxima solvencia</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -708,11 +698,6 @@
           <t>Zona premium — máxima solvencia</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -788,11 +773,6 @@
           <t>Zona premium — máxima solvencia</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -868,11 +848,6 @@
           <t>Zona premium — máxima solvencia</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -948,11 +923,6 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1028,12 +998,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1109,11 +1073,6 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1189,11 +1148,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1269,11 +1223,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1349,12 +1298,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1430,12 +1373,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1511,11 +1448,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1591,11 +1523,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1671,12 +1598,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1752,12 +1673,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1833,11 +1748,6 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1913,11 +1823,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1993,11 +1898,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2073,12 +1973,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2154,11 +2048,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2234,11 +2123,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2314,12 +2198,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2395,11 +2273,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2475,12 +2348,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2556,11 +2423,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2636,11 +2498,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2716,11 +2573,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2796,11 +2648,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2876,12 +2723,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2955,11 +2796,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3035,12 +2871,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3116,12 +2946,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3197,11 +3021,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3277,12 +3096,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3358,12 +3171,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3439,12 +3246,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3520,11 +3321,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3600,12 +3396,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3681,12 +3471,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3762,12 +3546,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3843,12 +3621,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3924,11 +3696,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4004,12 +3771,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4085,12 +3846,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4166,11 +3921,6 @@
           <t>Gran ciudad — mercado masivo</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>Gran ciudad</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4246,11 +3996,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4326,11 +4071,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4406,12 +4146,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4487,12 +4221,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4568,11 +4296,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4648,12 +4371,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4729,11 +4446,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4809,11 +4521,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4889,11 +4596,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4969,12 +4671,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5050,11 +4746,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5130,11 +4821,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5210,12 +4896,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5291,12 +4971,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5372,12 +5046,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5453,12 +5121,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5534,12 +5196,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5615,12 +5271,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5696,11 +5346,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5776,11 +5421,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5856,12 +5496,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5937,11 +5571,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6017,12 +5646,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6098,12 +5721,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6179,11 +5796,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6259,12 +5871,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6340,12 +5946,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6421,12 +6021,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6502,12 +6096,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6583,12 +6171,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6664,12 +6246,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6745,11 +6321,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6825,11 +6396,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6905,12 +6471,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6986,12 +6546,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7067,12 +6621,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7148,11 +6696,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7228,11 +6771,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7308,12 +6846,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7389,12 +6921,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7470,11 +6996,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7550,12 +7071,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7631,12 +7146,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7712,12 +7221,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7793,12 +7296,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7874,12 +7371,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7955,11 +7446,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8035,12 +7521,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8116,11 +7596,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8196,11 +7671,6 @@
           <t>Ciudad media — mercado relevante</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Ciudad media</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8274,12 +7744,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8355,12 +7819,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8436,12 +7894,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8517,12 +7969,6 @@
           <t>Zona envejecida — solvencia ajustada</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8596,12 +8042,6 @@
       <c r="W101" t="inlineStr">
         <is>
           <t>Zona envejecida — solvencia ajustada</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Solvencia
-ajustada</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8411,7 @@
         <v>40.41240833333333</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.888334666666665</v>
+        <v>-3.888334666666666</v>
       </c>
       <c r="T5" t="n">
         <v>4</v>
@@ -8993,7 +8433,7 @@
         <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4847794023813705</v>
+        <v>0.4847794023813706</v>
       </c>
       <c r="F6" t="n">
         <v>0.5077566522111981</v>
@@ -9078,7 +8518,7 @@
         <v>319329</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9142261290996812</v>
+        <v>0.9142261290996813</v>
       </c>
       <c r="M7" t="n">
         <v>39613</v>
@@ -9121,7 +8561,7 @@
         <v>1068</v>
       </c>
       <c r="E8" t="n">
-        <v>0.43823438740435</v>
+        <v>0.4382343874043501</v>
       </c>
       <c r="F8" t="n">
         <v>0.5008186096978743</v>
@@ -9185,7 +8625,7 @@
         <v>45</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4300104378358091</v>
+        <v>0.4300104378358092</v>
       </c>
       <c r="F9" t="n">
         <v>0.4439702879247481</v>
@@ -9249,7 +8689,7 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4273114272024347</v>
+        <v>0.4273114272024348</v>
       </c>
       <c r="F10" t="n">
         <v>0.4316250920747843</v>
@@ -9517,7 +8957,7 @@
         <v>3141</v>
       </c>
       <c r="I14" t="n">
-        <v>6.056076162310792</v>
+        <v>6.056076162310791</v>
       </c>
       <c r="J14" t="n">
         <v>1.749123352635103</v>
@@ -9569,7 +9009,7 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.419872088112816</v>
+        <v>0.4198720881128161</v>
       </c>
       <c r="F15" t="n">
         <v>0.4248811738237891</v>
@@ -9968,7 +9408,7 @@
         <v>10.7536513216607</v>
       </c>
       <c r="J21" t="n">
-        <v>1.662399414212096</v>
+        <v>1.662399414212095</v>
       </c>
       <c r="K21" t="n">
         <v>19881</v>
@@ -10081,10 +9521,10 @@
         <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4014445370661</v>
+        <v>0.4014445370661001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.409363285577031</v>
+        <v>0.4093632855770311</v>
       </c>
       <c r="G23" t="n">
         <v>1609</v>
@@ -10145,10 +9585,10 @@
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4005090199348843</v>
+        <v>0.4005090199348844</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4113456095546476</v>
+        <v>0.4113456095546477</v>
       </c>
       <c r="G24" t="n">
         <v>1142</v>
@@ -10340,7 +9780,7 @@
         <v>0.3970367508766875</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4219724242267962</v>
+        <v>0.4219724242267963</v>
       </c>
       <c r="G27" t="n">
         <v>5520</v>
@@ -10404,7 +9844,7 @@
         <v>0.3965893437364171</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4247937846737621</v>
+        <v>0.4247937846737622</v>
       </c>
       <c r="G28" t="n">
         <v>19697</v>
@@ -10465,7 +9905,7 @@
         <v>45</v>
       </c>
       <c r="E29" t="n">
-        <v>0.395681280366926</v>
+        <v>0.3956812803669261</v>
       </c>
       <c r="F29" t="n">
         <v>0.4186525982358722</v>
@@ -10596,7 +10036,7 @@
         <v>0.3939259329009059</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4096895019792347</v>
+        <v>0.4096895019792348</v>
       </c>
       <c r="G31" t="n">
         <v>7809</v>
@@ -10660,7 +10100,7 @@
         <v>0.3936927671285551</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4054971899163352</v>
+        <v>0.4054971899163353</v>
       </c>
       <c r="G32" t="n">
         <v>15857</v>
@@ -10721,7 +10161,7 @@
         <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3932994468335214</v>
+        <v>0.3932994468335215</v>
       </c>
       <c r="F33" t="n">
         <v>0.4138761207962848</v>
@@ -10916,7 +10356,7 @@
         <v>0.3901560043592153</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4310573778138027</v>
+        <v>0.4310573778138028</v>
       </c>
       <c r="G36" t="n">
         <v>4943</v>
@@ -11108,7 +10548,7 @@
         <v>0.3885511492249665</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4062963611076703</v>
+        <v>0.4062963611076704</v>
       </c>
       <c r="G39" t="n">
         <v>3649</v>
@@ -11169,7 +10609,7 @@
         <v>31</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3881643550528166</v>
+        <v>0.3881643550528167</v>
       </c>
       <c r="F40" t="n">
         <v>0.4029524221910833</v>
@@ -11233,7 +10673,7 @@
         <v>17</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3875510537389265</v>
+        <v>0.3875510537389266</v>
       </c>
       <c r="F41" t="n">
         <v>0.3978122287219664</v>
@@ -11309,7 +10749,7 @@
         <v>1064</v>
       </c>
       <c r="I42" t="n">
-        <v>9.035307829716205</v>
+        <v>9.035307829716203</v>
       </c>
       <c r="J42" t="n">
         <v>1.435204762679754</v>
@@ -11361,7 +10801,7 @@
         <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3865025101492191</v>
+        <v>0.3865025101492192</v>
       </c>
       <c r="F43" t="n">
         <v>0.3994604562223356</v>
@@ -11492,7 +10932,7 @@
         <v>0.3852515745175681</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3996727303529975</v>
+        <v>0.3996727303529976</v>
       </c>
       <c r="G45" t="n">
         <v>12052</v>
@@ -11510,7 +10950,7 @@
         <v>12048</v>
       </c>
       <c r="L45" t="n">
-        <v>0.9694076082655541</v>
+        <v>0.9694076082655539</v>
       </c>
       <c r="M45" t="n">
         <v>26874</v>
@@ -11684,7 +11124,7 @@
         <v>0.3840601728753373</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4012579135344258</v>
+        <v>0.4012579135344259</v>
       </c>
       <c r="G48" t="n">
         <v>20439</v>
@@ -11748,7 +11188,7 @@
         <v>0.3828955112052963</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3859991049433038</v>
+        <v>0.3859991049433039</v>
       </c>
       <c r="G49" t="n">
         <v>475</v>
@@ -12004,7 +11444,7 @@
         <v>0.3808434521491061</v>
       </c>
       <c r="F53" t="n">
-        <v>0.403672606152368</v>
+        <v>0.4036726061523681</v>
       </c>
       <c r="G53" t="n">
         <v>2915</v>
@@ -12065,7 +11505,7 @@
         <v>137</v>
       </c>
       <c r="E54" t="n">
-        <v>0.380376645082321</v>
+        <v>0.3803766450823211</v>
       </c>
       <c r="F54" t="n">
         <v>0.3996640849353248</v>
@@ -12132,7 +11572,7 @@
         <v>0.3794772647641941</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3959979800998416</v>
+        <v>0.3959979800998417</v>
       </c>
       <c r="G55" t="n">
         <v>4037</v>
@@ -12156,7 +11596,7 @@
         <v>31823</v>
       </c>
       <c r="N55" t="n">
-        <v>1281.549999999999</v>
+        <v>1281.55</v>
       </c>
       <c r="O55" t="n">
         <v>1645.4</v>
@@ -12272,13 +11712,13 @@
         <v>10.46124360510631</v>
       </c>
       <c r="J57" t="n">
-        <v>1.831254807970086</v>
+        <v>1.831254807970087</v>
       </c>
       <c r="K57" t="n">
         <v>7910</v>
       </c>
       <c r="L57" t="n">
-        <v>0.9758774464963172</v>
+        <v>0.9758774464963171</v>
       </c>
       <c r="M57" t="n">
         <v>30555</v>
@@ -12385,7 +11825,7 @@
         <v>12</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3764199619469969</v>
+        <v>0.376419961946997</v>
       </c>
       <c r="F59" t="n">
         <v>0.3879095256430624</v>
@@ -12449,7 +11889,7 @@
         <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>0.376375885271227</v>
+        <v>0.3763758852712271</v>
       </c>
       <c r="F60" t="n">
         <v>0.3802668306404175</v>
@@ -12577,10 +12017,10 @@
         <v>11</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3746687258517215</v>
+        <v>0.3746687258517216</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3849434188163882</v>
+        <v>0.3849434188163883</v>
       </c>
       <c r="G62" t="n">
         <v>907</v>
@@ -12662,7 +12102,7 @@
         <v>391</v>
       </c>
       <c r="L63" t="n">
-        <v>1.222414779226722</v>
+        <v>1.222414779226721</v>
       </c>
       <c r="M63" t="n">
         <v>48264</v>
@@ -12705,7 +12145,7 @@
         <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3734745910803766</v>
+        <v>0.3734745910803767</v>
       </c>
       <c r="F64" t="n">
         <v>0.38443622659578</v>
@@ -12811,7 +12251,7 @@
         <v>40.68065216666667</v>
       </c>
       <c r="S65" t="n">
-        <v>-3.622887166666666</v>
+        <v>-3.622887166666667</v>
       </c>
       <c r="T65" t="n">
         <v>64</v>
@@ -12833,7 +12273,7 @@
         <v>9</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3699041360218369</v>
+        <v>0.369904136021837</v>
       </c>
       <c r="F66" t="n">
         <v>0.3918231273859549</v>
@@ -12897,7 +12337,7 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3693278205467056</v>
+        <v>0.3693278205467057</v>
       </c>
       <c r="F67" t="n">
         <v>0.3750863904888986</v>
@@ -13092,7 +12532,7 @@
         <v>0.3644276061921603</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3844585154316089</v>
+        <v>0.384458515431609</v>
       </c>
       <c r="G70" t="n">
         <v>5554</v>
@@ -13104,7 +12544,7 @@
         <v>4.491093050992502</v>
       </c>
       <c r="J70" t="n">
-        <v>1.762816364595052</v>
+        <v>1.762816364595053</v>
       </c>
       <c r="K70" t="n">
         <v>11419</v>
@@ -13153,7 +12593,7 @@
         <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3636655230702408</v>
+        <v>0.3636655230702409</v>
       </c>
       <c r="F71" t="n">
         <v>0.3720566590275161</v>
@@ -13348,7 +12788,7 @@
         <v>0.3624715625854929</v>
       </c>
       <c r="F74" t="n">
-        <v>0.3668475111728306</v>
+        <v>0.3668475111728307</v>
       </c>
       <c r="G74" t="n">
         <v>651</v>
@@ -13494,7 +12934,7 @@
         <v>1004</v>
       </c>
       <c r="L76" t="n">
-        <v>1.959189395903754</v>
+        <v>1.959189395903755</v>
       </c>
       <c r="M76" t="n">
         <v>40819</v>
@@ -13665,10 +13105,10 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>0.3589500026778491</v>
+        <v>0.3589500026778492</v>
       </c>
       <c r="F79" t="n">
-        <v>0.3589500026778491</v>
+        <v>0.3589500026778492</v>
       </c>
       <c r="G79" t="n">
         <v>64</v>
@@ -13729,7 +13169,7 @@
         <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>0.3583163611528683</v>
+        <v>0.3583163611528684</v>
       </c>
       <c r="F80" t="n">
         <v>0.3680223783093874</v>
@@ -13857,7 +13297,7 @@
         <v>37</v>
       </c>
       <c r="E82" t="n">
-        <v>0.3572370294333511</v>
+        <v>0.3572370294333512</v>
       </c>
       <c r="F82" t="n">
         <v>0.3693886593503816</v>
@@ -13985,10 +13425,10 @@
         <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>0.3564901408509341</v>
+        <v>0.3564901408509342</v>
       </c>
       <c r="F84" t="n">
-        <v>0.3659229801701282</v>
+        <v>0.3659229801701283</v>
       </c>
       <c r="G84" t="n">
         <v>864</v>
@@ -14006,7 +13446,7 @@
         <v>1058</v>
       </c>
       <c r="L84" t="n">
-        <v>1.163100634274087</v>
+        <v>1.163100634274088</v>
       </c>
       <c r="M84" t="n">
         <v>40239</v>
@@ -14177,7 +13617,7 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>0.3558658475588367</v>
+        <v>0.3558658475588368</v>
       </c>
       <c r="F87" t="n">
         <v>0.3600030116439514</v>
@@ -14372,7 +13812,7 @@
         <v>0.35353956958039</v>
       </c>
       <c r="F90" t="n">
-        <v>0.3581746853543885</v>
+        <v>0.3581746853543886</v>
       </c>
       <c r="G90" t="n">
         <v>870</v>
@@ -14564,7 +14004,7 @@
         <v>0.3526744205811833</v>
       </c>
       <c r="F93" t="n">
-        <v>0.3639405362855737</v>
+        <v>0.3639405362855738</v>
       </c>
       <c r="G93" t="n">
         <v>952</v>
@@ -14628,7 +14068,7 @@
         <v>0.3526463906410703</v>
       </c>
       <c r="F94" t="n">
-        <v>0.3698353941668685</v>
+        <v>0.3698353941668686</v>
       </c>
       <c r="G94" t="n">
         <v>2251</v>
@@ -14692,7 +14132,7 @@
         <v>0.3525438283506304</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3611846153372366</v>
+        <v>0.3611846153372367</v>
       </c>
       <c r="G95" t="n">
         <v>2049</v>
@@ -14701,7 +14141,7 @@
         <v>1253</v>
       </c>
       <c r="I95" t="n">
-        <v>9.830101557888099</v>
+        <v>9.830101557888101</v>
       </c>
       <c r="J95" t="n">
         <v>1.672165547340094</v>
@@ -14765,7 +14205,7 @@
         <v>272</v>
       </c>
       <c r="I96" t="n">
-        <v>9.685651153807749</v>
+        <v>9.685651153807747</v>
       </c>
       <c r="J96" t="n">
         <v>1.844155844155844</v>
@@ -14884,7 +14324,7 @@
         <v>0.3504909622986595</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3958613088003835</v>
+        <v>0.3958613088003836</v>
       </c>
       <c r="G98" t="n">
         <v>84138</v>
@@ -15140,7 +14580,7 @@
         <v>0.3484387521769014</v>
       </c>
       <c r="F102" t="n">
-        <v>0.3535277087564429</v>
+        <v>0.353527708756443</v>
       </c>
       <c r="G102" t="n">
         <v>492</v>
@@ -15521,7 +14961,7 @@
         <v>3</v>
       </c>
       <c r="E108" t="n">
-        <v>0.347494206529801</v>
+        <v>0.3474942065298011</v>
       </c>
       <c r="F108" t="n">
         <v>0.35155729286413</v>
@@ -15606,7 +15046,7 @@
         <v>570</v>
       </c>
       <c r="L109" t="n">
-        <v>1.290249093897393</v>
+        <v>1.290249093897392</v>
       </c>
       <c r="M109" t="n">
         <v>36820</v>
@@ -15713,7 +15153,7 @@
         <v>8</v>
       </c>
       <c r="E111" t="n">
-        <v>0.3473161857320109</v>
+        <v>0.347316185732011</v>
       </c>
       <c r="F111" t="n">
         <v>0.3623751540608129</v>
@@ -15917,7 +15357,7 @@
         <v>283</v>
       </c>
       <c r="I114" t="n">
-        <v>7.420144885828749</v>
+        <v>7.42014488582875</v>
       </c>
       <c r="J114" t="n">
         <v>1.744852941176471</v>
@@ -15969,7 +15409,7 @@
         <v>5</v>
       </c>
       <c r="E115" t="n">
-        <v>0.3445387503718536</v>
+        <v>0.3445387503718537</v>
       </c>
       <c r="F115" t="n">
         <v>0.3528937734744636</v>
@@ -16072,7 +15512,7 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>41.646723</v>
+        <v>41.64672299999999</v>
       </c>
       <c r="S116" t="n">
         <v>2.2246395</v>
@@ -16432,7 +15872,7 @@
         <v>6.602240457057126</v>
       </c>
       <c r="J122" t="n">
-        <v>1.787901702412741</v>
+        <v>1.787901702412742</v>
       </c>
       <c r="K122" t="n">
         <v>4009</v>
@@ -16481,10 +15921,10 @@
         <v>4</v>
       </c>
       <c r="E123" t="n">
-        <v>0.3429391711160174</v>
+        <v>0.3429391711160175</v>
       </c>
       <c r="F123" t="n">
-        <v>0.3440759140193893</v>
+        <v>0.3440759140193894</v>
       </c>
       <c r="G123" t="n">
         <v>538</v>
@@ -16566,7 +16006,7 @@
         <v>646</v>
       </c>
       <c r="L124" t="n">
-        <v>0.9733196521415316</v>
+        <v>0.9733196521415315</v>
       </c>
       <c r="M124" t="n">
         <v>31216</v>
@@ -16609,7 +16049,7 @@
         <v>5</v>
       </c>
       <c r="E125" t="n">
-        <v>0.3425745150456661</v>
+        <v>0.3425745150456662</v>
       </c>
       <c r="F125" t="n">
         <v>0.3557973654320494</v>
@@ -16740,7 +16180,7 @@
         <v>0.3419902483940355</v>
       </c>
       <c r="F127" t="n">
-        <v>0.3572916938146931</v>
+        <v>0.3572916938146932</v>
       </c>
       <c r="G127" t="n">
         <v>1002</v>
@@ -16801,10 +16241,10 @@
         <v>4</v>
       </c>
       <c r="E128" t="n">
-        <v>0.341430820854751</v>
+        <v>0.3414308208547511</v>
       </c>
       <c r="F128" t="n">
-        <v>0.3473677125697982</v>
+        <v>0.3473677125697983</v>
       </c>
       <c r="G128" t="n">
         <v>854</v>
@@ -16944,7 +16384,7 @@
         <v>13.05752970235189</v>
       </c>
       <c r="J130" t="n">
-        <v>1.703760406389884</v>
+        <v>1.703760406389883</v>
       </c>
       <c r="K130" t="n">
         <v>642</v>
@@ -16996,7 +16436,7 @@
         <v>0.3404375415268026</v>
       </c>
       <c r="F131" t="n">
-        <v>0.357158660100719</v>
+        <v>0.3571586601007191</v>
       </c>
       <c r="G131" t="n">
         <v>1059</v>
@@ -17014,7 +16454,7 @@
         <v>1600</v>
       </c>
       <c r="L131" t="n">
-        <v>1.5371317652149</v>
+        <v>1.537131765214899</v>
       </c>
       <c r="M131" t="n">
         <v>38612</v>
@@ -17072,13 +16512,13 @@
         <v>9.80337986995522</v>
       </c>
       <c r="J132" t="n">
-        <v>1.655468035167284</v>
+        <v>1.655468035167283</v>
       </c>
       <c r="K132" t="n">
         <v>699</v>
       </c>
       <c r="L132" t="n">
-        <v>1.349917106902032</v>
+        <v>1.349917106902031</v>
       </c>
       <c r="M132" t="n">
         <v>35778</v>
@@ -17249,7 +16689,7 @@
         <v>10</v>
       </c>
       <c r="E135" t="n">
-        <v>0.3397393918684744</v>
+        <v>0.3397393918684745</v>
       </c>
       <c r="F135" t="n">
         <v>0.3490196149426877</v>
@@ -17264,13 +16704,13 @@
         <v>8.025755109182287</v>
       </c>
       <c r="J135" t="n">
-        <v>1.834735224426881</v>
+        <v>1.834735224426882</v>
       </c>
       <c r="K135" t="n">
         <v>1640</v>
       </c>
       <c r="L135" t="n">
-        <v>1.064240131553314</v>
+        <v>1.064240131553315</v>
       </c>
       <c r="M135" t="n">
         <v>36853</v>
@@ -17313,7 +16753,7 @@
         <v>3</v>
       </c>
       <c r="E136" t="n">
-        <v>0.3395182775403216</v>
+        <v>0.3395182775403217</v>
       </c>
       <c r="F136" t="n">
         <v>0.3599042121433954</v>
@@ -17569,10 +17009,10 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3389043976403409</v>
+        <v>0.338904397640341</v>
       </c>
       <c r="F140" t="n">
-        <v>0.3389043976403409</v>
+        <v>0.338904397640341</v>
       </c>
       <c r="G140" t="n">
         <v>32</v>
@@ -17633,10 +17073,10 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>0.3378514600335778</v>
+        <v>0.3378514600335779</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3378514600335778</v>
+        <v>0.3378514600335779</v>
       </c>
       <c r="G141" t="n">
         <v>38</v>
@@ -17956,7 +17396,7 @@
         <v>0.3371538055353117</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3598515295673787</v>
+        <v>0.3598515295673788</v>
       </c>
       <c r="G146" t="n">
         <v>45720</v>
@@ -17968,7 +17408,7 @@
         <v>13.70222885208217</v>
       </c>
       <c r="J146" t="n">
-        <v>2.18702816193344</v>
+        <v>2.187028161933439</v>
       </c>
       <c r="K146" t="n">
         <v>40724</v>
@@ -18084,7 +17524,7 @@
         <v>0.3369303914800811</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3571938683639717</v>
+        <v>0.3571938683639718</v>
       </c>
       <c r="G148" t="n">
         <v>23273</v>
@@ -18093,7 +17533,7 @@
         <v>14540</v>
       </c>
       <c r="I148" t="n">
-        <v>13.06230010984514</v>
+        <v>13.06230010984515</v>
       </c>
       <c r="J148" t="n">
         <v>2.182128026570019</v>
@@ -18148,7 +17588,7 @@
         <v>0.3369069158961846</v>
       </c>
       <c r="F149" t="n">
-        <v>0.3587779566964302</v>
+        <v>0.3587779566964303</v>
       </c>
       <c r="G149" t="n">
         <v>5142</v>
@@ -18209,10 +17649,10 @@
         <v>4</v>
       </c>
       <c r="E150" t="n">
-        <v>0.3367665989826386</v>
+        <v>0.3367665989826387</v>
       </c>
       <c r="F150" t="n">
-        <v>0.3420782775355406</v>
+        <v>0.3420782775355407</v>
       </c>
       <c r="G150" t="n">
         <v>665</v>
@@ -18276,7 +17716,7 @@
         <v>0.3366713227769409</v>
       </c>
       <c r="F151" t="n">
-        <v>0.3413913198707802</v>
+        <v>0.3413913198707803</v>
       </c>
       <c r="G151" t="n">
         <v>526</v>
@@ -18340,7 +17780,7 @@
         <v>0.3366517169307946</v>
       </c>
       <c r="F152" t="n">
-        <v>0.3376971337683271</v>
+        <v>0.3376971337683272</v>
       </c>
       <c r="G152" t="n">
         <v>310</v>
@@ -18465,10 +17905,10 @@
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>0.3363803136276705</v>
+        <v>0.3363803136276706</v>
       </c>
       <c r="F154" t="n">
-        <v>0.3363803136276705</v>
+        <v>0.3363803136276706</v>
       </c>
       <c r="G154" t="n">
         <v>188</v>
@@ -18593,10 +18033,10 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>0.3363593208801403</v>
+        <v>0.3363593208801404</v>
       </c>
       <c r="F156" t="n">
-        <v>0.3363593208801403</v>
+        <v>0.3363593208801404</v>
       </c>
       <c r="G156" t="n">
         <v>11</v>
@@ -18934,7 +18374,7 @@
         <v>1748</v>
       </c>
       <c r="L161" t="n">
-        <v>1.21101184361336</v>
+        <v>1.211011843613359</v>
       </c>
       <c r="M161" t="n">
         <v>35802</v>
@@ -19169,10 +18609,10 @@
         <v>7</v>
       </c>
       <c r="E165" t="n">
-        <v>0.3347382032169316</v>
+        <v>0.3347382032169317</v>
       </c>
       <c r="F165" t="n">
-        <v>0.3428594020778038</v>
+        <v>0.3428594020778039</v>
       </c>
       <c r="G165" t="n">
         <v>925</v>
@@ -19297,7 +18737,7 @@
         <v>3</v>
       </c>
       <c r="E167" t="n">
-        <v>0.3343240645604314</v>
+        <v>0.3343240645604315</v>
       </c>
       <c r="F167" t="n">
         <v>0.3394629336735995</v>
@@ -19745,7 +19185,7 @@
         <v>6</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3336115272062382</v>
+        <v>0.3336115272062383</v>
       </c>
       <c r="F174" t="n">
         <v>0.3366760052169868</v>
@@ -20016,7 +19456,7 @@
         <v>7.098020391957707</v>
       </c>
       <c r="J178" t="n">
-        <v>1.584300132050556</v>
+        <v>1.584300132050557</v>
       </c>
       <c r="K178" t="n">
         <v>557</v>
@@ -20232,7 +19672,7 @@
         <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>41.5001935</v>
+        <v>41.50019349999999</v>
       </c>
       <c r="S181" t="n">
         <v>1.8107835</v>
@@ -20321,7 +19761,7 @@
         <v>10</v>
       </c>
       <c r="E183" t="n">
-        <v>0.3323461046215545</v>
+        <v>0.3323461046215546</v>
       </c>
       <c r="F183" t="n">
         <v>0.3436782720398054</v>
@@ -20388,7 +19828,7 @@
         <v>0.3322064970080352</v>
       </c>
       <c r="F184" t="n">
-        <v>0.3374800212773512</v>
+        <v>0.3374800212773513</v>
       </c>
       <c r="G184" t="n">
         <v>239</v>
@@ -20513,10 +19953,10 @@
         <v>5</v>
       </c>
       <c r="E186" t="n">
-        <v>0.3321529740105023</v>
+        <v>0.3321529740105024</v>
       </c>
       <c r="F186" t="n">
-        <v>0.3370399722029228</v>
+        <v>0.3370399722029229</v>
       </c>
       <c r="G186" t="n">
         <v>361</v>
@@ -20641,7 +20081,7 @@
         <v>14</v>
       </c>
       <c r="E188" t="n">
-        <v>0.3320182686599205</v>
+        <v>0.3320182686599206</v>
       </c>
       <c r="F188" t="n">
         <v>0.3507133388878987</v>
@@ -20781,7 +20221,7 @@
         <v>710</v>
       </c>
       <c r="I190" t="n">
-        <v>7.865038304036035</v>
+        <v>7.865038304036037</v>
       </c>
       <c r="J190" t="n">
         <v>1.461013641648754</v>
@@ -20790,7 +20230,7 @@
         <v>1529</v>
       </c>
       <c r="L190" t="n">
-        <v>1.225822603603632</v>
+        <v>1.225822603603631</v>
       </c>
       <c r="M190" t="n">
         <v>35735</v>
@@ -20833,7 +20273,7 @@
         <v>3</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3314039591001554</v>
+        <v>0.3314039591001555</v>
       </c>
       <c r="F191" t="n">
         <v>0.3365561550999066</v>
@@ -20912,7 +20352,7 @@
         <v>8.953676983482755</v>
       </c>
       <c r="J192" t="n">
-        <v>1.8141777356406</v>
+        <v>1.814177735640599</v>
       </c>
       <c r="K192" t="n">
         <v>7299</v>
@@ -21238,7 +20678,7 @@
         <v>676</v>
       </c>
       <c r="L197" t="n">
-        <v>1.047571718748807</v>
+        <v>1.047571718748806</v>
       </c>
       <c r="M197" t="n">
         <v>31683</v>
@@ -21284,7 +20724,7 @@
         <v>0.330252210035711</v>
       </c>
       <c r="F198" t="n">
-        <v>0.3341488848573328</v>
+        <v>0.3341488848573329</v>
       </c>
       <c r="G198" t="n">
         <v>351</v>
@@ -21412,7 +20852,7 @@
         <v>0.3302155520851952</v>
       </c>
       <c r="F200" t="n">
-        <v>0.3428193247519909</v>
+        <v>0.342819324751991</v>
       </c>
       <c r="G200" t="n">
         <v>1073</v>
@@ -21473,10 +20913,10 @@
         <v>6</v>
       </c>
       <c r="E201" t="n">
-        <v>0.3301903660471358</v>
+        <v>0.3301903660471359</v>
       </c>
       <c r="F201" t="n">
-        <v>0.3335031463741962</v>
+        <v>0.3335031463741963</v>
       </c>
       <c r="G201" t="n">
         <v>636</v>
@@ -21537,10 +20977,10 @@
         <v>2</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3301301662951726</v>
+        <v>0.3301301662951727</v>
       </c>
       <c r="F202" t="n">
-        <v>0.3305676266655823</v>
+        <v>0.3305676266655824</v>
       </c>
       <c r="G202" t="n">
         <v>384</v>
@@ -21558,7 +20998,7 @@
         <v>404</v>
       </c>
       <c r="L202" t="n">
-        <v>0.993269648284846</v>
+        <v>0.9932696482848459</v>
       </c>
       <c r="M202" t="n">
         <v>31361</v>
@@ -21665,7 +21105,7 @@
         <v>41</v>
       </c>
       <c r="E204" t="n">
-        <v>0.3299831200654829</v>
+        <v>0.329983120065483</v>
       </c>
       <c r="F204" t="n">
         <v>0.3498282146338849</v>
@@ -21707,7 +21147,7 @@
         <v>39.67150431707317</v>
       </c>
       <c r="S204" t="n">
-        <v>-0.2472086585365853</v>
+        <v>-0.2472086585365854</v>
       </c>
       <c r="T204" t="n">
         <v>203</v>
@@ -21857,10 +21297,10 @@
         <v>3</v>
       </c>
       <c r="E207" t="n">
-        <v>0.329699968051822</v>
+        <v>0.3296999680518221</v>
       </c>
       <c r="F207" t="n">
-        <v>0.335309120694591</v>
+        <v>0.3353091206945911</v>
       </c>
       <c r="G207" t="n">
         <v>558</v>
@@ -21921,7 +21361,7 @@
         <v>4</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3296807485305449</v>
+        <v>0.329680748530545</v>
       </c>
       <c r="F208" t="n">
         <v>0.3347690163770282</v>
@@ -21988,7 +21428,7 @@
         <v>0.3296353943204953</v>
       </c>
       <c r="F209" t="n">
-        <v>0.3396426098913377</v>
+        <v>0.3396426098913378</v>
       </c>
       <c r="G209" t="n">
         <v>1800</v>
@@ -22049,10 +21489,10 @@
         <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>0.3295647809053258</v>
+        <v>0.3295647809053259</v>
       </c>
       <c r="F210" t="n">
-        <v>0.3295647809053258</v>
+        <v>0.3295647809053259</v>
       </c>
       <c r="G210" t="n">
         <v>273</v>
@@ -22244,7 +21684,7 @@
         <v>0.329220750345429</v>
       </c>
       <c r="F213" t="n">
-        <v>0.3328598224838199</v>
+        <v>0.33285982248382</v>
       </c>
       <c r="G213" t="n">
         <v>626</v>
@@ -22369,10 +21809,10 @@
         <v>1</v>
       </c>
       <c r="E215" t="n">
-        <v>0.3288520458387898</v>
+        <v>0.3288520458387899</v>
       </c>
       <c r="F215" t="n">
-        <v>0.3288520458387898</v>
+        <v>0.3288520458387899</v>
       </c>
       <c r="G215" t="n">
         <v>22</v>
@@ -22817,7 +22257,7 @@
         <v>4</v>
       </c>
       <c r="E222" t="n">
-        <v>0.3281578627481791</v>
+        <v>0.3281578627481792</v>
       </c>
       <c r="F222" t="n">
         <v>0.3483945112197996</v>
@@ -23021,7 +22461,7 @@
         <v>188</v>
       </c>
       <c r="I225" t="n">
-        <v>9.317843498537416</v>
+        <v>9.317843498537417</v>
       </c>
       <c r="J225" t="n">
         <v>1.487108013937282</v>
@@ -23085,7 +22525,7 @@
         <v>861</v>
       </c>
       <c r="I226" t="n">
-        <v>9.689084092686649</v>
+        <v>9.689084092686647</v>
       </c>
       <c r="J226" t="n">
         <v>1.876049117562184</v>
@@ -23393,10 +22833,10 @@
         <v>3</v>
       </c>
       <c r="E231" t="n">
-        <v>0.3260987262923089</v>
+        <v>0.326098726292309</v>
       </c>
       <c r="F231" t="n">
-        <v>0.3345181867520292</v>
+        <v>0.3345181867520293</v>
       </c>
       <c r="G231" t="n">
         <v>446</v>
@@ -23521,10 +22961,10 @@
         <v>1</v>
       </c>
       <c r="E233" t="n">
-        <v>0.3258861843347507</v>
+        <v>0.3258861843347508</v>
       </c>
       <c r="F233" t="n">
-        <v>0.3258861843347507</v>
+        <v>0.3258861843347508</v>
       </c>
       <c r="G233" t="n">
         <v>102</v>
@@ -23585,10 +23025,10 @@
         <v>4</v>
       </c>
       <c r="E234" t="n">
-        <v>0.3257486488970021</v>
+        <v>0.3257486488970022</v>
       </c>
       <c r="F234" t="n">
-        <v>0.3313379288951161</v>
+        <v>0.3313379288951162</v>
       </c>
       <c r="G234" t="n">
         <v>753</v>
@@ -23905,10 +23345,10 @@
         <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>0.3255640243350475</v>
+        <v>0.3255640243350476</v>
       </c>
       <c r="F239" t="n">
-        <v>0.3255640243350475</v>
+        <v>0.3255640243350476</v>
       </c>
       <c r="G239" t="n">
         <v>92</v>
@@ -24033,10 +23473,10 @@
         <v>1</v>
       </c>
       <c r="E241" t="n">
-        <v>0.3254302555153422</v>
+        <v>0.3254302555153423</v>
       </c>
       <c r="F241" t="n">
-        <v>0.3254302555153422</v>
+        <v>0.3254302555153423</v>
       </c>
       <c r="G241" t="n">
         <v>267</v>
@@ -24112,7 +23552,7 @@
         <v>12.08517876777488</v>
       </c>
       <c r="J242" t="n">
-        <v>2.19399906119057</v>
+        <v>2.193999061190571</v>
       </c>
       <c r="K242" t="n">
         <v>15372</v>
@@ -24417,10 +23857,10 @@
         <v>1</v>
       </c>
       <c r="E247" t="n">
-        <v>0.3250442398952365</v>
+        <v>0.3250442398952366</v>
       </c>
       <c r="F247" t="n">
-        <v>0.3250442398952365</v>
+        <v>0.3250442398952366</v>
       </c>
       <c r="G247" t="n">
         <v>193</v>
@@ -24609,7 +24049,7 @@
         <v>6</v>
       </c>
       <c r="E250" t="n">
-        <v>0.3246494190107556</v>
+        <v>0.3246494190107557</v>
       </c>
       <c r="F250" t="n">
         <v>0.3339422166650123</v>
@@ -24624,7 +24064,7 @@
         <v>14.05672251361634</v>
       </c>
       <c r="J250" t="n">
-        <v>1.82621140555351</v>
+        <v>1.826211405553511</v>
       </c>
       <c r="K250" t="n">
         <v>842</v>
@@ -24712,7 +24152,7 @@
         <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>41.62632163636364</v>
+        <v>41.62632163636363</v>
       </c>
       <c r="S251" t="n">
         <v>2.299966</v>
@@ -25581,7 +25021,7 @@
         <v>187</v>
       </c>
       <c r="I265" t="n">
-        <v>9.127212594191391</v>
+        <v>9.127212594191393</v>
       </c>
       <c r="J265" t="n">
         <v>1.588806660499537</v>
@@ -25675,7 +25115,7 @@
         <v>38.40051353846154</v>
       </c>
       <c r="S266" t="n">
-        <v>-0.4339552307692307</v>
+        <v>-0.4339552307692308</v>
       </c>
       <c r="T266" t="n">
         <v>265</v>
@@ -25697,10 +25137,10 @@
         <v>1</v>
       </c>
       <c r="E267" t="n">
-        <v>0.3230905431231859</v>
+        <v>0.323090543123186</v>
       </c>
       <c r="F267" t="n">
-        <v>0.3230905431231859</v>
+        <v>0.323090543123186</v>
       </c>
       <c r="G267" t="n">
         <v>18</v>
@@ -25889,10 +25329,10 @@
         <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>0.3228713337193747</v>
+        <v>0.3228713337193748</v>
       </c>
       <c r="F270" t="n">
-        <v>0.3228713337193747</v>
+        <v>0.3228713337193748</v>
       </c>
       <c r="G270" t="n">
         <v>77</v>
@@ -25953,7 +25393,7 @@
         <v>12</v>
       </c>
       <c r="E271" t="n">
-        <v>0.322806648431384</v>
+        <v>0.3228066484313841</v>
       </c>
       <c r="F271" t="n">
         <v>0.3360812302462473</v>
@@ -26209,10 +25649,10 @@
         <v>1</v>
       </c>
       <c r="E275" t="n">
-        <v>0.3222172051185519</v>
+        <v>0.322217205118552</v>
       </c>
       <c r="F275" t="n">
-        <v>0.3222172051185519</v>
+        <v>0.322217205118552</v>
       </c>
       <c r="G275" t="n">
         <v>27</v>
@@ -26465,10 +25905,10 @@
         <v>1</v>
       </c>
       <c r="E279" t="n">
-        <v>0.3217571277854826</v>
+        <v>0.3217571277854827</v>
       </c>
       <c r="F279" t="n">
-        <v>0.3217571277854826</v>
+        <v>0.3217571277854827</v>
       </c>
       <c r="G279" t="n">
         <v>31</v>
@@ -26532,7 +25972,7 @@
         <v>0.3217503126052968</v>
       </c>
       <c r="F280" t="n">
-        <v>0.354685472353778</v>
+        <v>0.3546854723537781</v>
       </c>
       <c r="G280" t="n">
         <v>66968</v>
@@ -26544,7 +25984,7 @@
         <v>10.59990746047573</v>
       </c>
       <c r="J280" t="n">
-        <v>2.146141140670536</v>
+        <v>2.146141140670535</v>
       </c>
       <c r="K280" t="n">
         <v>73233</v>
@@ -26608,7 +26048,7 @@
         <v>6.318060469808222</v>
       </c>
       <c r="J281" t="n">
-        <v>1.89079619733629</v>
+        <v>1.890796197336291</v>
       </c>
       <c r="K281" t="n">
         <v>4103</v>
@@ -26660,7 +26100,7 @@
         <v>0.321667871880153</v>
       </c>
       <c r="F282" t="n">
-        <v>0.3312283422949549</v>
+        <v>0.331228342294955</v>
       </c>
       <c r="G282" t="n">
         <v>1887</v>
@@ -26788,7 +26228,7 @@
         <v>0.3214737592160181</v>
       </c>
       <c r="F284" t="n">
-        <v>0.3399375209895033</v>
+        <v>0.3399375209895034</v>
       </c>
       <c r="G284" t="n">
         <v>2359</v>
@@ -26977,10 +26417,10 @@
         <v>1</v>
       </c>
       <c r="E287" t="n">
-        <v>0.3211166405134282</v>
+        <v>0.3211166405134283</v>
       </c>
       <c r="F287" t="n">
-        <v>0.3211166405134282</v>
+        <v>0.3211166405134283</v>
       </c>
       <c r="G287" t="n">
         <v>254</v>
@@ -27041,10 +26481,10 @@
         <v>11</v>
       </c>
       <c r="E288" t="n">
-        <v>0.321046976166173</v>
+        <v>0.3210469761661731</v>
       </c>
       <c r="F288" t="n">
-        <v>0.3359631230912986</v>
+        <v>0.3359631230912987</v>
       </c>
       <c r="G288" t="n">
         <v>1688</v>
@@ -27105,7 +26545,7 @@
         <v>2</v>
       </c>
       <c r="E289" t="n">
-        <v>0.3210409320102232</v>
+        <v>0.3210409320102233</v>
       </c>
       <c r="F289" t="n">
         <v>0.3213055618329161</v>
@@ -27233,7 +26673,7 @@
         <v>2</v>
       </c>
       <c r="E291" t="n">
-        <v>0.3206551345760859</v>
+        <v>0.320655134576086</v>
       </c>
       <c r="F291" t="n">
         <v>0.3242809762293826</v>
@@ -27245,7 +26685,7 @@
         <v>161</v>
       </c>
       <c r="I291" t="n">
-        <v>10.93152762946478</v>
+        <v>10.93152762946477</v>
       </c>
       <c r="J291" t="n">
         <v>1.946949602122016</v>
@@ -27364,7 +26804,7 @@
         <v>0.3204368209897947</v>
       </c>
       <c r="F293" t="n">
-        <v>0.3326685353903736</v>
+        <v>0.3326685353903737</v>
       </c>
       <c r="G293" t="n">
         <v>685</v>
@@ -27489,10 +26929,10 @@
         <v>1</v>
       </c>
       <c r="E295" t="n">
-        <v>0.3203380850853581</v>
+        <v>0.3203380850853582</v>
       </c>
       <c r="F295" t="n">
-        <v>0.3203380850853581</v>
+        <v>0.3203380850853582</v>
       </c>
       <c r="G295" t="n">
         <v>259</v>
@@ -27556,7 +26996,7 @@
         <v>0.3202470414526689</v>
       </c>
       <c r="F296" t="n">
-        <v>0.3247176724269185</v>
+        <v>0.3247176724269186</v>
       </c>
       <c r="G296" t="n">
         <v>159</v>
@@ -27684,7 +27124,7 @@
         <v>0.3202320683080685</v>
       </c>
       <c r="F298" t="n">
-        <v>0.3290600334387848</v>
+        <v>0.3290600334387849</v>
       </c>
       <c r="G298" t="n">
         <v>605</v>
@@ -27760,7 +27200,7 @@
         <v>6.155503853201426</v>
       </c>
       <c r="J299" t="n">
-        <v>1.777033492822966</v>
+        <v>1.777033492822967</v>
       </c>
       <c r="K299" t="n">
         <v>503</v>
@@ -28257,10 +27697,10 @@
         <v>1</v>
       </c>
       <c r="E307" t="n">
-        <v>0.3191475100336163</v>
+        <v>0.3191475100336164</v>
       </c>
       <c r="F307" t="n">
-        <v>0.3191475100336163</v>
+        <v>0.3191475100336164</v>
       </c>
       <c r="G307" t="n">
         <v>156</v>
@@ -28424,7 +27864,7 @@
         <v>1</v>
       </c>
       <c r="R309" t="n">
-        <v>38.35649095918368</v>
+        <v>38.35649095918367</v>
       </c>
       <c r="S309" t="n">
         <v>-0.4861343714285714</v>
@@ -28461,7 +27901,7 @@
         <v>391</v>
       </c>
       <c r="I310" t="n">
-        <v>9.275179886400499</v>
+        <v>9.275179886400501</v>
       </c>
       <c r="J310" t="n">
         <v>2.012082228116711</v>
@@ -28470,7 +27910,7 @@
         <v>602</v>
       </c>
       <c r="L310" t="n">
-        <v>0.968516827655492</v>
+        <v>0.9685168276554921</v>
       </c>
       <c r="M310" t="n">
         <v>32708</v>
@@ -28513,10 +27953,10 @@
         <v>12</v>
       </c>
       <c r="E311" t="n">
-        <v>0.3187239765688959</v>
+        <v>0.318723976568896</v>
       </c>
       <c r="F311" t="n">
-        <v>0.3271661386202826</v>
+        <v>0.3271661386202827</v>
       </c>
       <c r="G311" t="n">
         <v>1784</v>
@@ -28644,7 +28084,7 @@
         <v>0.3186458887224272</v>
       </c>
       <c r="F313" t="n">
-        <v>0.3221233235308547</v>
+        <v>0.3221233235308548</v>
       </c>
       <c r="G313" t="n">
         <v>313</v>
@@ -28662,7 +28102,7 @@
         <v>325</v>
       </c>
       <c r="L313" t="n">
-        <v>0.991435799601858</v>
+        <v>0.9914357996018581</v>
       </c>
       <c r="M313" t="n">
         <v>32501</v>
@@ -28784,7 +28224,7 @@
         <v>10.1736516433682</v>
       </c>
       <c r="J315" t="n">
-        <v>1.558938746438746</v>
+        <v>1.558938746438747</v>
       </c>
       <c r="K315" t="n">
         <v>341</v>
@@ -29089,7 +28529,7 @@
         <v>3</v>
       </c>
       <c r="E320" t="n">
-        <v>0.3182549887196785</v>
+        <v>0.3182549887196786</v>
       </c>
       <c r="F320" t="n">
         <v>0.3188216909457059</v>
@@ -29110,7 +28550,7 @@
         <v>672</v>
       </c>
       <c r="L320" t="n">
-        <v>1.267914973797326</v>
+        <v>1.267914973797327</v>
       </c>
       <c r="M320" t="n">
         <v>27491</v>
@@ -29168,7 +28608,7 @@
         <v>10.00600764545793</v>
       </c>
       <c r="J321" t="n">
-        <v>1.890317567736922</v>
+        <v>1.890317567736923</v>
       </c>
       <c r="K321" t="n">
         <v>334</v>
@@ -29284,7 +28724,7 @@
         <v>0.3178081686324966</v>
       </c>
       <c r="F323" t="n">
-        <v>0.344094364382571</v>
+        <v>0.3440943643825711</v>
       </c>
       <c r="G323" t="n">
         <v>1981</v>
@@ -29348,7 +28788,7 @@
         <v>0.3175382503600953</v>
       </c>
       <c r="F324" t="n">
-        <v>0.3233075797288346</v>
+        <v>0.3233075797288347</v>
       </c>
       <c r="G324" t="n">
         <v>410</v>
@@ -29857,7 +29297,7 @@
         <v>4</v>
       </c>
       <c r="E332" t="n">
-        <v>0.3166344380501802</v>
+        <v>0.3166344380501803</v>
       </c>
       <c r="F332" t="n">
         <v>0.3190591922373012</v>
@@ -29872,7 +29312,7 @@
         <v>13.96103243382594</v>
       </c>
       <c r="J332" t="n">
-        <v>1.898077010938698</v>
+        <v>1.898077010938699</v>
       </c>
       <c r="K332" t="n">
         <v>645</v>
@@ -30177,10 +29617,10 @@
         <v>1</v>
       </c>
       <c r="E337" t="n">
-        <v>0.3164440578764887</v>
+        <v>0.3164440578764888</v>
       </c>
       <c r="F337" t="n">
-        <v>0.3164440578764887</v>
+        <v>0.3164440578764888</v>
       </c>
       <c r="G337" t="n">
         <v>40</v>
@@ -30317,7 +29757,7 @@
         <v>1487</v>
       </c>
       <c r="I339" t="n">
-        <v>7.910923727941268</v>
+        <v>7.910923727941269</v>
       </c>
       <c r="J339" t="n">
         <v>1.738632581223976</v>
@@ -30576,7 +30016,7 @@
         <v>12.37696682640618</v>
       </c>
       <c r="J343" t="n">
-        <v>2.039484942171521</v>
+        <v>2.039484942171522</v>
       </c>
       <c r="K343" t="n">
         <v>12258</v>
@@ -30628,7 +30068,7 @@
         <v>0.3157357496315826</v>
       </c>
       <c r="F344" t="n">
-        <v>0.3307535160440208</v>
+        <v>0.3307535160440209</v>
       </c>
       <c r="G344" t="n">
         <v>584</v>
@@ -30646,7 +30086,7 @@
         <v>519</v>
       </c>
       <c r="L344" t="n">
-        <v>0.9028926897068824</v>
+        <v>0.9028926897068823</v>
       </c>
       <c r="M344" t="n">
         <v>29705</v>
@@ -30753,7 +30193,7 @@
         <v>8</v>
       </c>
       <c r="E346" t="n">
-        <v>0.3157004409217342</v>
+        <v>0.3157004409217343</v>
       </c>
       <c r="F346" t="n">
         <v>0.3309952264876523</v>
@@ -30945,10 +30385,10 @@
         <v>1</v>
       </c>
       <c r="E349" t="n">
-        <v>0.3155853613788213</v>
+        <v>0.3155853613788214</v>
       </c>
       <c r="F349" t="n">
-        <v>0.3155853613788213</v>
+        <v>0.3155853613788214</v>
       </c>
       <c r="G349" t="n">
         <v>15</v>
@@ -31329,10 +30769,10 @@
         <v>1</v>
       </c>
       <c r="E355" t="n">
-        <v>0.3150097940746545</v>
+        <v>0.3150097940746546</v>
       </c>
       <c r="F355" t="n">
-        <v>0.3150097940746545</v>
+        <v>0.3150097940746546</v>
       </c>
       <c r="G355" t="n">
         <v>37</v>
@@ -31457,10 +30897,10 @@
         <v>1</v>
       </c>
       <c r="E357" t="n">
-        <v>0.3148460959716987</v>
+        <v>0.3148460959716988</v>
       </c>
       <c r="F357" t="n">
-        <v>0.3148460959716987</v>
+        <v>0.3148460959716988</v>
       </c>
       <c r="G357" t="n">
         <v>163</v>
@@ -31652,7 +31092,7 @@
         <v>0.3147523774388667</v>
       </c>
       <c r="F360" t="n">
-        <v>0.3215192950258321</v>
+        <v>0.3215192950258322</v>
       </c>
       <c r="G360" t="n">
         <v>1155</v>
@@ -31905,10 +31345,10 @@
         <v>1</v>
       </c>
       <c r="E364" t="n">
-        <v>0.3144971705425547</v>
+        <v>0.3144971705425548</v>
       </c>
       <c r="F364" t="n">
-        <v>0.3144971705425547</v>
+        <v>0.3144971705425548</v>
       </c>
       <c r="G364" t="n">
         <v>72</v>
@@ -31969,10 +31409,10 @@
         <v>1</v>
       </c>
       <c r="E365" t="n">
-        <v>0.3144107114596898</v>
+        <v>0.3144107114596899</v>
       </c>
       <c r="F365" t="n">
-        <v>0.3144107114596898</v>
+        <v>0.3144107114596899</v>
       </c>
       <c r="G365" t="n">
         <v>29</v>
@@ -32033,7 +31473,7 @@
         <v>9</v>
       </c>
       <c r="E366" t="n">
-        <v>0.3143448520914907</v>
+        <v>0.3143448520914908</v>
       </c>
       <c r="F366" t="n">
         <v>0.3232056845014462</v>
@@ -32481,10 +31921,10 @@
         <v>1</v>
       </c>
       <c r="E373" t="n">
-        <v>0.312985779224541</v>
+        <v>0.3129857792245411</v>
       </c>
       <c r="F373" t="n">
-        <v>0.312985779224541</v>
+        <v>0.3129857792245411</v>
       </c>
       <c r="G373" t="n">
         <v>153</v>
@@ -32749,7 +32189,7 @@
         <v>150</v>
       </c>
       <c r="I377" t="n">
-        <v>7.00877505238326</v>
+        <v>7.008775052383259</v>
       </c>
       <c r="J377" t="n">
         <v>1.246612466124661</v>
@@ -32865,10 +32305,10 @@
         <v>1</v>
       </c>
       <c r="E379" t="n">
-        <v>0.3120280817996821</v>
+        <v>0.3120280817996822</v>
       </c>
       <c r="F379" t="n">
-        <v>0.3120280817996821</v>
+        <v>0.3120280817996822</v>
       </c>
       <c r="G379" t="n">
         <v>26</v>
@@ -32929,10 +32369,10 @@
         <v>1</v>
       </c>
       <c r="E380" t="n">
-        <v>0.3119869431567872</v>
+        <v>0.3119869431567873</v>
       </c>
       <c r="F380" t="n">
-        <v>0.3119869431567872</v>
+        <v>0.3119869431567873</v>
       </c>
       <c r="G380" t="n">
         <v>104</v>
@@ -32993,7 +32433,7 @@
         <v>2</v>
       </c>
       <c r="E381" t="n">
-        <v>0.3119485255053589</v>
+        <v>0.311948525505359</v>
       </c>
       <c r="F381" t="n">
         <v>0.317922363817449</v>
@@ -33185,7 +32625,7 @@
         <v>2</v>
       </c>
       <c r="E384" t="n">
-        <v>0.3115085337220818</v>
+        <v>0.3115085337220819</v>
       </c>
       <c r="F384" t="n">
         <v>0.3156893620498343</v>
@@ -33249,10 +32689,10 @@
         <v>1</v>
       </c>
       <c r="E385" t="n">
-        <v>0.3113934913705073</v>
+        <v>0.3113934913705074</v>
       </c>
       <c r="F385" t="n">
-        <v>0.3113934913705073</v>
+        <v>0.3113934913705074</v>
       </c>
       <c r="G385" t="n">
         <v>95</v>
@@ -33313,10 +32753,10 @@
         <v>1</v>
       </c>
       <c r="E386" t="n">
-        <v>0.3112667363690339</v>
+        <v>0.311266736369034</v>
       </c>
       <c r="F386" t="n">
-        <v>0.3112667363690339</v>
+        <v>0.311266736369034</v>
       </c>
       <c r="G386" t="n">
         <v>25</v>
@@ -33377,7 +32817,7 @@
         <v>2</v>
       </c>
       <c r="E387" t="n">
-        <v>0.3112113120402724</v>
+        <v>0.3112113120402725</v>
       </c>
       <c r="F387" t="n">
         <v>0.314460858029472</v>
@@ -33441,10 +32881,10 @@
         <v>1</v>
       </c>
       <c r="E388" t="n">
-        <v>0.3111159224342011</v>
+        <v>0.3111159224342012</v>
       </c>
       <c r="F388" t="n">
-        <v>0.3111159224342011</v>
+        <v>0.3111159224342012</v>
       </c>
       <c r="G388" t="n">
         <v>37</v>
@@ -33825,7 +33265,7 @@
         <v>5</v>
       </c>
       <c r="E394" t="n">
-        <v>0.3102056398691096</v>
+        <v>0.3102056398691097</v>
       </c>
       <c r="F394" t="n">
         <v>0.3192455715867416</v>
@@ -33837,7 +33277,7 @@
         <v>618</v>
       </c>
       <c r="I394" t="n">
-        <v>10.05342216980452</v>
+        <v>10.05342216980451</v>
       </c>
       <c r="J394" t="n">
         <v>2.075693360898736</v>
@@ -33892,7 +33332,7 @@
         <v>0.3101660850232988</v>
       </c>
       <c r="F395" t="n">
-        <v>0.3243120795072576</v>
+        <v>0.3243120795072577</v>
       </c>
       <c r="G395" t="n">
         <v>5638</v>
@@ -33968,7 +33408,7 @@
         <v>11.76383295469065</v>
       </c>
       <c r="J396" t="n">
-        <v>1.746942221864823</v>
+        <v>1.746942221864822</v>
       </c>
       <c r="K396" t="n">
         <v>672</v>
@@ -34145,10 +33585,10 @@
         <v>1</v>
       </c>
       <c r="E399" t="n">
-        <v>0.3096426320229223</v>
+        <v>0.3096426320229224</v>
       </c>
       <c r="F399" t="n">
-        <v>0.3096426320229223</v>
+        <v>0.3096426320229224</v>
       </c>
       <c r="G399" t="n">
         <v>50</v>
@@ -34212,7 +33652,7 @@
         <v>0.3094646977424613</v>
       </c>
       <c r="F400" t="n">
-        <v>0.3096960199464252</v>
+        <v>0.3096960199464253</v>
       </c>
       <c r="G400" t="n">
         <v>299</v>
@@ -34273,10 +33713,10 @@
         <v>1</v>
       </c>
       <c r="E401" t="n">
-        <v>0.3094338085819328</v>
+        <v>0.3094338085819329</v>
       </c>
       <c r="F401" t="n">
-        <v>0.3094338085819328</v>
+        <v>0.3094338085819329</v>
       </c>
       <c r="G401" t="n">
         <v>190</v>
@@ -34337,10 +33777,10 @@
         <v>1</v>
       </c>
       <c r="E402" t="n">
-        <v>0.3093870291278734</v>
+        <v>0.3093870291278735</v>
       </c>
       <c r="F402" t="n">
-        <v>0.3093870291278734</v>
+        <v>0.3093870291278735</v>
       </c>
       <c r="G402" t="n">
         <v>133</v>
@@ -34529,7 +33969,7 @@
         <v>18</v>
       </c>
       <c r="E405" t="n">
-        <v>0.3090724413734105</v>
+        <v>0.3090724413734106</v>
       </c>
       <c r="F405" t="n">
         <v>0.3224307257577231</v>
@@ -34593,7 +34033,7 @@
         <v>436</v>
       </c>
       <c r="E406" t="n">
-        <v>0.3090579140518368</v>
+        <v>0.3090579140518369</v>
       </c>
       <c r="F406" t="n">
         <v>0.3444812024480358</v>
@@ -34657,7 +34097,7 @@
         <v>22</v>
       </c>
       <c r="E407" t="n">
-        <v>0.3090535297640085</v>
+        <v>0.3090535297640086</v>
       </c>
       <c r="F407" t="n">
         <v>0.3263443137764212</v>
@@ -34678,7 +34118,7 @@
         <v>3078</v>
       </c>
       <c r="L407" t="n">
-        <v>1.21113253280489</v>
+        <v>1.211132532804891</v>
       </c>
       <c r="M407" t="n">
         <v>30427</v>
@@ -35425,10 +34865,10 @@
         <v>1</v>
       </c>
       <c r="E419" t="n">
-        <v>0.307028722324987</v>
+        <v>0.3070287223249871</v>
       </c>
       <c r="F419" t="n">
-        <v>0.307028722324987</v>
+        <v>0.3070287223249871</v>
       </c>
       <c r="G419" t="n">
         <v>38</v>
@@ -35568,7 +35008,7 @@
         <v>7.913010461386512</v>
       </c>
       <c r="J421" t="n">
-        <v>1.751035196687371</v>
+        <v>1.75103519668737</v>
       </c>
       <c r="K421" t="n">
         <v>381</v>
@@ -35681,7 +35121,7 @@
         <v>14</v>
       </c>
       <c r="E423" t="n">
-        <v>0.3064668388202723</v>
+        <v>0.3064668388202724</v>
       </c>
       <c r="F423" t="n">
         <v>0.3171263849706852</v>
@@ -36004,7 +35444,7 @@
         <v>0.3056068954894542</v>
       </c>
       <c r="F428" t="n">
-        <v>0.3222022697792508</v>
+        <v>0.3222022697792509</v>
       </c>
       <c r="G428" t="n">
         <v>5148</v>
@@ -36065,7 +35505,7 @@
         <v>20</v>
       </c>
       <c r="E429" t="n">
-        <v>0.3055782913036606</v>
+        <v>0.3055782913036607</v>
       </c>
       <c r="F429" t="n">
         <v>0.315835867304829</v>
@@ -36086,7 +35526,7 @@
         <v>3389</v>
       </c>
       <c r="L429" t="n">
-        <v>1.161003006042746</v>
+        <v>1.161003006042747</v>
       </c>
       <c r="M429" t="n">
         <v>29827</v>
@@ -36129,10 +35569,10 @@
         <v>1</v>
       </c>
       <c r="E430" t="n">
-        <v>0.3055777951669587</v>
+        <v>0.3055777951669588</v>
       </c>
       <c r="F430" t="n">
-        <v>0.3055777951669587</v>
+        <v>0.3055777951669588</v>
       </c>
       <c r="G430" t="n">
         <v>210</v>
@@ -36705,10 +36145,10 @@
         <v>1</v>
       </c>
       <c r="E439" t="n">
-        <v>0.3040173742022928</v>
+        <v>0.3040173742022929</v>
       </c>
       <c r="F439" t="n">
-        <v>0.3040173742022928</v>
+        <v>0.3040173742022929</v>
       </c>
       <c r="G439" t="n">
         <v>28</v>
@@ -36772,7 +36212,7 @@
         <v>0.303875080186826</v>
       </c>
       <c r="F440" t="n">
-        <v>0.3107946203529896</v>
+        <v>0.3107946203529897</v>
       </c>
       <c r="G440" t="n">
         <v>1106</v>
@@ -36833,10 +36273,10 @@
         <v>1</v>
       </c>
       <c r="E441" t="n">
-        <v>0.3038322072544597</v>
+        <v>0.3038322072544598</v>
       </c>
       <c r="F441" t="n">
-        <v>0.3038322072544597</v>
+        <v>0.3038322072544598</v>
       </c>
       <c r="G441" t="n">
         <v>94</v>
@@ -36897,7 +36337,7 @@
         <v>24</v>
       </c>
       <c r="E442" t="n">
-        <v>0.3037284871873534</v>
+        <v>0.3037284871873535</v>
       </c>
       <c r="F442" t="n">
         <v>0.3163917054120908</v>
@@ -37601,10 +37041,10 @@
         <v>3</v>
       </c>
       <c r="E453" t="n">
-        <v>0.3011101401417282</v>
+        <v>0.3011101401417283</v>
       </c>
       <c r="F453" t="n">
-        <v>0.3051157463326815</v>
+        <v>0.3051157463326816</v>
       </c>
       <c r="G453" t="n">
         <v>428</v>
@@ -37643,7 +37083,7 @@
         <v>39.53594933333333</v>
       </c>
       <c r="S453" t="n">
-        <v>-0.4131933333333333</v>
+        <v>-0.4131933333333334</v>
       </c>
       <c r="T453" t="n">
         <v>452</v>
@@ -37732,7 +37172,7 @@
         <v>0.3009533206352796</v>
       </c>
       <c r="F455" t="n">
-        <v>0.3100245477052818</v>
+        <v>0.3100245477052819</v>
       </c>
       <c r="G455" t="n">
         <v>1951</v>
@@ -37793,10 +37233,10 @@
         <v>1</v>
       </c>
       <c r="E456" t="n">
-        <v>0.3008142620710641</v>
+        <v>0.3008142620710642</v>
       </c>
       <c r="F456" t="n">
-        <v>0.3008142620710641</v>
+        <v>0.3008142620710642</v>
       </c>
       <c r="G456" t="n">
         <v>75</v>
@@ -38070,7 +37510,7 @@
         <v>10257</v>
       </c>
       <c r="L460" t="n">
-        <v>0.9603380913481584</v>
+        <v>0.9603380913481585</v>
       </c>
       <c r="M460" t="n">
         <v>28193</v>
@@ -38192,7 +37632,7 @@
         <v>11.65582751425326</v>
       </c>
       <c r="J462" t="n">
-        <v>1.740500258576812</v>
+        <v>1.740500258576811</v>
       </c>
       <c r="K462" t="n">
         <v>29207</v>
@@ -38217,7 +37657,7 @@
         <v>42.85095603614458</v>
       </c>
       <c r="S462" t="n">
-        <v>-2.677920487951808</v>
+        <v>-2.677920487951807</v>
       </c>
       <c r="T462" t="n">
         <v>461</v>
@@ -38370,7 +37810,7 @@
         <v>0.2974216980227385</v>
       </c>
       <c r="F465" t="n">
-        <v>0.3087666540190922</v>
+        <v>0.3087666540190923</v>
       </c>
       <c r="G465" t="n">
         <v>433</v>
@@ -38495,7 +37935,7 @@
         <v>164</v>
       </c>
       <c r="E467" t="n">
-        <v>0.2967169242625251</v>
+        <v>0.2967169242625252</v>
       </c>
       <c r="F467" t="n">
         <v>0.3169867543189262</v>
@@ -38623,7 +38063,7 @@
         <v>12</v>
       </c>
       <c r="E469" t="n">
-        <v>0.2942561307048359</v>
+        <v>0.294256130704836</v>
       </c>
       <c r="F469" t="n">
         <v>0.3051684946176933</v>
@@ -38754,7 +38194,7 @@
         <v>0.2939417504730179</v>
       </c>
       <c r="F471" t="n">
-        <v>0.3085524535061474</v>
+        <v>0.3085524535061475</v>
       </c>
       <c r="G471" t="n">
         <v>2799</v>
@@ -38958,7 +38398,7 @@
         <v>12.41265615146908</v>
       </c>
       <c r="J474" t="n">
-        <v>1.756206548892384</v>
+        <v>1.756206548892383</v>
       </c>
       <c r="K474" t="n">
         <v>1791</v>
@@ -39497,7 +38937,7 @@
         <v>35.28889113636364</v>
       </c>
       <c r="S482" t="n">
-        <v>-2.946369295454545</v>
+        <v>-2.946369295454546</v>
       </c>
       <c r="T482" t="n">
         <v>481</v>
@@ -39586,7 +39026,7 @@
         <v>0.2894748958897518</v>
       </c>
       <c r="F484" t="n">
-        <v>0.3350688975420893</v>
+        <v>0.3350688975420894</v>
       </c>
       <c r="G484" t="n">
         <v>34198</v>
@@ -39604,7 +39044,7 @@
         <v>36071</v>
       </c>
       <c r="L484" t="n">
-        <v>1.03688677776142</v>
+        <v>1.036886777761419</v>
       </c>
       <c r="M484" t="n">
         <v>31139</v>
@@ -39650,7 +39090,7 @@
         <v>0.289130782821451</v>
       </c>
       <c r="F485" t="n">
-        <v>0.3153751110729922</v>
+        <v>0.3153751110729923</v>
       </c>
       <c r="G485" t="n">
         <v>35560</v>
@@ -39711,10 +39151,10 @@
         <v>3</v>
       </c>
       <c r="E486" t="n">
-        <v>0.2889505129230268</v>
+        <v>0.2889505129230269</v>
       </c>
       <c r="F486" t="n">
-        <v>0.2985986729281932</v>
+        <v>0.2985986729281933</v>
       </c>
       <c r="G486" t="n">
         <v>598</v>
@@ -39775,7 +39215,7 @@
         <v>84</v>
       </c>
       <c r="E487" t="n">
-        <v>0.2886998744632298</v>
+        <v>0.2886998744632299</v>
       </c>
       <c r="F487" t="n">
         <v>0.315863057153002</v>
@@ -39903,10 +39343,10 @@
         <v>1</v>
       </c>
       <c r="E489" t="n">
-        <v>0.2881091710155672</v>
+        <v>0.2881091710155673</v>
       </c>
       <c r="F489" t="n">
-        <v>0.2881091710155672</v>
+        <v>0.2881091710155673</v>
       </c>
       <c r="G489" t="n">
         <v>22</v>
@@ -40098,7 +39538,7 @@
         <v>0.2865922193769849</v>
       </c>
       <c r="F492" t="n">
-        <v>0.2921104624413645</v>
+        <v>0.2921104624413646</v>
       </c>
       <c r="G492" t="n">
         <v>502</v>
@@ -40287,7 +39727,7 @@
         <v>87</v>
       </c>
       <c r="E495" t="n">
-        <v>0.2856866982292256</v>
+        <v>0.2856866982292257</v>
       </c>
       <c r="F495" t="n">
         <v>0.3081897637275707</v>
@@ -40302,7 +39742,7 @@
         <v>8.024810093925742</v>
       </c>
       <c r="J495" t="n">
-        <v>1.698042052441506</v>
+        <v>1.698042052441507</v>
       </c>
       <c r="K495" t="n">
         <v>11687</v>
@@ -40482,7 +39922,7 @@
         <v>0.2842168595442841</v>
       </c>
       <c r="F498" t="n">
-        <v>0.2920491601937034</v>
+        <v>0.2920491601937035</v>
       </c>
       <c r="G498" t="n">
         <v>2458</v>
@@ -40582,7 +40022,7 @@
         <v>1</v>
       </c>
       <c r="R499" t="n">
-        <v>28.48232125925927</v>
+        <v>28.48232125925926</v>
       </c>
       <c r="S499" t="n">
         <v>-16.3161704537037</v>
@@ -40607,10 +40047,10 @@
         <v>253</v>
       </c>
       <c r="E500" t="n">
-        <v>0.2840728243335207</v>
+        <v>0.2840728243335208</v>
       </c>
       <c r="F500" t="n">
-        <v>0.3070093945519804</v>
+        <v>0.3070093945519805</v>
       </c>
       <c r="G500" t="n">
         <v>30848</v>
@@ -41553,7 +40993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41579,6 +41019,16 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>pension</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>precio_m2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>fofm_medio</t>
         </is>
       </c>
@@ -41599,6 +41049,12 @@
         <v>19064.73</v>
       </c>
       <c r="E2" t="n">
+        <v>1463.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2002.33</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -41618,6 +41074,12 @@
         <v>103063.75</v>
       </c>
       <c r="E3" t="n">
+        <v>1479.83</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2995.62</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -41637,6 +41099,12 @@
         <v>5158.04</v>
       </c>
       <c r="E4" t="n">
+        <v>1363.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2016.9</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.27</v>
       </c>
     </row>
@@ -41656,6 +41124,12 @@
         <v>4997.25</v>
       </c>
       <c r="E5" t="n">
+        <v>1818.15</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4757.9</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -41705,7 +41179,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gráfico de barras con los 4 perfiles estratégicos — meter en slides</t>
+          <t>Gráfico de barras con los 4 perfiles estratégicos</t>
         </is>
       </c>
     </row>
@@ -41717,7 +41191,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ranking visual del top 20 municipios — meter en slides</t>
+          <t>Ranking visual del top 20 municipios</t>
         </is>
       </c>
     </row>
@@ -41729,7 +41203,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scatter solvencia vs mercado — meter en slides</t>
+          <t>Scatter solvencia vs tamaño de mercado</t>
         </is>
       </c>
     </row>
